--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.2%</t>
+          <t>430.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.7%</t>
+          <t>-646.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-160.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-304.9%</t>
+          <t>-304.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.121385670672937</v>
+        <v>-4.158103147422342</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.120008052099879</v>
+        <v>1.105321061400117</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.083002008114786</v>
+        <v>-4.11971948486419</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.132780958465508</v>
+        <v>1.118093967765746</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.90588567807962</v>
+        <v>-3.942603154829024</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.200356519324876</v>
+        <v>1.185669528625114</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.950977922913165</v>
+        <v>-3.98769539966257</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.183003013153371</v>
+        <v>1.168316022453609</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.771602501674398</v>
+        <v>-3.808319978423802</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.248540156955292</v>
+        <v>1.23385316625553</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.816616715195004</v>
+        <v>-3.853334191944409</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.21134192687864</v>
+        <v>1.196654936178878</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.083621225467439</v>
+        <v>-4.120338702216844</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.110231685108611</v>
+        <v>1.095544694408849</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.184819006904612</v>
+        <v>-4.221536483654017</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.068956494430243</v>
+        <v>1.054269503730481</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.178308040290299</v>
+        <v>-4.215025517039704</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.069160842630285</v>
+        <v>1.054473851930523</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.159269912583002</v>
+        <v>-4.195987389332407</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.073300812921449</v>
+        <v>1.058613822221687</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.211785714857823</v>
+        <v>-4.248503191607227</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.171588893645711</v>
+        <v>1.156901902945949</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.22565247619174</v>
+        <v>-4.262369952941145</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.166875518098278</v>
+        <v>1.152188527398516</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.180848304651811</v>
+        <v>-4.217565781401215</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.190805717111175</v>
+        <v>1.176118726411414</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.033105334416808</v>
+        <v>-4.069822811166213</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.147853126482376</v>
+        <v>1.133166135782614</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.116926555691506</v>
+        <v>-4.153644032440911</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.117118259503978</v>
+        <v>1.102431268804216</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.110773849638722</v>
+        <v>-4.147491326388127</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.12024169031675</v>
+        <v>1.105554699616988</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.127583147789224</v>
+        <v>-4.164300624538629</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.112598447796659</v>
+        <v>1.097911457096897</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.065285149013102</v>
+        <v>-4.102002625762506</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.203853201103929</v>
+        <v>1.189166210404167</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.863494951347944</v>
+        <v>-3.900212428097348</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.086861281884119</v>
+        <v>1.072174291184357</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.914381664034138</v>
+        <v>-3.951099140783543</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.136796829131817</v>
+        <v>1.122109838432055</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.827770921384331</v>
+        <v>-3.864488398133736</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.186068862307783</v>
+        <v>1.171381871608021</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.887980219389616</v>
+        <v>-3.92469769613902</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.160521123930341</v>
+        <v>1.145834133230579</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.811558172957689</v>
+        <v>-3.848275649707094</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.18958156054304</v>
+        <v>1.174894569843278</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.76718504131912</v>
+        <v>-3.803902518068525</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.207193680633904</v>
+        <v>1.192506689934142</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.789665392178005</v>
+        <v>-3.82638286892741</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.192595334428941</v>
+        <v>1.177908343729179</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.742009661616949</v>
+        <v>-3.778727138366354</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.218039383681168</v>
+        <v>1.203352392981406</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.641491503118194</v>
+        <v>-3.678208979867599</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.263139020455394</v>
+        <v>1.248452029755632</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.625586173685842</v>
+        <v>-3.662303650435247</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.256255824704207</v>
+        <v>1.241568834004446</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.580747772077444</v>
+        <v>-3.617465248826849</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.278288887958195</v>
+        <v>1.263601897258433</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.600246228319452</v>
+        <v>-3.636963705068857</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.27465044509247</v>
+        <v>1.259963454392708</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.556043391233552</v>
+        <v>-3.592760867982956</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.298211182454667</v>
+        <v>1.283524191754905</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.563603057070599</v>
+        <v>-3.600320533820003</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.293597316589096</v>
+        <v>1.278910325889334</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.405311639531326</v>
+        <v>-3.442029116280731</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.408161648787845</v>
+        <v>1.393474658088083</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.19766963589685</v>
+        <v>-3.234387112646255</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.489659154835888</v>
+        <v>1.474972164136126</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.146637543174322</v>
+        <v>-3.183355019923727</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.505020220163169</v>
+        <v>1.490333229463408</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.081413362047116</v>
+        <v>-3.118130838796521</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.548297296706757</v>
+        <v>1.533610306006995</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.043986341975983</v>
+        <v>-3.080703818725387</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.559229077034491</v>
+        <v>1.544542086334729</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.064097998010691</v>
+        <v>-3.100815474760096</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.552441206951848</v>
+        <v>1.537754216252086</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.010353183583486</v>
+        <v>-3.047070660332891</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.73449690374394</v>
+        <v>1.719809913044178</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.935570922558473</v>
+        <v>-2.972288399307878</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.884522717371763</v>
+        <v>1.869835726672001</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.909486838294665</v>
+        <v>-2.94620431504407</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.886664327091145</v>
+        <v>1.871977336391383</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.821608925185545</v>
+        <v>-2.85832640193495</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.920008687918572</v>
+        <v>1.905321697218811</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.812716463792261</v>
+        <v>-2.849433940541666</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.941120078202677</v>
+        <v>1.926433087502915</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.981192580762139</v>
+        <v>-3.017910057511544</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.86558467881931</v>
+        <v>1.850897688119548</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.534936388132699</v>
+        <v>-2.571653864882104</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.025356853058948</v>
+        <v>2.010669862359186</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.512215284449547</v>
+        <v>-2.548932761198952</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.025109317029114</v>
+        <v>2.010422326329351</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.641417097743589</v>
+        <v>-2.678134574492994</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.132334717562665</v>
+        <v>2.117647726862903</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.796198104521845</v>
+        <v>-2.83291558127125</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.10750013734501</v>
+        <v>2.092813146645248</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.789143414306671</v>
+        <v>-2.825860891056076</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.106997369420625</v>
+        <v>2.092310378720862</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.762192189980183</v>
+        <v>-2.798909666729588</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.127784012795961</v>
+        <v>2.113097022096199</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.8981451980365</v>
+        <v>-2.934862674785904</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.257505941718394</v>
+        <v>2.242818951018632</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.920553315841372</v>
+        <v>-2.957270792590776</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.240659389499439</v>
+        <v>2.225972398799676</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.948777551418972</v>
+        <v>-2.985495028168377</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.231423694818036</v>
+        <v>2.216736704118274</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.958218477307502</v>
+        <v>-2.994935954056907</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.283901042184471</v>
+        <v>2.269214051484709</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.010492084643143</v>
+        <v>-3.047209561392548</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.265882693795516</v>
+        <v>2.251195703095753</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.086822062244049</v>
+        <v>-3.123539538993454</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.233462515648928</v>
+        <v>2.218775524949166</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.289075782568402</v>
+        <v>-3.325793259317807</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.147381257122049</v>
+        <v>2.132694266422287</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.450644208095658</v>
+        <v>-3.487361684845062</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.081187897121299</v>
+        <v>2.066500906421537</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.582945500193211</v>
+        <v>-3.619662976942616</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.041340787148197</v>
+        <v>2.026653796448435</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.768813811032441</v>
+        <v>-3.805531287781846</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.958998659595445</v>
+        <v>1.944311668895683</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.796714598141914</v>
+        <v>-3.833432074891319</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.946362385878658</v>
+        <v>1.931675395178896</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.919240700844808</v>
+        <v>-3.955958177594213</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.894116388774699</v>
+        <v>1.879429398074937</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.149755197030396</v>
+        <v>-4.186472673779801</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.868616549890967</v>
+        <v>1.853929559191205</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.40647601502522</v>
+        <v>-4.443193491774625</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.906239941694885</v>
+        <v>1.891552950995123</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.56046243280136</v>
+        <v>-4.597179909550766</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.913625643730068</v>
+        <v>1.898938653030306</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.509940528973694</v>
+        <v>-4.5466580057231</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.919885607381255</v>
+        <v>1.905198616681493</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.762415682981419</v>
+        <v>-4.799133159730824</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.83076603483358</v>
+        <v>1.816079044133817</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.055311439460831</v>
+        <v>-5.092028916210237</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.714818266760759</v>
+        <v>1.700131276060997</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.212855511190273</v>
+        <v>-5.249572987939678</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.655922380296303</v>
+        <v>1.641235389596541</v>
       </c>
       <c r="F2021" t="n">
         <v>0.23732834414886</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.490819906773546</v>
+        <v>-5.527537383522952</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.539814474799183</v>
+        <v>1.525127484099421</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1477086098633758</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.607787599412437</v>
+        <v>-5.644505076161843</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.655231454442671</v>
+        <v>1.640544463742909</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1477086098633758</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.69250554163339</v>
+        <v>-5.729223018382796</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.616190915518104</v>
+        <v>1.601503924818342</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06259258093532938</v>
@@ -48126,10 +48126,10 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.774440359902274</v>
+        <v>-5.811157836651679</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.593646405779042</v>
+        <v>1.57895941507928</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05265783534824919</v>
@@ -48149,10 +48149,10 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.876416482150681</v>
+        <v>-5.913133958900087</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.561781595335581</v>
+        <v>1.547094604635819</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04931828690015838</v>
@@ -48172,10 +48172,10 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.766410198673459</v>
+        <v>-5.803127675422865</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.597936995970645</v>
+        <v>1.583250005270883</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02611371498288317</v>
@@ -48195,10 +48195,10 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.623350622932534</v>
+        <v>-5.66006809968194</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.65941083698899</v>
+        <v>1.644723846289228</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.0181002883929039</v>
@@ -48218,10 +48218,10 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.321903897460697</v>
+        <v>-5.358621374210102</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.787250410060261</v>
+        <v>1.772563419360499</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2833464370789334</v>
@@ -48241,10 +48241,10 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.346494141695881</v>
+        <v>-5.383211618445286</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.778385490118898</v>
+        <v>1.763698499419136</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2833464370789334</v>
@@ -48264,10 +48264,10 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.29545576568936</v>
+        <v>-5.332173242438766</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.799643744901261</v>
+        <v>1.784956754201499</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2833464370789334</v>
@@ -48287,10 +48287,10 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.254316470822729</v>
+        <v>-5.291033947572135</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.835137561722059</v>
+        <v>1.820450571022297</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3244857319455642</v>
@@ -48310,10 +48310,10 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.143710330743128</v>
+        <v>-5.180427807492533</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.695564013877834</v>
+        <v>1.680877023178072</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4350918720251662</v>
@@ -48333,10 +48333,10 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.27429106527397</v>
+        <v>-5.311008542023376</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.646833764139461</v>
+        <v>1.632146773439699</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3045111374943237</v>
@@ -48356,10 +48356,10 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.109794731083008</v>
+        <v>-5.146512207832414</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.697059116891928</v>
+        <v>1.682372126192166</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3045111374943237</v>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.13716466376744</v>
+        <v>-5.173882140516846</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.685298854254585</v>
+        <v>1.670611863554823</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3045111374943237</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.14754985865733</v>
+        <v>-5.184267335406735</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.691013555423702</v>
+        <v>1.676326564723939</v>
       </c>
       <c r="F2037" t="n">
         <v>0.2941259426044344</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.166138017379555</v>
+        <v>-5.20285549412896</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.754415297711237</v>
+        <v>1.739728307011474</v>
       </c>
       <c r="F2038" t="n">
         <v>0.275537783882209</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.166436564075591</v>
+        <v>-5.203154040824996</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.751164889851121</v>
+        <v>1.736477899151359</v>
       </c>
       <c r="F2039" t="n">
         <v>0.275537783882209</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.065613430385163</v>
+        <v>-5.102330907134569</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.796025038266683</v>
+        <v>1.781338047566921</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2880019993665628</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.874832069632756</v>
+        <v>-4.911549546382162</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.872466836046189</v>
+        <v>1.857779845346427</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4787833601189702</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.856315215590936</v>
+        <v>-4.893032692340341</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.859710423400514</v>
+        <v>1.845023432700752</v>
       </c>
       <c r="F2042" t="n">
         <v>0.4917134895441784</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.831122031089618</v>
+        <v>-4.867839507839023</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.9047546338131</v>
+        <v>1.890067643113337</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5169066740454967</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.819067904176655</v>
+        <v>-4.85578538092606</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.903262852479723</v>
+        <v>1.88857586177996</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5289608009584595</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.825691150867013</v>
+        <v>-4.862408627616419</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.902494183987715</v>
+        <v>1.887807193287953</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5223375542681012</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.72281056133842</v>
+        <v>-4.759528038087826</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.956497445677035</v>
+        <v>1.941810454977273</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6252181437966942</v>
@@ -48632,10 +48632,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.746252600518507</v>
+        <v>-4.782970077267913</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.967323300178594</v>
+        <v>1.952636309478832</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6252181437966942</v>
@@ -48655,10 +48655,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.764325108810119</v>
+        <v>-4.801042585559524</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.96009429686195</v>
+        <v>1.945407306162187</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6252181437966942</v>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.995498902686751</v>
+        <v>-5.032216379436156</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.827876692904763</v>
+        <v>1.813189702205001</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6252181437966942</v>
@@ -48701,10 +48701,10 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.964212882146295</v>
+        <v>-5.000930358895701</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.847413720117886</v>
+        <v>1.832726729418123</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6565041643371495</v>
@@ -48724,10 +48724,10 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.811187490033011</v>
+        <v>-4.847904966782417</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.007794876536103</v>
+        <v>1.993107885836341</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8095295564504337</v>
@@ -48747,10 +48747,10 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.839494803906281</v>
+        <v>-4.876212280655687</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.183938175895088</v>
+        <v>2.169251185195326</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8095295564504337</v>
@@ -48770,10 +48770,10 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.006088029019804</v>
+        <v>-5.042805505769209</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.086703837203761</v>
+        <v>2.072016846503999</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6429363313369112</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.419029664292874</v>
+        <v>3.798017350053306</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.831765586254543</v>
+        <v>-4.844977937074891</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.160109216971583</v>
+        <v>2.154824276643444</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6429363313369112</v>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-646.1%</t>
+          <t>-648.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.7%</t>
+          <t>-161.7%</t>
         </is>
       </c>
     </row>
@@ -48793,10 +48793,10 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.844977937074891</v>
+        <v>-4.869741126386909</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.154824276643444</v>
+        <v>2.144919000918637</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6429363313369112</v>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>49.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.0%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.3%</t>
+          <t>430.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-648.5%</t>
+          <t>-635.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-156.7%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-304.3%</t>
+          <t>-304.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.158103147422342</v>
+        <v>-4.121385670672937</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.105321061400117</v>
+        <v>1.120008052099879</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.11971948486419</v>
+        <v>-4.083002008114786</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.118093967765746</v>
+        <v>1.132780958465508</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.942603154829024</v>
+        <v>-3.90588567807962</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.185669528625114</v>
+        <v>1.200356519324876</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.98769539966257</v>
+        <v>-3.950977922913165</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.168316022453609</v>
+        <v>1.183003013153371</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.808319978423802</v>
+        <v>-3.771602501674398</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.23385316625553</v>
+        <v>1.248540156955292</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.853334191944409</v>
+        <v>-3.816616715195004</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.196654936178878</v>
+        <v>1.21134192687864</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.120338702216844</v>
+        <v>-4.083621225467439</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.095544694408849</v>
+        <v>1.110231685108611</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.221536483654017</v>
+        <v>-4.184819006904612</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.054269503730481</v>
+        <v>1.068956494430243</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.215025517039704</v>
+        <v>-4.178308040290299</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.054473851930523</v>
+        <v>1.069160842630285</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.195987389332407</v>
+        <v>-4.159269912583002</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.058613822221687</v>
+        <v>1.073300812921449</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.248503191607227</v>
+        <v>-4.211785714857823</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.156901902945949</v>
+        <v>1.171588893645711</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.262369952941145</v>
+        <v>-4.22565247619174</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.152188527398516</v>
+        <v>1.166875518098278</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.217565781401215</v>
+        <v>-4.180848304651811</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.176118726411414</v>
+        <v>1.190805717111175</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.069822811166213</v>
+        <v>-4.033105334416808</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.133166135782614</v>
+        <v>1.147853126482376</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.153644032440911</v>
+        <v>-4.116926555691506</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.102431268804216</v>
+        <v>1.117118259503978</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.147491326388127</v>
+        <v>-4.110773849638722</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.105554699616988</v>
+        <v>1.12024169031675</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.164300624538629</v>
+        <v>-4.127583147789224</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.097911457096897</v>
+        <v>1.112598447796659</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.102002625762506</v>
+        <v>-4.065285149013102</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.189166210404167</v>
+        <v>1.203853201103929</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.900212428097348</v>
+        <v>-3.863494951347944</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.072174291184357</v>
+        <v>1.086861281884119</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.951099140783543</v>
+        <v>-3.914381664034138</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.122109838432055</v>
+        <v>1.136796829131817</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.864488398133736</v>
+        <v>-3.827770921384331</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.171381871608021</v>
+        <v>1.186068862307783</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.92469769613902</v>
+        <v>-3.887980219389616</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.145834133230579</v>
+        <v>1.160521123930341</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.848275649707094</v>
+        <v>-3.811558172957689</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.174894569843278</v>
+        <v>1.18958156054304</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.803902518068525</v>
+        <v>-3.76718504131912</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.192506689934142</v>
+        <v>1.207193680633904</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.82638286892741</v>
+        <v>-3.789665392178005</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.177908343729179</v>
+        <v>1.192595334428941</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.778727138366354</v>
+        <v>-3.742009661616949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.203352392981406</v>
+        <v>1.218039383681168</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.678208979867599</v>
+        <v>-3.641491503118194</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.248452029755632</v>
+        <v>1.263139020455394</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.662303650435247</v>
+        <v>-3.625586173685842</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.241568834004446</v>
+        <v>1.256255824704207</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.617465248826849</v>
+        <v>-3.580747772077444</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.263601897258433</v>
+        <v>1.278288887958195</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.636963705068857</v>
+        <v>-3.600246228319452</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.259963454392708</v>
+        <v>1.27465044509247</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.592760867982956</v>
+        <v>-3.556043391233552</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.283524191754905</v>
+        <v>1.298211182454667</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.600320533820003</v>
+        <v>-3.563603057070599</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.278910325889334</v>
+        <v>1.293597316589096</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.442029116280731</v>
+        <v>-3.405311639531326</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.393474658088083</v>
+        <v>1.408161648787845</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.234387112646255</v>
+        <v>-3.19766963589685</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.474972164136126</v>
+        <v>1.489659154835888</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.183355019923727</v>
+        <v>-3.146637543174322</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.490333229463408</v>
+        <v>1.505020220163169</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.118130838796521</v>
+        <v>-3.081413362047116</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.533610306006995</v>
+        <v>1.548297296706757</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.080703818725387</v>
+        <v>-3.043986341975983</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.544542086334729</v>
+        <v>1.559229077034491</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.100815474760096</v>
+        <v>-3.064097998010691</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.537754216252086</v>
+        <v>1.552441206951848</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.047070660332891</v>
+        <v>-3.010353183583486</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.719809913044178</v>
+        <v>1.73449690374394</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.972288399307878</v>
+        <v>-2.935570922558473</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.869835726672001</v>
+        <v>1.884522717371763</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.94620431504407</v>
+        <v>-2.909486838294665</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.871977336391383</v>
+        <v>1.886664327091145</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.85832640193495</v>
+        <v>-2.821608925185545</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.905321697218811</v>
+        <v>1.920008687918572</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.849433940541666</v>
+        <v>-2.812716463792261</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.926433087502915</v>
+        <v>1.941120078202677</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.017910057511544</v>
+        <v>-2.981192580762139</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.850897688119548</v>
+        <v>1.86558467881931</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.571653864882104</v>
+        <v>-2.534936388132699</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.010669862359186</v>
+        <v>2.025356853058948</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.548932761198952</v>
+        <v>-2.512215284449547</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.010422326329351</v>
+        <v>2.025109317029114</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.678134574492994</v>
+        <v>-2.641417097743589</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.117647726862903</v>
+        <v>2.132334717562665</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.83291558127125</v>
+        <v>-2.796198104521845</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.092813146645248</v>
+        <v>2.10750013734501</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.825860891056076</v>
+        <v>-2.789143414306671</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.092310378720862</v>
+        <v>2.106997369420625</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.798909666729588</v>
+        <v>-2.762192189980183</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.113097022096199</v>
+        <v>2.127784012795961</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.934862674785904</v>
+        <v>-2.808661282460166</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.242818951018632</v>
+        <v>2.293299507948928</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.957270792590776</v>
+        <v>-2.831069400265038</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.225972398799676</v>
+        <v>2.276452955729972</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.985495028168377</v>
+        <v>-2.859293635842638</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.216736704118274</v>
+        <v>2.267217261048569</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.994935954056907</v>
+        <v>-2.868734561731168</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.269214051484709</v>
+        <v>2.319694608415005</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.047209561392548</v>
+        <v>-2.921008169066809</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.251195703095753</v>
+        <v>2.301676260026049</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.123539538993454</v>
+        <v>-2.997338146667715</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.218775524949166</v>
+        <v>2.269256081879462</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.325793259317807</v>
+        <v>-3.199591866992069</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.132694266422287</v>
+        <v>2.183174823352583</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.487361684845062</v>
+        <v>-3.361160292519324</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.066500906421537</v>
+        <v>2.116981463351833</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.619662976942616</v>
+        <v>-3.493461584616877</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.026653796448435</v>
+        <v>2.07713435337873</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.805531287781846</v>
+        <v>-3.679329895456107</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.944311668895683</v>
+        <v>1.994792225825978</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.833432074891319</v>
+        <v>-3.70723068256558</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.931675395178896</v>
+        <v>1.982155952109191</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.955958177594213</v>
+        <v>-3.829756785268474</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.879429398074937</v>
+        <v>1.929909955005233</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.186472673779801</v>
+        <v>-4.060271281454063</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.853929559191205</v>
+        <v>1.9044101161215</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.443193491774625</v>
+        <v>-4.316992099448887</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.891552950995123</v>
+        <v>1.942033507925418</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.597179909550766</v>
+        <v>-4.470978517225028</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.898938653030306</v>
+        <v>1.949419209960602</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.5466580057231</v>
+        <v>-4.420456613397362</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.905198616681493</v>
+        <v>1.955679173611788</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.799133159730824</v>
+        <v>-4.672931767405086</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.816079044133817</v>
+        <v>1.866559601064113</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.092028916210237</v>
+        <v>-4.965827523884498</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.700131276060997</v>
+        <v>1.750611832991292</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.249572987939678</v>
+        <v>-5.12337159561394</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.641235389596541</v>
+        <v>1.691715946526836</v>
       </c>
       <c r="F2021" t="n">
         <v>0.23732834414886</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.527537383522952</v>
+        <v>-5.401335991197214</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.525127484099421</v>
+        <v>1.575608041029716</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1477086098633758</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.644505076161843</v>
+        <v>-5.518303683836105</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.640544463742909</v>
+        <v>1.691025020673204</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1477086098633758</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.729223018382796</v>
+        <v>-5.603021626057058</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.601503924818342</v>
+        <v>1.651984481748637</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06259258093532938</v>
@@ -48126,10 +48126,10 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.811157836651679</v>
+        <v>-5.684956444325941</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.57895941507928</v>
+        <v>1.629439972009575</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05265783534824919</v>
@@ -48149,10 +48149,10 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.913133958900087</v>
+        <v>-5.786932566574349</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.547094604635819</v>
+        <v>1.597575161566114</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04931828690015838</v>
@@ -48172,10 +48172,10 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.803127675422865</v>
+        <v>-5.676926283097127</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.583250005270883</v>
+        <v>1.633730562201178</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02611371498288317</v>
@@ -48195,10 +48195,10 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.66006809968194</v>
+        <v>-5.533866707356202</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.644723846289228</v>
+        <v>1.695204403219523</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.0181002883929039</v>
@@ -48218,10 +48218,10 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.358621374210102</v>
+        <v>-5.232419981884364</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.772563419360499</v>
+        <v>1.823043976290794</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2833464370789334</v>
@@ -48241,10 +48241,10 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.383211618445286</v>
+        <v>-5.257010226119548</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.763698499419136</v>
+        <v>1.814179056349431</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2833464370789334</v>
@@ -48264,10 +48264,10 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.332173242438766</v>
+        <v>-5.205971850113028</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.784956754201499</v>
+        <v>1.835437311131794</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2833464370789334</v>
@@ -48287,10 +48287,10 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.291033947572135</v>
+        <v>-5.164832555246397</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.820450571022297</v>
+        <v>1.870931127952592</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3244857319455642</v>
@@ -48310,10 +48310,10 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.180427807492533</v>
+        <v>-5.054226415166795</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.680877023178072</v>
+        <v>1.731357580108367</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4350918720251662</v>
@@ -48333,10 +48333,10 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.311008542023376</v>
+        <v>-5.184807149697638</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.632146773439699</v>
+        <v>1.682627330369994</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3045111374943237</v>
@@ -48356,10 +48356,10 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.146512207832414</v>
+        <v>-5.020310815506676</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.682372126192166</v>
+        <v>1.732852683122461</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3045111374943237</v>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.173882140516846</v>
+        <v>-5.047680748191108</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.670611863554823</v>
+        <v>1.721092420485118</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3045111374943237</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.184267335406735</v>
+        <v>-5.058065943080997</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.676326564723939</v>
+        <v>1.726807121654235</v>
       </c>
       <c r="F2037" t="n">
         <v>0.2941259426044344</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.20285549412896</v>
+        <v>-5.076654101803222</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.739728307011474</v>
+        <v>1.79020886394177</v>
       </c>
       <c r="F2038" t="n">
         <v>0.275537783882209</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.203154040824996</v>
+        <v>-5.076952648499258</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.736477899151359</v>
+        <v>1.786958456081654</v>
       </c>
       <c r="F2039" t="n">
         <v>0.275537783882209</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.102330907134569</v>
+        <v>-4.97612951480883</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.781338047566921</v>
+        <v>1.831818604497216</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2880019993665628</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.911549546382162</v>
+        <v>-4.785348154056424</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.857779845346427</v>
+        <v>1.908260402276722</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4787833601189702</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.893032692340341</v>
+        <v>-4.766831300014603</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.845023432700752</v>
+        <v>1.895503989631047</v>
       </c>
       <c r="F2042" t="n">
         <v>0.4917134895441784</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.867839507839023</v>
+        <v>-4.741638115513285</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.890067643113337</v>
+        <v>1.940548200043633</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5169066740454967</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.85578538092606</v>
+        <v>-4.729583988600322</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.88857586177996</v>
+        <v>1.939056418710256</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5289608009584595</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.862408627616419</v>
+        <v>-4.736207235290681</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.887807193287953</v>
+        <v>1.938287750218248</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5223375542681012</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.759528038087826</v>
+        <v>-4.633326645762088</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.941810454977273</v>
+        <v>1.992291011907568</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6252181437966942</v>
@@ -48632,10 +48632,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.782970077267913</v>
+        <v>-4.656768684942175</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.952636309478832</v>
+        <v>2.003116866409127</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6252181437966942</v>
@@ -48655,10 +48655,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.801042585559524</v>
+        <v>-4.674841193233786</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.945407306162187</v>
+        <v>1.995887863092483</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6252181437966942</v>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.032216379436156</v>
+        <v>-4.906014987110418</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.813189702205001</v>
+        <v>1.863670259135296</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6252181437966942</v>
@@ -48701,10 +48701,10 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.000930358895701</v>
+        <v>-4.874728966569963</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.832726729418123</v>
+        <v>1.883207286348419</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6565041643371495</v>
@@ -48724,10 +48724,10 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.847904966782417</v>
+        <v>-4.721703574456678</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.993107885836341</v>
+        <v>2.043588442766636</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8095295564504337</v>
@@ -48747,10 +48747,10 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.876212280655687</v>
+        <v>-4.750010888329949</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.169251185195326</v>
+        <v>2.219731742125621</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8095295564504337</v>
@@ -48770,10 +48770,10 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.042805505769209</v>
+        <v>-4.916604113443471</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.072016846503999</v>
+        <v>2.122497403434294</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6429363313369112</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.798017350053306</v>
+        <v>3.777831910082019</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.869741126386909</v>
+        <v>-4.743539734061171</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.144919000918637</v>
+        <v>2.195399557848932</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6429363313369112</v>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>111.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-635.9%</t>
+          <t>-640.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-158.7%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-23.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2054"/>
+  <dimension ref="A1:G2055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130012</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.121385670672937</v>
+        <v>-4.158103147422342</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.120008052099879</v>
+        <v>1.105321061400117</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.083002008114786</v>
+        <v>-4.11971948486419</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.132780958465508</v>
+        <v>1.118093967765746</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.90588567807962</v>
+        <v>-3.942603154829024</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.200356519324876</v>
+        <v>1.185669528625114</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.950977922913165</v>
+        <v>-3.98769539966257</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.183003013153371</v>
+        <v>1.168316022453609</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.771602501674398</v>
+        <v>-3.808319978423802</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.248540156955292</v>
+        <v>1.23385316625553</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.816616715195004</v>
+        <v>-3.853334191944409</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.21134192687864</v>
+        <v>1.196654936178878</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.083621225467439</v>
+        <v>-4.120338702216844</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.110231685108611</v>
+        <v>1.095544694408849</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.184819006904612</v>
+        <v>-4.221536483654017</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.068956494430243</v>
+        <v>1.054269503730481</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.178308040290299</v>
+        <v>-4.215025517039704</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.069160842630285</v>
+        <v>1.054473851930523</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.159269912583002</v>
+        <v>-4.195987389332407</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.073300812921449</v>
+        <v>1.058613822221687</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.211785714857823</v>
+        <v>-4.248503191607227</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.171588893645711</v>
+        <v>1.156901902945949</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.22565247619174</v>
+        <v>-4.262369952941145</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.166875518098278</v>
+        <v>1.152188527398516</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.180848304651811</v>
+        <v>-4.217565781401215</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.190805717111175</v>
+        <v>1.176118726411414</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.033105334416808</v>
+        <v>-4.069822811166213</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.147853126482376</v>
+        <v>1.133166135782614</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.116926555691506</v>
+        <v>-4.153644032440911</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.117118259503978</v>
+        <v>1.102431268804216</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.110773849638722</v>
+        <v>-4.147491326388127</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.12024169031675</v>
+        <v>1.105554699616988</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.127583147789224</v>
+        <v>-4.164300624538629</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.112598447796659</v>
+        <v>1.097911457096897</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.065285149013102</v>
+        <v>-4.102002625762506</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.203853201103929</v>
+        <v>1.189166210404167</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.863494951347944</v>
+        <v>-3.900212428097348</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.086861281884119</v>
+        <v>1.072174291184357</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.914381664034138</v>
+        <v>-3.951099140783543</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.136796829131817</v>
+        <v>1.122109838432055</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.827770921384331</v>
+        <v>-3.864488398133736</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.186068862307783</v>
+        <v>1.171381871608021</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.887980219389616</v>
+        <v>-3.92469769613902</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.160521123930341</v>
+        <v>1.145834133230579</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.811558172957689</v>
+        <v>-3.848275649707094</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.18958156054304</v>
+        <v>1.174894569843278</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.76718504131912</v>
+        <v>-3.803902518068525</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.207193680633904</v>
+        <v>1.192506689934142</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.789665392178005</v>
+        <v>-3.82638286892741</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.192595334428941</v>
+        <v>1.177908343729179</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.742009661616949</v>
+        <v>-3.778727138366354</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.218039383681168</v>
+        <v>1.203352392981406</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.641491503118194</v>
+        <v>-3.678208979867599</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.263139020455394</v>
+        <v>1.248452029755632</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.625586173685842</v>
+        <v>-3.662303650435247</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.256255824704207</v>
+        <v>1.241568834004446</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.580747772077444</v>
+        <v>-3.617465248826849</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.278288887958195</v>
+        <v>1.263601897258433</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.600246228319452</v>
+        <v>-3.636963705068857</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.27465044509247</v>
+        <v>1.259963454392708</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.556043391233552</v>
+        <v>-3.592760867982956</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.298211182454667</v>
+        <v>1.283524191754905</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.563603057070599</v>
+        <v>-3.600320533820003</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.293597316589096</v>
+        <v>1.278910325889334</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.405311639531326</v>
+        <v>-3.442029116280731</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.408161648787845</v>
+        <v>1.393474658088083</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.19766963589685</v>
+        <v>-3.234387112646255</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.489659154835888</v>
+        <v>1.474972164136126</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.146637543174322</v>
+        <v>-3.183355019923727</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.505020220163169</v>
+        <v>1.490333229463408</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.081413362047116</v>
+        <v>-3.118130838796521</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.548297296706757</v>
+        <v>1.533610306006995</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.043986341975983</v>
+        <v>-3.080703818725387</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.559229077034491</v>
+        <v>1.544542086334729</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.064097998010691</v>
+        <v>-3.100815474760096</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.552441206951848</v>
+        <v>1.537754216252086</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.010353183583486</v>
+        <v>-3.047070660332891</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.73449690374394</v>
+        <v>1.719809913044178</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.935570922558473</v>
+        <v>-2.972288399307878</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.884522717371763</v>
+        <v>1.869835726672001</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.909486838294665</v>
+        <v>-2.94620431504407</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.886664327091145</v>
+        <v>1.871977336391383</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.821608925185545</v>
+        <v>-2.85832640193495</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.920008687918572</v>
+        <v>1.905321697218811</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.812716463792261</v>
+        <v>-2.849433940541666</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.941120078202677</v>
+        <v>1.926433087502915</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.981192580762139</v>
+        <v>-3.017910057511544</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.86558467881931</v>
+        <v>1.850897688119548</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.534936388132699</v>
+        <v>-2.571653864882104</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.025356853058948</v>
+        <v>2.010669862359186</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.512215284449547</v>
+        <v>-2.548932761198952</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.025109317029114</v>
+        <v>2.010422326329351</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.641417097743589</v>
+        <v>-2.678134574492994</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.132334717562665</v>
+        <v>2.117647726862903</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.796198104521845</v>
+        <v>-2.83291558127125</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.10750013734501</v>
+        <v>2.092813146645248</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.789143414306671</v>
+        <v>-2.825860891056076</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.106997369420625</v>
+        <v>2.092310378720862</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.762192189980183</v>
+        <v>-2.798909666729588</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.127784012795961</v>
+        <v>2.113097022096199</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.808661282460166</v>
+        <v>-2.858662284323076</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.293299507948928</v>
+        <v>2.273299107203764</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.831069400265038</v>
+        <v>-2.881070402127948</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.276452955729972</v>
+        <v>2.256452554984808</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.859293635842638</v>
+        <v>-2.909294637705548</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.267217261048569</v>
+        <v>2.247216860303405</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.868734561731168</v>
+        <v>-2.918735563594078</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.319694608415005</v>
+        <v>2.299694207669841</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.921008169066809</v>
+        <v>-2.97100917092972</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.301676260026049</v>
+        <v>2.281675859280885</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.997338146667715</v>
+        <v>-3.047339148530626</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.269256081879462</v>
+        <v>2.249255681134298</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.199591866992069</v>
+        <v>-3.249592868854979</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.183174823352583</v>
+        <v>2.163174422607419</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.361160292519324</v>
+        <v>-3.411161294382234</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.116981463351833</v>
+        <v>2.096981062606669</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.493461584616877</v>
+        <v>-3.543462586479787</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.07713435337873</v>
+        <v>2.057133952633566</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.679329895456107</v>
+        <v>-3.729330897319017</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.994792225825978</v>
+        <v>1.974791825080814</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.70723068256558</v>
+        <v>-3.75723168442849</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.982155952109191</v>
+        <v>1.962155551364027</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.829756785268474</v>
+        <v>-3.879757787131384</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.929909955005233</v>
+        <v>1.909909554260068</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.060271281454063</v>
+        <v>-4.110272283316973</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.9044101161215</v>
+        <v>1.884409715376337</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.316992099448887</v>
+        <v>-4.366993101311797</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.942033507925418</v>
+        <v>1.922033107180254</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.470978517225028</v>
+        <v>-4.520979519087938</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.949419209960602</v>
+        <v>1.929418809215437</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.420456613397362</v>
+        <v>-4.470457615260272</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.955679173611788</v>
+        <v>1.935678772866625</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.672931767405086</v>
+        <v>-4.722932769267996</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.866559601064113</v>
+        <v>1.846559200318949</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.965827523884498</v>
+        <v>-5.015828525747408</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.750611832991292</v>
+        <v>1.730611432246128</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.12337159561394</v>
+        <v>-5.17337259747685</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.691715946526836</v>
+        <v>1.671715545781673</v>
       </c>
       <c r="F2021" t="n">
         <v>0.23732834414886</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.401335991197214</v>
+        <v>-5.451336993060123</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.575608041029716</v>
+        <v>1.555607640284553</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1477086098633758</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.518303683836105</v>
+        <v>-5.568304685699014</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.691025020673204</v>
+        <v>1.67102461992804</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1477086098633758</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.603021626057058</v>
+        <v>-5.653022627919968</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.651984481748637</v>
+        <v>1.631984081003473</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06259258093532938</v>
@@ -48126,10 +48126,10 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.684956444325941</v>
+        <v>-5.734957446188851</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.629439972009575</v>
+        <v>1.609439571264411</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05265783534824919</v>
@@ -48149,10 +48149,10 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.786932566574349</v>
+        <v>-5.836933568437258</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.597575161566114</v>
+        <v>1.57757476082095</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04931828690015838</v>
@@ -48172,10 +48172,10 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.676926283097127</v>
+        <v>-5.726927284960037</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.633730562201178</v>
+        <v>1.613730161456014</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02611371498288317</v>
@@ -48195,10 +48195,10 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.533866707356202</v>
+        <v>-5.583867709219112</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.695204403219523</v>
+        <v>1.675204002474359</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.0181002883929039</v>
@@ -48218,10 +48218,10 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.232419981884364</v>
+        <v>-5.282420983747274</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.823043976290794</v>
+        <v>1.80304357554563</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2833464370789334</v>
@@ -48241,10 +48241,10 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.257010226119548</v>
+        <v>-5.307011227982458</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.814179056349431</v>
+        <v>1.794178655604267</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2833464370789334</v>
@@ -48264,10 +48264,10 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.205971850113028</v>
+        <v>-5.255972851975938</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.835437311131794</v>
+        <v>1.81543691038663</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2833464370789334</v>
@@ -48287,10 +48287,10 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.164832555246397</v>
+        <v>-5.214833557109307</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.870931127952592</v>
+        <v>1.850930727207428</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3244857319455642</v>
@@ -48310,10 +48310,10 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.054226415166795</v>
+        <v>-5.104227417029705</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.731357580108367</v>
+        <v>1.711357179363203</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4350918720251662</v>
@@ -48333,10 +48333,10 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.184807149697638</v>
+        <v>-5.234808151560547</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.682627330369994</v>
+        <v>1.66262692962483</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3045111374943237</v>
@@ -48356,10 +48356,10 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.020310815506676</v>
+        <v>-5.070311817369586</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.732852683122461</v>
+        <v>1.712852282377297</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3045111374943237</v>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.047680748191108</v>
+        <v>-5.097681750054018</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.721092420485118</v>
+        <v>1.701092019739954</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3045111374943237</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.058065943080997</v>
+        <v>-5.108066944943907</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.726807121654235</v>
+        <v>1.70680672090907</v>
       </c>
       <c r="F2037" t="n">
         <v>0.2941259426044344</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.076654101803222</v>
+        <v>-5.126655103666132</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.79020886394177</v>
+        <v>1.770208463196606</v>
       </c>
       <c r="F2038" t="n">
         <v>0.275537783882209</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.076952648499258</v>
+        <v>-5.126953650362168</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.786958456081654</v>
+        <v>1.76695805533649</v>
       </c>
       <c r="F2039" t="n">
         <v>0.275537783882209</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.97612951480883</v>
+        <v>-5.02613051667174</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.831818604497216</v>
+        <v>1.811818203752052</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2880019993665628</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.785348154056424</v>
+        <v>-4.835349155919333</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.908260402276722</v>
+        <v>1.888260001531558</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4787833601189702</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.766831300014603</v>
+        <v>-4.816832301877513</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.895503989631047</v>
+        <v>1.875503588885883</v>
       </c>
       <c r="F2042" t="n">
         <v>0.4917134895441784</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.741638115513285</v>
+        <v>-4.791639117376195</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.940548200043633</v>
+        <v>1.920547799298469</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5169066740454967</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.729583988600322</v>
+        <v>-4.779584990463232</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.939056418710256</v>
+        <v>1.919056017965092</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5289608009584595</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.736207235290681</v>
+        <v>-4.78620823715359</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.938287750218248</v>
+        <v>1.918287349473085</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5223375542681012</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.633326645762088</v>
+        <v>-4.683327647624997</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.992291011907568</v>
+        <v>1.972290611162404</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6252181437966942</v>
@@ -48632,10 +48632,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.656768684942175</v>
+        <v>-4.706769686805084</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.003116866409127</v>
+        <v>1.983116465663963</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6252181437966942</v>
@@ -48655,10 +48655,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.674841193233786</v>
+        <v>-4.724842195096696</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.995887863092483</v>
+        <v>1.975887462347319</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6252181437966942</v>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.906014987110418</v>
+        <v>-4.956015988973328</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.863670259135296</v>
+        <v>1.843669858390133</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6252181437966942</v>
@@ -48701,10 +48701,10 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.874728966569963</v>
+        <v>-4.924729968432873</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.883207286348419</v>
+        <v>1.863206885603255</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6565041643371495</v>
@@ -48724,10 +48724,10 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.721703574456678</v>
+        <v>-4.771704576319588</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.043588442766636</v>
+        <v>2.023588042021473</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8095295564504337</v>
@@ -48747,10 +48747,10 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.750010888329949</v>
+        <v>-4.800011890192859</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.219731742125621</v>
+        <v>2.199731341380457</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8095295564504337</v>
@@ -48770,10 +48770,10 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.916604113443471</v>
+        <v>-4.966605115306381</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.122497403434294</v>
+        <v>2.10249700268913</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6429363313369112</v>
@@ -48787,22 +48787,45 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.777831910082019</v>
+        <v>3.708202704568385</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.743539734061171</v>
+        <v>-4.793540735924081</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.195399557848932</v>
+        <v>2.175399157103768</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6429363313369112</v>
       </c>
       <c r="G2054" t="n">
         <v>4.478933674589294</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="2" t="n">
+        <v>45517</v>
+      </c>
+      <c r="B2055" t="n">
+        <v>3.777206261478955</v>
+      </c>
+      <c r="C2055" t="n">
+        <v>4.228007577565428</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>-4.793540735924081</v>
+      </c>
+      <c r="E2055" t="n">
+        <v>2.175399157103768</v>
+      </c>
+      <c r="F2055" t="n">
+        <v>0.6429363313369112</v>
+      </c>
+      <c r="G2055" t="n">
+        <v>4.221071374551796</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.9%</t>
+          <t>-635.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-156.7%</t>
         </is>
       </c>
     </row>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.158103147422342</v>
+        <v>-4.121385670672937</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.105321061400117</v>
+        <v>1.120008052099879</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.11971948486419</v>
+        <v>-4.083002008114786</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.118093967765746</v>
+        <v>1.132780958465508</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.942603154829024</v>
+        <v>-3.90588567807962</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.185669528625114</v>
+        <v>1.200356519324876</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.98769539966257</v>
+        <v>-3.950977922913165</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.168316022453609</v>
+        <v>1.183003013153371</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.808319978423802</v>
+        <v>-3.771602501674398</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.23385316625553</v>
+        <v>1.248540156955292</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.853334191944409</v>
+        <v>-3.816616715195004</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.196654936178878</v>
+        <v>1.21134192687864</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.120338702216844</v>
+        <v>-4.083621225467439</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.095544694408849</v>
+        <v>1.110231685108611</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.221536483654017</v>
+        <v>-4.184819006904612</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.054269503730481</v>
+        <v>1.068956494430243</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.215025517039704</v>
+        <v>-4.178308040290299</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.054473851930523</v>
+        <v>1.069160842630285</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.195987389332407</v>
+        <v>-4.159269912583002</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.058613822221687</v>
+        <v>1.073300812921449</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.248503191607227</v>
+        <v>-4.211785714857823</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.156901902945949</v>
+        <v>1.171588893645711</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.262369952941145</v>
+        <v>-4.22565247619174</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.152188527398516</v>
+        <v>1.166875518098278</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.217565781401215</v>
+        <v>-4.180848304651811</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.176118726411414</v>
+        <v>1.190805717111175</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.069822811166213</v>
+        <v>-4.033105334416808</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.133166135782614</v>
+        <v>1.147853126482376</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.153644032440911</v>
+        <v>-4.116926555691506</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.102431268804216</v>
+        <v>1.117118259503978</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.147491326388127</v>
+        <v>-4.110773849638722</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.105554699616988</v>
+        <v>1.12024169031675</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.164300624538629</v>
+        <v>-4.127583147789224</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.097911457096897</v>
+        <v>1.112598447796659</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.102002625762506</v>
+        <v>-4.065285149013102</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.189166210404167</v>
+        <v>1.203853201103929</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.900212428097348</v>
+        <v>-3.863494951347944</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.072174291184357</v>
+        <v>1.086861281884119</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.951099140783543</v>
+        <v>-3.914381664034138</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.122109838432055</v>
+        <v>1.136796829131817</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.864488398133736</v>
+        <v>-3.827770921384331</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.171381871608021</v>
+        <v>1.186068862307783</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.92469769613902</v>
+        <v>-3.887980219389616</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.145834133230579</v>
+        <v>1.160521123930341</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.848275649707094</v>
+        <v>-3.811558172957689</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.174894569843278</v>
+        <v>1.18958156054304</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.803902518068525</v>
+        <v>-3.76718504131912</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.192506689934142</v>
+        <v>1.207193680633904</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.82638286892741</v>
+        <v>-3.789665392178005</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.177908343729179</v>
+        <v>1.192595334428941</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.778727138366354</v>
+        <v>-3.742009661616949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.203352392981406</v>
+        <v>1.218039383681168</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.678208979867599</v>
+        <v>-3.641491503118194</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.248452029755632</v>
+        <v>1.263139020455394</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.662303650435247</v>
+        <v>-3.625586173685842</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.241568834004446</v>
+        <v>1.256255824704207</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.617465248826849</v>
+        <v>-3.580747772077444</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.263601897258433</v>
+        <v>1.278288887958195</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.636963705068857</v>
+        <v>-3.600246228319452</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.259963454392708</v>
+        <v>1.27465044509247</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.592760867982956</v>
+        <v>-3.556043391233552</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.283524191754905</v>
+        <v>1.298211182454667</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.600320533820003</v>
+        <v>-3.563603057070599</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.278910325889334</v>
+        <v>1.293597316589096</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.442029116280731</v>
+        <v>-3.405311639531326</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.393474658088083</v>
+        <v>1.408161648787845</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.234387112646255</v>
+        <v>-3.19766963589685</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.474972164136126</v>
+        <v>1.489659154835888</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.183355019923727</v>
+        <v>-3.146637543174322</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.490333229463408</v>
+        <v>1.505020220163169</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.118130838796521</v>
+        <v>-3.081413362047116</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.533610306006995</v>
+        <v>1.548297296706757</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.080703818725387</v>
+        <v>-3.043986341975983</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.544542086334729</v>
+        <v>1.559229077034491</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.100815474760096</v>
+        <v>-3.064097998010691</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.537754216252086</v>
+        <v>1.552441206951848</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.047070660332891</v>
+        <v>-3.010353183583486</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.719809913044178</v>
+        <v>1.73449690374394</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.972288399307878</v>
+        <v>-2.935570922558473</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.869835726672001</v>
+        <v>1.884522717371763</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.94620431504407</v>
+        <v>-2.909486838294665</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.871977336391383</v>
+        <v>1.886664327091145</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.85832640193495</v>
+        <v>-2.821608925185545</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.905321697218811</v>
+        <v>1.920008687918572</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.849433940541666</v>
+        <v>-2.812716463792261</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.926433087502915</v>
+        <v>1.941120078202677</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.017910057511544</v>
+        <v>-2.981192580762139</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.850897688119548</v>
+        <v>1.86558467881931</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.571653864882104</v>
+        <v>-2.534936388132699</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.010669862359186</v>
+        <v>2.025356853058948</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.548932761198952</v>
+        <v>-2.512215284449547</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.010422326329351</v>
+        <v>2.025109317029114</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.678134574492994</v>
+        <v>-2.641417097743589</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.117647726862903</v>
+        <v>2.132334717562665</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.83291558127125</v>
+        <v>-2.796198104521845</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.092813146645248</v>
+        <v>2.10750013734501</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.825860891056076</v>
+        <v>-2.789143414306671</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.092310378720862</v>
+        <v>2.106997369420625</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.798909666729588</v>
+        <v>-2.762192189980183</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.113097022096199</v>
+        <v>2.127784012795961</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.858662284323076</v>
+        <v>-2.808661282460166</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.273299107203764</v>
+        <v>2.293299507948928</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.881070402127948</v>
+        <v>-2.831069400265038</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.256452554984808</v>
+        <v>2.276452955729972</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.909294637705548</v>
+        <v>-2.859293635842638</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.247216860303405</v>
+        <v>2.267217261048569</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.918735563594078</v>
+        <v>-2.868734561731168</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.299694207669841</v>
+        <v>2.319694608415005</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.97100917092972</v>
+        <v>-2.921008169066809</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.281675859280885</v>
+        <v>2.301676260026049</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.047339148530626</v>
+        <v>-2.997338146667715</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.249255681134298</v>
+        <v>2.269256081879462</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.249592868854979</v>
+        <v>-3.199591866992069</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.163174422607419</v>
+        <v>2.183174823352583</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.411161294382234</v>
+        <v>-3.361160292519324</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.096981062606669</v>
+        <v>2.116981463351833</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.543462586479787</v>
+        <v>-3.493461584616877</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.057133952633566</v>
+        <v>2.07713435337873</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.729330897319017</v>
+        <v>-3.679329895456107</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.974791825080814</v>
+        <v>1.994792225825978</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.75723168442849</v>
+        <v>-3.70723068256558</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.962155551364027</v>
+        <v>1.982155952109191</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.879757787131384</v>
+        <v>-3.829756785268474</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.909909554260068</v>
+        <v>1.929909955005233</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.110272283316973</v>
+        <v>-4.060271281454063</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.884409715376337</v>
+        <v>1.9044101161215</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.366993101311797</v>
+        <v>-4.316992099448887</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.922033107180254</v>
+        <v>1.942033507925418</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.520979519087938</v>
+        <v>-4.470978517225028</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.929418809215437</v>
+        <v>1.949419209960602</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.470457615260272</v>
+        <v>-4.420456613397362</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.935678772866625</v>
+        <v>1.955679173611788</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.722932769267996</v>
+        <v>-4.672931767405086</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.846559200318949</v>
+        <v>1.866559601064113</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.015828525747408</v>
+        <v>-4.965827523884498</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.730611432246128</v>
+        <v>1.750611832991292</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.17337259747685</v>
+        <v>-5.12337159561394</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.671715545781673</v>
+        <v>1.691715946526836</v>
       </c>
       <c r="F2021" t="n">
         <v>0.23732834414886</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.451336993060123</v>
+        <v>-5.401335991197214</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.555607640284553</v>
+        <v>1.575608041029716</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1477086098633758</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.568304685699014</v>
+        <v>-5.518303683836105</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.67102461992804</v>
+        <v>1.691025020673204</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1477086098633758</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.653022627919968</v>
+        <v>-5.603021626057058</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.631984081003473</v>
+        <v>1.651984481748637</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06259258093532938</v>
@@ -48126,10 +48126,10 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.734957446188851</v>
+        <v>-5.684956444325941</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.609439571264411</v>
+        <v>1.629439972009575</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05265783534824919</v>
@@ -48149,10 +48149,10 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.836933568437258</v>
+        <v>-5.786932566574349</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.57757476082095</v>
+        <v>1.597575161566114</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04931828690015838</v>
@@ -48172,10 +48172,10 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.726927284960037</v>
+        <v>-5.676926283097127</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.613730161456014</v>
+        <v>1.633730562201178</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02611371498288317</v>
@@ -48195,10 +48195,10 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.583867709219112</v>
+        <v>-5.533866707356202</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.675204002474359</v>
+        <v>1.695204403219523</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.0181002883929039</v>
@@ -48218,10 +48218,10 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.282420983747274</v>
+        <v>-5.232419981884364</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.80304357554563</v>
+        <v>1.823043976290794</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2833464370789334</v>
@@ -48241,10 +48241,10 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.307011227982458</v>
+        <v>-5.257010226119548</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.794178655604267</v>
+        <v>1.814179056349431</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2833464370789334</v>
@@ -48264,10 +48264,10 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.255972851975938</v>
+        <v>-5.205971850113028</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.81543691038663</v>
+        <v>1.835437311131794</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2833464370789334</v>
@@ -48287,10 +48287,10 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.214833557109307</v>
+        <v>-5.164832555246397</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.850930727207428</v>
+        <v>1.870931127952592</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3244857319455642</v>
@@ -48310,10 +48310,10 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.104227417029705</v>
+        <v>-5.054226415166795</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.711357179363203</v>
+        <v>1.731357580108367</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4350918720251662</v>
@@ -48333,10 +48333,10 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.234808151560547</v>
+        <v>-5.184807149697638</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.66262692962483</v>
+        <v>1.682627330369994</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3045111374943237</v>
@@ -48356,10 +48356,10 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.070311817369586</v>
+        <v>-5.020310815506676</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.712852282377297</v>
+        <v>1.732852683122461</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3045111374943237</v>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.097681750054018</v>
+        <v>-5.047680748191108</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.701092019739954</v>
+        <v>1.721092420485118</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3045111374943237</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.108066944943907</v>
+        <v>-5.058065943080997</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.70680672090907</v>
+        <v>1.726807121654235</v>
       </c>
       <c r="F2037" t="n">
         <v>0.2941259426044344</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.126655103666132</v>
+        <v>-5.076654101803222</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.770208463196606</v>
+        <v>1.79020886394177</v>
       </c>
       <c r="F2038" t="n">
         <v>0.275537783882209</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.126953650362168</v>
+        <v>-5.076952648499258</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.76695805533649</v>
+        <v>1.786958456081654</v>
       </c>
       <c r="F2039" t="n">
         <v>0.275537783882209</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.02613051667174</v>
+        <v>-4.97612951480883</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.811818203752052</v>
+        <v>1.831818604497216</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2880019993665628</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.835349155919333</v>
+        <v>-4.785348154056424</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.888260001531558</v>
+        <v>1.908260402276722</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4787833601189702</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.816832301877513</v>
+        <v>-4.766831300014603</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.875503588885883</v>
+        <v>1.895503989631047</v>
       </c>
       <c r="F2042" t="n">
         <v>0.4917134895441784</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.791639117376195</v>
+        <v>-4.741638115513285</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.920547799298469</v>
+        <v>1.940548200043633</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5169066740454967</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.779584990463232</v>
+        <v>-4.729583988600322</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.919056017965092</v>
+        <v>1.939056418710256</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5289608009584595</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.78620823715359</v>
+        <v>-4.736207235290681</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.918287349473085</v>
+        <v>1.938287750218248</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5223375542681012</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.683327647624997</v>
+        <v>-4.633326645762088</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.972290611162404</v>
+        <v>1.992291011907568</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6252181437966942</v>
@@ -48632,10 +48632,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.706769686805084</v>
+        <v>-4.656768684942175</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.983116465663963</v>
+        <v>2.003116866409127</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6252181437966942</v>
@@ -48655,10 +48655,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.724842195096696</v>
+        <v>-4.674841193233786</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.975887462347319</v>
+        <v>1.995887863092483</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6252181437966942</v>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.956015988973328</v>
+        <v>-4.906014987110418</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.843669858390133</v>
+        <v>1.863670259135296</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6252181437966942</v>
@@ -48701,10 +48701,10 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.924729968432873</v>
+        <v>-4.874728966569963</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.863206885603255</v>
+        <v>1.883207286348419</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6565041643371495</v>
@@ -48724,10 +48724,10 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.771704576319588</v>
+        <v>-4.721703574456678</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.023588042021473</v>
+        <v>2.043588442766636</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8095295564504337</v>
@@ -48747,10 +48747,10 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.800011890192859</v>
+        <v>-4.750010888329949</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.199731341380457</v>
+        <v>2.219731742125621</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8095295564504337</v>
@@ -48770,10 +48770,10 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.966605115306381</v>
+        <v>-4.916604113443471</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.10249700268913</v>
+        <v>2.122497403434294</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6429363313369112</v>
@@ -48793,10 +48793,10 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.793540735924081</v>
+        <v>-4.743539734061171</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.175399157103768</v>
+        <v>2.195399557848932</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6429363313369112</v>
@@ -48816,10 +48816,10 @@
         <v>4.228007577565428</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.793540735924081</v>
+        <v>-4.743539734061171</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.175399157103768</v>
+        <v>2.195399557848932</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6429363313369112</v>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,22 +859,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.6%</t>
+          <t>427.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-635.9%</t>
+          <t>-656.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-165.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-304.4%</t>
+          <t>-373.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.7%</t>
+          <t>-174.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-54.4%</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.791730173643971</v>
+        <v>-4.803496784729577</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.060396852561846</v>
+        <v>1.055690208127603</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.4633550555806165</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.255458379681552</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.680303414318051</v>
+        <v>-4.692070025403657</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.08616181507601</v>
+        <v>1.081455170641767</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.4633550555806165</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.236652638465348</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.69080603738334</v>
+        <v>-4.702572648468946</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.083703842474771</v>
+        <v>1.078997198040529</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4528524325153276</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.232094141251051</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.618563469212146</v>
+        <v>-4.630330080297751</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.116530183578069</v>
+        <v>1.111823539143827</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4528524325153276</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.236023455085872</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.60084978233428</v>
+        <v>-4.612616393419886</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.124294242246555</v>
+        <v>1.119587597812313</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4560337614122444</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.238610836341361</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.492044896854553</v>
+        <v>-4.503811507940159</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.16481426765844</v>
+        <v>1.160107623224197</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4560337614122444</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.235608907561355</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.272024098817543</v>
+        <v>-4.283790709903148</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.254401623883858</v>
+        <v>1.249694979449616</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.5972536064802246</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.321919851612757</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.139156409754265</v>
+        <v>-4.150923020839871</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.323442882310992</v>
+        <v>1.31873623787675</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.5972536064802246</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.337814034414581</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.018983326389766</v>
+        <v>-4.030749937475372</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.372657960097094</v>
+        <v>1.367951315662852</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.7174266898447236</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.411063728873582</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.883729965059789</v>
+        <v>-3.895496576145395</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.436847407190525</v>
+        <v>1.432140762756282</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.8526800511747007</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.502303848233008</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.943604792417482</v>
+        <v>-3.955371403503087</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.398934967648873</v>
+        <v>1.394228323214631</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7928052238170086</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.452416443219819</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.823784561506644</v>
+        <v>-3.83555117259225</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.462152229247417</v>
+        <v>1.457445584813175</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7928052238170086</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.467705612454027</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.82625426796845</v>
+        <v>-3.838020879054056</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.368808545985136</v>
+        <v>1.364101901550894</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.7903355173552025</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.373867987899385</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.89462445429246</v>
+        <v>-3.906391065378066</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.260722332940833</v>
+        <v>1.256015688506591</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7996112163914174</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.298695268806416</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.908412507139507</v>
+        <v>-3.920179118225112</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.245643820433906</v>
+        <v>1.240937175999664</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7996112163914174</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.289131977438307</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.963932583032096</v>
+        <v>-3.975699194117702</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.360466626769073</v>
+        <v>1.35575998233483</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7996112163914174</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.426162814130509</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.788458323239627</v>
+        <v>-3.800224934325233</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.435223562677848</v>
+        <v>1.430516918243606</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7996112163914174</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.430730046122297</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.899394575880875</v>
+        <v>-3.911161186966481</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.366591090382556</v>
+        <v>1.361884445948313</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7996112163914174</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.406472074883504</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.865731030408594</v>
+        <v>-3.8774976414942</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.308594821972918</v>
+        <v>1.303888177538676</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8332747618636993</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.362268482219687</v>
+        <v>3.355208515568323</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.80587841120487</v>
+        <v>-3.817645022290476</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.34270825608654</v>
+        <v>1.338001611652298</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8332747618636993</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.372440868651819</v>
+        <v>3.365380902000455</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.719634948178493</v>
+        <v>-3.731401559264099</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.372151911870951</v>
+        <v>1.367445267436709</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8332747618636993</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.367387139225679</v>
+        <v>3.360327172574316</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.764941767577473</v>
+        <v>-3.776708378663079</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.345804959555885</v>
+        <v>1.341098315121642</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.7924645988544685</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.334676816864667</v>
+        <v>3.327616850213303</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.793974872279775</v>
+        <v>-3.80574148336538</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.334743590708066</v>
+        <v>1.330036946273824</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.7924645988544685</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.335228689897768</v>
+        <v>3.328168723246404</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.701164390828915</v>
+        <v>-3.712931001914521</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.301140475179775</v>
+        <v>1.296433830745533</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8970416913909339</v>
+        <v>0.8852750803053279</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.320187670659649</v>
+        <v>3.313127704008286</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.745553860158343</v>
+        <v>-3.757320471243949</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.285258163372605</v>
+        <v>1.280551518938362</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8526522220615063</v>
+        <v>0.8408856109759002</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.295427464986593</v>
+        <v>3.28836749833523</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862095465263686</v>
+        <v>-3.873862076349292</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.233717229842191</v>
+        <v>1.229010585407948</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.7243440058705575</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220578210435111</v>
+        <v>3.213518243783747</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.902019559846257</v>
+        <v>-3.913786170931863</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.223238887839829</v>
+        <v>1.218532243405587</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.7243440058705575</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.226069506265778</v>
+        <v>3.219009539614414</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.929799957747611</v>
+        <v>-3.941566568833216</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223623930447827</v>
+        <v>1.218917286013585</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7083302190548104</v>
+        <v>0.6965636079692044</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220898469293505</v>
+        <v>3.213838502642142</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.048180630477749</v>
+        <v>-4.059947241563354</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.014627381356425</v>
+        <v>1.009920736922183</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6293457558182282</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018923478003573</v>
+        <v>3.011863511352209</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.15679470892108</v>
+        <v>-4.168561320006686</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.091331410698298</v>
+        <v>1.086624766264056</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6293457558182282</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.139073138722778</v>
+        <v>3.132013172071415</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.121385670672937</v>
+        <v>-4.133152281758543</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.120008052099879</v>
+        <v>1.115301407665636</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6293457558182282</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153586164825101</v>
+        <v>3.146526198173738</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.083002008114786</v>
+        <v>-4.094768619200392</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.132780958465508</v>
+        <v>1.128074314031265</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.6677294183763793</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.174035803702361</v>
+        <v>3.166975837050997</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.90588567807962</v>
+        <v>-3.917652289165225</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.200356519324876</v>
+        <v>1.195649874890634</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.6677294183763793</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170764832547663</v>
+        <v>3.163704865896299</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.950977922913165</v>
+        <v>-3.962744533998771</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.183003013153371</v>
+        <v>1.178296368719129</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6175999862925956</v>
+        <v>0.6058333752069895</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134310598407942</v>
+        <v>3.127250631756578</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.771602501674398</v>
+        <v>-3.783369112760004</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.248540156955292</v>
+        <v>1.24383351252105</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7743767444633143</v>
+        <v>0.7626101333777082</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.222163628616787</v>
+        <v>3.215103661965424</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.816616715195004</v>
+        <v>-3.82838332628061</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.21134192687864</v>
+        <v>1.206635282444397</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7440278491487097</v>
+        <v>0.7322612380631036</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.184761746759615</v>
+        <v>3.177701780108251</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.083621225467439</v>
+        <v>-4.095387836553045</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.110231685108611</v>
+        <v>1.105525040674369</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5496648111057612</v>
+        <v>0.5378982000201551</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073835486272791</v>
+        <v>3.066775519621427</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.184819006904612</v>
+        <v>-4.196585617990218</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.068956494430243</v>
+        <v>1.064249849996001</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.481255997560442</v>
+        <v>0.4694893864748359</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031994120042101</v>
+        <v>3.024934153390737</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.178308040290299</v>
+        <v>-4.190074651375905</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.069160842630285</v>
+        <v>1.064454198196043</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.481255997560442</v>
+        <v>0.4694893864748359</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029594081596418</v>
+        <v>3.022534114945054</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.159269912583002</v>
+        <v>-4.171036523668608</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.073300812921449</v>
+        <v>1.068594168487207</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.4113057751436414</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.991208634005946</v>
+        <v>2.984148667354583</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.211785714857823</v>
+        <v>-4.223552325943428</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.171588893645711</v>
+        <v>1.166882249211469</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.4113057751436414</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.110503035640136</v>
+        <v>3.103443068988772</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.22565247619174</v>
+        <v>-4.237419087277346</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.166875518098278</v>
+        <v>1.162168873664035</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.3734478584098184</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088621614585976</v>
+        <v>3.081561647934612</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.180848304651811</v>
+        <v>-4.192614915737416</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.190805717111175</v>
+        <v>1.186099072676933</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.3734478584098184</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094630144982902</v>
+        <v>3.087570178331538</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.033105334416808</v>
+        <v>-4.224643559255988</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.147853126482376</v>
+        <v>1.071237836546704</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.4045857911514822</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.093264780601031</v>
+        <v>3.004203159253736</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.116926555691506</v>
+        <v>-4.308464780530686</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.117118259503978</v>
+        <v>1.040502969568306</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.4045857911514822</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.006996780785217</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.110773849638722</v>
+        <v>-4.302312074477902</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.12024169031675</v>
+        <v>1.043626400381078</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5591745327830919</v>
+        <v>0.4107384972042665</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.011350752808546</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.127583147789224</v>
+        <v>-4.319121372628404</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.112598447796659</v>
+        <v>1.035983157860987</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5423652346325902</v>
+        <v>0.3939291990537648</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.000345650658355</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.065285149013102</v>
+        <v>-4.256823373852281</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.203853201103929</v>
+        <v>1.127237911168257</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5876594989070323</v>
+        <v>0.4392234633282069</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.093857763019841</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.863494951347944</v>
+        <v>-4.055033176187123</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.086861281884119</v>
+        <v>1.010245991948447</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7856776910761867</v>
+        <v>0.6372416554973612</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.014960680035461</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.914381664034138</v>
+        <v>-4.105919888873318</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.136796829131817</v>
+        <v>1.060181539196145</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7347909783899922</v>
+        <v>0.5863549428111667</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.054718884745919</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.827770921384331</v>
+        <v>-4.019309146223511</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.186068862307783</v>
+        <v>1.109453572372111</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8134167095951504</v>
+        <v>0.664980674016325</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.116522059585058</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.887980219389616</v>
+        <v>-4.079518444228796</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.160521123930341</v>
+        <v>1.083905833994669</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.6047713760110405</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.078932461606559</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.811558172957689</v>
+        <v>-4.003096397796869</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.18958156054304</v>
+        <v>1.112966270607368</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.6047713760110405</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.077424079646488</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.76718504131912</v>
+        <v>-3.958723266158301</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.207193680633904</v>
+        <v>1.130578390698232</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.6491445076496091</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.103910826065065</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.789665392178005</v>
+        <v>-3.981203617017186</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.192595334428941</v>
+        <v>1.115980044493268</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.6491445076496091</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.098304620203656</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.742009661616949</v>
+        <v>-3.93354788645613</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.218039383681168</v>
+        <v>1.141424093745495</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8452362737894902</v>
+        <v>0.6968002382106647</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.133279815568093</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.641491503118194</v>
+        <v>-3.833029727957375</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.263139020455394</v>
+        <v>1.186523730519722</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9457544322882447</v>
+        <v>0.7973183967094193</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.198483084042071</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.625586173685842</v>
+        <v>-3.817124398525022</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.256255824704207</v>
+        <v>1.179640534768535</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8666417715790058</v>
+        <v>0.7182057360001803</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.1377701600924</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.580747772077444</v>
+        <v>-3.772285996916624</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.278288887958195</v>
+        <v>1.201673598022523</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8711852045238753</v>
+        <v>0.7227491689450498</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.14459392246995</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.600246228319452</v>
+        <v>-3.791784453158633</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.27465044509247</v>
+        <v>1.198035155156798</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.823100563243971</v>
+        <v>0.6746645276651455</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.119904077333086</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.556043391233552</v>
+        <v>-3.747581616072732</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.298211182454667</v>
+        <v>1.221595892518995</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8673034003298714</v>
+        <v>0.718867364751046</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.152305382112463</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.563603057070599</v>
+        <v>-3.755141281909779</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.293597316589096</v>
+        <v>1.216982026653424</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.7736707687608653</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.183597424987602</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.405311639531326</v>
+        <v>-3.596849864370507</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.408161648787845</v>
+        <v>1.331546358852172</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.7736707687608653</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.234845190170642</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.19766963589685</v>
+        <v>-3.389207860736031</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.489659154835888</v>
+        <v>1.413043864900216</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.129748807974167</v>
+        <v>0.9813127723953414</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.357871096945581</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.146637543174322</v>
+        <v>-3.338175768013503</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.505020220163169</v>
+        <v>1.428404930227497</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.180780900696695</v>
+        <v>1.032344865117869</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.383438580817367</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.081413362047116</v>
+        <v>-3.272951586886297</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.548297296706757</v>
+        <v>1.471682006771085</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.246005081823901</v>
+        <v>1.097569046245075</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.439760493586396</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.043986341975983</v>
+        <v>-3.235524566815163</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.559229077034491</v>
+        <v>1.482613787098818</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.251256619853082</v>
+        <v>1.102820584274257</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.438872388703185</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.064097998010691</v>
+        <v>-3.255636222849871</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.552441206951848</v>
+        <v>1.475825917016175</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.262283964850502</v>
+        <v>1.113847929271676</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.446745588032877</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.010353183583486</v>
+        <v>-3.201891408422667</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.73449690374394</v>
+        <v>1.657881613808268</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.272347274290964</v>
+        <v>1.123911238712138</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.613341344718365</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.935570922558473</v>
+        <v>-3.127109147397654</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.884522717371763</v>
+        <v>1.80790742743609</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.347129535315976</v>
+        <v>1.198693499737151</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.77832361055119</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.909486838294665</v>
+        <v>-3.101025063133846</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.886664327091145</v>
+        <v>1.810049037155472</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.347129535315976</v>
+        <v>1.198693499737151</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.770031586565049</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.821608925185545</v>
+        <v>-3.013147150024726</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.920008687918572</v>
+        <v>1.8433933979829</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.463055177739327</v>
+        <v>1.314619142160502</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.837780167602839</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.812716463792261</v>
+        <v>-3.004254688631442</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.941120078202677</v>
+        <v>1.864504788267005</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.463055177739327</v>
+        <v>1.314619142160502</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.85533457332963</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.981192580762139</v>
+        <v>-3.17273080560132</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.86558467881931</v>
+        <v>1.788969388883638</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.435107342022747</v>
+        <v>1.286671306443921</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.830420919304266</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.534936388132699</v>
+        <v>-2.72647461297188</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.025356853058948</v>
+        <v>1.948741563123276</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.340388672353114</v>
+        <v>1.191952636774289</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.754859414690348</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.512215284449547</v>
+        <v>-2.703753509288727</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.025109317029114</v>
+        <v>1.948494027093441</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.340388672353114</v>
+        <v>1.191952636774289</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.745523437187253</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.641417097743589</v>
+        <v>-2.83295532258277</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.132334717562665</v>
+        <v>2.055719427626993</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.211186859059072</v>
+        <v>1.062750823480246</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.826908475061996</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.796198104521845</v>
+        <v>-2.987736329361026</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.10750013734501</v>
+        <v>2.030884847409338</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177819185004596</v>
+        <v>1.02938314942577</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.843965693122957</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.789143414306671</v>
+        <v>-2.980681639145852</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.106997369420625</v>
+        <v>2.030382079484952</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184873875219769</v>
+        <v>1.036437839640944</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.844873863241607</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.762192189980183</v>
+        <v>-2.953730414819364</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.127784012795961</v>
+        <v>2.051168722860289</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199754221247489</v>
+        <v>1.051318185668663</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.86380822450298</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.808661282460166</v>
+        <v>-3.08968342287568</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.293299507948928</v>
+        <v>2.180890651782722</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199754221247489</v>
+        <v>1.051318185668663</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.04791135664794</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.831069400265038</v>
+        <v>-3.112091540680552</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.276452955729972</v>
+        <v>2.164044099563767</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199754221247489</v>
+        <v>1.051318185668663</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.040028051550933</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.859293635842638</v>
+        <v>-3.140315776258153</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.267217261048569</v>
+        <v>2.154808404882364</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217730973698797</v>
+        <v>1.069294938119972</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.052868102571355</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.868734561731168</v>
+        <v>-3.149756702146683</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.319694608415005</v>
+        <v>2.207285752248799</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340158091242189</v>
+        <v>1.191722055663363</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.182578090819237</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.921008169066809</v>
+        <v>-3.202030309482324</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.301676260026049</v>
+        <v>2.189267403859843</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.287884483906547</v>
+        <v>1.139448448327722</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.154105020963153</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.997338146667715</v>
+        <v>-3.27836028708323</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.269256081879462</v>
+        <v>2.156847225713256</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.287884483906547</v>
+        <v>1.139448448327722</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.152216833856929</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.199591866992069</v>
+        <v>-3.480614007407583</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.183174823352583</v>
+        <v>2.070765967186377</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.085630763582194</v>
+        <v>0.9371947280033683</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.025684831265179</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.361160292519324</v>
+        <v>-3.642182432934838</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.116981463351833</v>
+        <v>2.004572607185627</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.810411804205489</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>3.948049087196603</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.493461584616877</v>
+        <v>-3.774483725032391</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.07713435337873</v>
+        <v>1.964725497212525</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.810411804205489</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>3.961122494062522</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.679329895456107</v>
+        <v>-3.960352035871622</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.994792225825978</v>
+        <v>1.882383369659772</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8002822464643667</v>
+        <v>0.6518462108855413</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.857988334853494</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.70723068256558</v>
+        <v>-3.988252822981095</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.982155952109191</v>
+        <v>1.869747095942985</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7656853223214319</v>
+        <v>0.6172492867426065</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.835754221494735</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.829756785268474</v>
+        <v>-4.110778925683988</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.929909955005233</v>
+        <v>1.817501098839027</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6431592196185381</v>
+        <v>0.4947231840397126</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.759003003850197</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.060271281454063</v>
+        <v>-4.341293421869577</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.9044101161215</v>
+        <v>1.792001259955295</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4126447234329493</v>
+        <v>0.2642086878541239</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.687400265729348</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.316992099448887</v>
+        <v>-4.598014239864401</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.942033507925418</v>
+        <v>1.829624651759212</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.155794113710309</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.762663240244906</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.470978517225028</v>
+        <v>-4.752000657640542</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.949419209960602</v>
+        <v>1.837010353794396</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.155794113710309</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.831643509390545</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.420456613397362</v>
+        <v>-4.701478753812876</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.955679173611788</v>
+        <v>1.843270317445583</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.155794113710309</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.817694711510666</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.672931767405086</v>
+        <v>-4.87997522816077</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.866559601064113</v>
+        <v>1.783742216761839</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.155794113710309</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.82956520056608</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.965827523884498</v>
+        <v>-5.172870984640182</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.750611832991292</v>
+        <v>1.667794448689018</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.155794113710309</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.830775735085024</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.12337159561394</v>
+        <v>-5.330415056369624</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.691715946526836</v>
+        <v>1.608898562224563</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.23732834414886</v>
+        <v>0.08889230857003455</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.883818015575476</v>
+        <v>3.794756394228181</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.401335991197214</v>
+        <v>-5.608379451952898</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.575608041029716</v>
+        <v>1.492790656727443</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1477086098633758</v>
+        <v>-0.0007274257154497032</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.825124027740375</v>
+        <v>3.73606240639308</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.518303683836105</v>
+        <v>-5.725347144591789</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.691025020673204</v>
+        <v>1.608207636370931</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1477086098633758</v>
+        <v>-0.0007274257154497032</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.987328084439419</v>
+        <v>3.898266463092124</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.603021626057058</v>
+        <v>-5.810065086812742</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.651984481748637</v>
+        <v>1.569167097446364</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.06259258093532938</v>
+        <v>-0.08584345464349608</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.931105105046405</v>
+        <v>3.84204348369911</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.684956444325941</v>
+        <v>-5.891999905081625</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.629439972009575</v>
+        <v>1.546622587707301</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.05265783534824919</v>
+        <v>-0.09577820023057626</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.935373675262649</v>
+        <v>3.846312053915353</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.786932566574349</v>
+        <v>-5.993976027330032</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.597575161566114</v>
+        <v>1.514757777263841</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.04931828690015838</v>
+        <v>-0.1977543224789838</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.883113640369506</v>
+        <v>3.794052019022211</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.676926283097127</v>
+        <v>-5.883969743852811</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.633730562201178</v>
+        <v>1.550913177898905</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02611371498288317</v>
+        <v>-0.1745497505617086</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.889189270764047</v>
+        <v>3.800127649416751</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.533866707356202</v>
+        <v>-5.740910168111885</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.695204403219523</v>
+        <v>1.61238701891725</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.0181002883929039</v>
+        <v>-0.1665363239717293</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.898247337440008</v>
+        <v>3.809185716092713</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.232419981884364</v>
+        <v>-5.439463442640047</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.823043976290794</v>
+        <v>1.740226591988521</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.1349104015001079</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.086376255605647</v>
+        <v>3.997314634258352</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.257010226119548</v>
+        <v>-5.464053686875231</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.814179056349431</v>
+        <v>1.731361672047158</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.1349104015001079</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.087347433358357</v>
+        <v>3.998285812011062</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.205971850113028</v>
+        <v>-5.413015310868711</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.835437311131794</v>
+        <v>1.752619926829521</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.1349104015001079</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.088190337738113</v>
+        <v>3.999128716390818</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.164832555246397</v>
+        <v>-5.37187601600208</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.870931127952592</v>
+        <v>1.788113743650319</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3244857319455642</v>
+        <v>0.1760496963667387</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.131912013532236</v>
+        <v>4.042850392184941</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.054226415166795</v>
+        <v>-5.261269875922478</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.731357580108367</v>
+        <v>1.648540195806094</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4350918720251662</v>
+        <v>0.2866558364463407</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.014459693703932</v>
+        <v>3.925398072356638</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.184807149697638</v>
+        <v>-5.391850610453321</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.682627330369994</v>
+        <v>1.599809946067721</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.1560751019154982</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.939613297059391</v>
+        <v>3.850551675712095</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.020310815506676</v>
+        <v>-5.227354276262359</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.732852683122461</v>
+        <v>1.650035298820188</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.1560751019154982</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.924040116135473</v>
+        <v>3.834978494788178</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.047680748191108</v>
+        <v>-5.254724208946791</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.721092420485118</v>
+        <v>1.638275036182845</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.1560751019154982</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.923227826571903</v>
+        <v>3.834166205224608</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.058065943080997</v>
+        <v>-5.26510940383668</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.726807121654235</v>
+        <v>1.643989737351961</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2941259426044344</v>
+        <v>0.1456899070256089</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.926865488763042</v>
+        <v>3.837803867415746</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.076654101803222</v>
+        <v>-5.283697562558905</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.79020886394177</v>
+        <v>1.707391479639496</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.275537783882209</v>
+        <v>0.1271017483033836</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.986549599306132</v>
+        <v>3.897487977958837</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.076952648499258</v>
+        <v>-5.283996109254941</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.786958456081654</v>
+        <v>1.704141071779381</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.275537783882209</v>
+        <v>0.1271017483033836</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.98341861012443</v>
+        <v>3.894356988777135</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.97612951480883</v>
+        <v>-5.183172975564514</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.831818604497216</v>
+        <v>1.749001220194943</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2880019993665628</v>
+        <v>0.1395659637877374</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.995428034354433</v>
+        <v>3.906366413007138</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.785348154056424</v>
+        <v>-4.992391614812107</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.908260402276722</v>
+        <v>1.825443017974449</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4787833601189702</v>
+        <v>0.3303473245401448</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.110026104284421</v>
+        <v>4.020964482937126</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.766831300014603</v>
+        <v>-4.973874760770286</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.895503989631047</v>
+        <v>1.812686605328774</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4917134895441784</v>
+        <v>0.343277453965353</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.097621027677143</v>
+        <v>4.008559406329848</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.741638115513285</v>
+        <v>-4.948681576268968</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.940548200043633</v>
+        <v>1.857730815741359</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5169066740454967</v>
+        <v>0.3684706384666713</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.147703874989992</v>
+        <v>4.058642253642697</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.729583988600322</v>
+        <v>-4.936627449356005</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.939056418710256</v>
+        <v>1.856239034407982</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5289608009584595</v>
+        <v>0.3805247653796341</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.148622919039208</v>
+        <v>4.059561297691912</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.736207235290681</v>
+        <v>-4.943250696046364</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.938287750218248</v>
+        <v>1.855470365915975</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5223375542681012</v>
+        <v>0.3739015186892758</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.146529601209129</v>
+        <v>4.057467979861833</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.633326645762088</v>
+        <v>-4.840370106517771</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.992291011907568</v>
+        <v>1.909473627605295</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.4767821082178687</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.221108980804167</v>
+        <v>4.132047359456871</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.656768684942175</v>
+        <v>-4.863812145697858</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.003116866409127</v>
+        <v>1.920299482106854</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.4767821082178687</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.241311650977761</v>
+        <v>4.152250029630466</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.674841193233786</v>
+        <v>-4.881884653989469</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.995887863092483</v>
+        <v>1.91307047879021</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.4767821082178687</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.241311650977761</v>
+        <v>4.152250029630466</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.906014987110418</v>
+        <v>-5.113058447866101</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.863670259135296</v>
+        <v>1.780852874833023</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.4767821082178687</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.201563564571228</v>
+        <v>4.112501943223933</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.874728966569963</v>
+        <v>-5.081772427325646</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.883207286348419</v>
+        <v>1.800389902046145</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6565041643371495</v>
+        <v>0.5080681287583241</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.227357795892441</v>
+        <v>4.138296174545146</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.721703574456678</v>
+        <v>-4.928747035212361</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.043588442766636</v>
+        <v>1.960771058464363</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8095295564504337</v>
+        <v>0.6610935208716082</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.418344030733316</v>
+        <v>4.32928240938602</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.750010888329949</v>
+        <v>-4.957054349085632</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.219731742125621</v>
+        <v>2.136914357823348</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8095295564504337</v>
+        <v>0.6610935208716082</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.605810255641608</v>
+        <v>4.516748634294313</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.916604113443471</v>
+        <v>-5.123647574199154</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.122497403434294</v>
+        <v>2.039680019132021</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.4945002957580857</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.475257271927576</v>
+        <v>4.386195650580282</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568385</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.743539734061171</v>
+        <v>-4.950583194816854</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.195399557848932</v>
+        <v>2.112582173546659</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.4945002957580857</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.478933674589294</v>
+        <v>4.389872053242</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.777206261478955</v>
+        <v>3.441649689663235</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.228007577565428</v>
+        <v>3.922772990377027</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.743539734061171</v>
+        <v>-4.950583194816854</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.195399557848932</v>
+        <v>2.112582173546659</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.4945002957580857</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.221071374551796</v>
+        <v>3.915836787363395</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>49.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>76.4%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>69.9%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>32.1%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>100.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-583.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.5%</t>
+          <t>430.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-656.6%</t>
+          <t>-632.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-239.3%</t>
+          <t>-233.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.0%</t>
+          <t>-155.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-225.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-373.6%</t>
+          <t>-319.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.5%</t>
+          <t>-157.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-135.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.4%</t>
+          <t>-34.3%</t>
         </is>
       </c>
     </row>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.122144662255674</v>
+        <v>-3.986026926768527</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.474857244814767</v>
+        <v>1.529304339009626</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.02157549763324162</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>3.111126235450839</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.356838656388226</v>
+        <v>-4.220720920901079</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.369264422163837</v>
+        <v>1.423711516358696</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.04760358204652515</v>
+        <v>-0.01523923040398645</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.08379415980496</v>
+        <v>3.103212770790483</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.692501303618679</v>
+        <v>-4.556383568131531</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.233579954927621</v>
+        <v>1.28802704912248</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.08317021589289125</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.041616160167582</v>
+        <v>3.061034771153105</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.76894563382155</v>
+        <v>-4.632827898334403</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.209489783080714</v>
+        <v>1.263936877275573</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.002724706799229371</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>3.115789636843544</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.134073016460297</v>
+        <v>-4.99795528097315</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.062693345031047</v>
+        <v>1.117140439225905</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.2990354910982419</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.937257681269968</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.542661793640976</v>
+        <v>-5.406544058153829</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8980193781735339</v>
+        <v>0.9524664723683931</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7076242682789203</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.69086595897632</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.656422205663841</v>
+        <v>-5.520304470176693</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8477006458358489</v>
+        <v>0.9021477400307076</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7076242682789203</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.68605139144778</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.072814079950838</v>
+        <v>-5.936696344463691</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6791379467299272</v>
+        <v>0.7335850409247859</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7076242682789203</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.684045442056658</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.433987709767826</v>
+        <v>-6.297869974280679</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5449271854718107</v>
+        <v>0.5993742796666699</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7076242682789203</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.694304132725337</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.777246229410845</v>
+        <v>-6.641128493923698</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4037233427602986</v>
+        <v>0.4581704369551574</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7076242682789203</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.690403697871032</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.825449046653189</v>
+        <v>-6.689331311166042</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3828471359183618</v>
+        <v>0.437294230113221</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7076242682789203</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.688808617926033</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-6.985992652976239</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.3224086693183499</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7763674040127989</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.651341712414914</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.172712361285542</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.243694481460226</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7763674040127989</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.647315407880511</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.555713750028173</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>0.09039182464158912</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7763674040127989</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.647213306558927</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.560200195229561</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>0.09116876253246398</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7808538492141877</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.647092955409524</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-7.919730517733563</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.04729306317108639</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7808538492141877</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.652443258707574</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-7.970079581187785</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.0595166685955979</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-0.8312029126684097</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.630149840592218</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.067698858609182</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.09552262894238783</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-0.9288221900898064</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.574620024761149</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.121770358117541</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.1142576724241589</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-0.9828936895981658</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.545070681377705</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.326028533447404</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.1904477454374622</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.110532634212155</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.474000511727954</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.359681371955878</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.1994263263564156</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.210946002129192</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.418235045462168</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.286211540288429</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1546666921960149</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.137476170461743</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.477688645956059</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.461335957674972</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.2101612384031153</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.312600587848287</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.387169216271649</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.695788051689462</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.3111612409105073</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.312600587848287</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.379950051370053</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.800162782715908</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.3595833240950621</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.416975318874733</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.310653021980209</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-8.962676248414493</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.4234729205359393</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.51460874929342</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.253188753567553</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.088713041782782</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.4711939092541404</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489357126483677</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.271033455882514</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.031641269886851</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4443748648093671</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489357126483677</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.275023791568914</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.173313111610971</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.5025188283977569</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489357126483677</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.273548564670173</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.123722267186137</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.467629080462951</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.439766282058843</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.318356481489945</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-8.974803932714281</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4211128803208912</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.40851669132367</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.324055102284366</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.748958779994869</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.3211957461969179</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.366590015736507</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.358790180672873</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.624380123657277</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.2702251391058224</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.366590015736507</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.359929325228932</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.677275411701563</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.2887494801614294</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.361634669648061</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.365536307044107</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.605142236413682</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2541625058076402</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.361634669648061</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.371270011282744</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.543103925459326</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2390844438197628</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.299596358693703</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.398755735461493</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.449644891474101</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.2115843115385805</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.299596358693703</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.388872254148585</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.438991709920669</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.209157599416582</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.299596358693703</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.387037693649212</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.341084671244179</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.1702950989194463</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.231610608833147</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.427528828592085</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.317131130268221</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1600451763835697</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.207657067857189</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.442569459323153</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.053071191945424</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.06768151721620308</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.943597129534393</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.587745106155078</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.345991568440586</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.2123632985254313</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.943597129534393</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.584958072494778</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.305807270074395</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.2287806417597489</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.9034128311682023</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.609412275402334</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.142407399135033</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.2935074113562508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.7400129602288398</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.706819019186708</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-6.908926176905434</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.3948243290859428</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.5065317379992412</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.854832181362319</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.759259785897919</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.4517986751759895</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.4136282467567053</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.907682065794882</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.626984312267033</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.500076351375371</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.2813527731258186</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.982414836720441</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.471245979707291</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.5651867450869048</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.1256144405660771</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.078672896943922</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.386281312977971</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.6120789530022912</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.0406497738367575</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.142558038205173</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.491871302751075</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.441867027493831</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.1462397636098619</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.951228114742092</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.423636718125648</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.5177052032210883</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.1278244407373259</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>3.0108216503427</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.275696676718049</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.4570022970959604</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.1075035248287683</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.903135277199667</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.22272715446406</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.4694761197440775</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.05453400257477942</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.926203004298582</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.056938958503769</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.528830786033101</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.05453400257477942</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.919242392203488</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-6.023575752025001</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.5566384230057513</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.05453400257477942</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.933704746584632</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-5.915316614902479</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.594474198313955</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.05453400257477942</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.928236867043827</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-5.792025480085348</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.6412887462513845</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.06875713224235108</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>2.999709641944682</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-5.739328612954057</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.6700684713412262</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1214539993736423</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>3.039028740460782</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.495563170970613</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.7633553564816546</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1214539993736423</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>3.034809448807832</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.40578749859414</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.8013899393522594</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1830534442879523</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.073893429676434</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.155937104645066</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.8940721719155915</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1830534442879523</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.066635504660137</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-4.980045012177634</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.968028132423213</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1830534442879523</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.070234628180785</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-4.80859854915517</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>1.049934223686752</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.3544999073104154</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.186430012048817</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.855365915877906</v>
+        <v>-4.728576262046049</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.030247754613955</v>
+        <v>1.080963616146697</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.4345221944195364</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.233463861930586</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.803496784729577</v>
+        <v>-4.664940519812115</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.055690208127603</v>
+        <v>1.111112714094588</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4633550555806165</v>
+        <v>0.498157936653471</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.255458379681552</v>
+        <v>3.276340108325265</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.692070025403657</v>
+        <v>-4.553513760486195</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.081455170641767</v>
+        <v>1.136877676608752</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4633550555806165</v>
+        <v>0.498157936653471</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.236652638465348</v>
+        <v>3.25753436710906</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.702572648468946</v>
+        <v>-4.564016383551484</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.078997198040529</v>
+        <v>1.134419704007514</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4528524325153276</v>
+        <v>0.4876553135881821</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.232094141251051</v>
+        <v>3.252975869894764</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.630330080297751</v>
+        <v>-4.491773815380289</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.111823539143827</v>
+        <v>1.167246045110812</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4528524325153276</v>
+        <v>0.4876553135881821</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.236023455085872</v>
+        <v>3.256905183729584</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.612616393419886</v>
+        <v>-4.474060128502424</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.119587597812313</v>
+        <v>1.175010103779298</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4560337614122444</v>
+        <v>0.490836642485099</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.238610836341361</v>
+        <v>3.259492564985075</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.503811507940159</v>
+        <v>-4.365255243022697</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.160107623224197</v>
+        <v>1.215530129191182</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4560337614122444</v>
+        <v>0.490836642485099</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.235608907561355</v>
+        <v>3.256490636205068</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.283790709903148</v>
+        <v>-4.145234444985686</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.249694979449616</v>
+        <v>1.305117485416601</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5972536064802246</v>
+        <v>0.6320564875530792</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.321919851612757</v>
+        <v>3.34280158025647</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.150923020839871</v>
+        <v>-4.012366755922408</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.31873623787675</v>
+        <v>1.374158743843735</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5972536064802246</v>
+        <v>0.6320564875530792</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.337814034414581</v>
+        <v>3.358695763058293</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.030749937475372</v>
+        <v>-3.89219367255791</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.367951315662852</v>
+        <v>1.423373821629836</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7174266898447236</v>
+        <v>0.7522295709175781</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.411063728873582</v>
+        <v>3.431945457517295</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.895496576145395</v>
+        <v>-3.756940311227932</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.432140762756282</v>
+        <v>1.487563268723267</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8526800511747007</v>
+        <v>0.8874829322475553</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.502303848233008</v>
+        <v>3.523185576876721</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.955371403503087</v>
+        <v>-3.816815138585625</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.394228323214631</v>
+        <v>1.449650829181616</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7928052238170086</v>
+        <v>0.8276081048898631</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.452416443219819</v>
+        <v>3.473298171863531</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.83555117259225</v>
+        <v>-3.696994907674787</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.457445584813175</v>
+        <v>1.512868090780159</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7928052238170086</v>
+        <v>0.8276081048898631</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.467705612454027</v>
+        <v>3.48858734109774</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.838020879054056</v>
+        <v>-3.699464614136593</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.364101901550894</v>
+        <v>1.419524407517879</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7903355173552025</v>
+        <v>0.8251383984280569</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.373867987899385</v>
+        <v>3.394749716543098</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.906391065378066</v>
+        <v>-3.767834800460603</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.256015688506591</v>
+        <v>1.311438194473576</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7996112163914174</v>
+        <v>0.8344140974642719</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.298695268806416</v>
+        <v>3.319576997450128</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.920179118225112</v>
+        <v>-3.78162285330765</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.240937175999664</v>
+        <v>1.296359681966649</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7996112163914174</v>
+        <v>0.8344140974642719</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.289131977438307</v>
+        <v>3.310013706082019</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.975699194117702</v>
+        <v>-3.837142929200239</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.35575998233483</v>
+        <v>1.411182488301815</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7996112163914174</v>
+        <v>0.8344140974642719</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.426162814130509</v>
+        <v>3.447044542774222</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.800224934325233</v>
+        <v>-3.66166866940777</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.430516918243606</v>
+        <v>1.485939424210591</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7996112163914174</v>
+        <v>0.8344140974642719</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.430730046122297</v>
+        <v>3.451611774766009</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.911161186966481</v>
+        <v>-3.772604922049019</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.361884445948313</v>
+        <v>1.417306951915299</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7996112163914174</v>
+        <v>0.8344140974642719</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.406472074883504</v>
+        <v>3.427353803527216</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.8774976414942</v>
+        <v>-3.738941376576737</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.303888177538676</v>
+        <v>1.359310683505661</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8332747618636993</v>
+        <v>0.8680776429365538</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.355208515568323</v>
+        <v>3.376090244212036</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.817645022290476</v>
+        <v>-3.679088757373014</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.338001611652298</v>
+        <v>1.393424117619283</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8332747618636993</v>
+        <v>0.8680776429365538</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.365380902000455</v>
+        <v>3.386262630644168</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.731401559264099</v>
+        <v>-3.592845294346636</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.367445267436709</v>
+        <v>1.422867773403694</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8332747618636993</v>
+        <v>0.8680776429365538</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.360327172574316</v>
+        <v>3.381208901218028</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.776708378663079</v>
+        <v>-3.638152113745616</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.341098315121642</v>
+        <v>1.396520821088628</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7924645988544685</v>
+        <v>0.827267479927323</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.327616850213303</v>
+        <v>3.348498578857015</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.80574148336538</v>
+        <v>-3.667185218447918</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.330036946273824</v>
+        <v>1.385459452240808</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7924645988544685</v>
+        <v>0.827267479927323</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.328168723246404</v>
+        <v>3.349050451890117</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.712931001914521</v>
+        <v>-3.574374736997059</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.296433830745533</v>
+        <v>1.351856336712518</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8852750803053279</v>
+        <v>0.9200779613781823</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.313127704008286</v>
+        <v>3.334009432651998</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.757320471243949</v>
+        <v>-3.618764206326486</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.280551518938362</v>
+        <v>1.335974024905348</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8408856109759002</v>
+        <v>0.8756884920487547</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.28836749833523</v>
+        <v>3.309249226978943</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.873862076349292</v>
+        <v>-3.735305811431829</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.229010585407948</v>
+        <v>1.284433091374933</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7243440058705575</v>
+        <v>0.7591468869434119</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.213518243783747</v>
+        <v>3.23439997242746</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.913786170931863</v>
+        <v>-3.775229906014401</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.218532243405587</v>
+        <v>1.273954749372572</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7243440058705575</v>
+        <v>0.7591468869434119</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.219009539614414</v>
+        <v>3.239891268258127</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.941566568833216</v>
+        <v>-3.803010303915754</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.218917286013585</v>
+        <v>1.27433979198057</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6965636079692044</v>
+        <v>0.7313664890420588</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.213838502642142</v>
+        <v>3.234720231285854</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.059947241563354</v>
+        <v>-3.921390976645892</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.009920736922183</v>
+        <v>1.065343242889168</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6293457558182282</v>
+        <v>0.6641486368910826</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.011863511352209</v>
+        <v>3.032745239995922</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.168561320006686</v>
+        <v>-4.030005055089223</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.086624766264056</v>
+        <v>1.142047272231041</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6293457558182282</v>
+        <v>0.6641486368910826</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.132013172071415</v>
+        <v>3.152894900715127</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.133152281758543</v>
+        <v>-3.99459601684108</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.115301407665636</v>
+        <v>1.170723913632621</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6293457558182282</v>
+        <v>0.6641486368910826</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.146526198173738</v>
+        <v>3.16740792681745</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.094768619200392</v>
+        <v>-3.956212354282929</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.128074314031265</v>
+        <v>1.18349681999825</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6677294183763793</v>
+        <v>0.7025322994492338</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.166975837050997</v>
+        <v>3.18785756569471</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.917652289165225</v>
+        <v>-3.779096024247763</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.195649874890634</v>
+        <v>1.251072380857619</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6677294183763793</v>
+        <v>0.7025322994492338</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.163704865896299</v>
+        <v>3.184586594540012</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.962744533998771</v>
+        <v>-3.824188269081309</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.178296368719129</v>
+        <v>1.233718874686113</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6058333752069895</v>
+        <v>0.640636256279844</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.127250631756578</v>
+        <v>3.148132360400291</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.783369112760004</v>
+        <v>-3.644812847842541</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.24383351252105</v>
+        <v>1.299256018488035</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7626101333777082</v>
+        <v>0.7974130144505627</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.215103661965424</v>
+        <v>3.235985390609136</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.82838332628061</v>
+        <v>-3.689827061363147</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.206635282444397</v>
+        <v>1.262057788411382</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7322612380631036</v>
+        <v>0.7670641191359581</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.177701780108251</v>
+        <v>3.198583508751963</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.095387836553045</v>
+        <v>-3.956831571635583</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.105525040674369</v>
+        <v>1.160947546641354</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5378982000201551</v>
+        <v>0.5727010810930095</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.066775519621427</v>
+        <v>3.08765724826514</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.196585617990218</v>
+        <v>-4.058029353072755</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.064249849996001</v>
+        <v>1.119672355962986</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4694893864748359</v>
+        <v>0.5042922675476904</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.024934153390737</v>
+        <v>3.04581588203445</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.190074651375905</v>
+        <v>-4.051518386458443</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.064454198196043</v>
+        <v>1.119876704163028</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4694893864748359</v>
+        <v>0.5042922675476904</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.022534114945054</v>
+        <v>3.043415843588767</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.171036523668608</v>
+        <v>-4.032480258751145</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.068594168487207</v>
+        <v>1.124016674454192</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4113057751436414</v>
+        <v>0.4461086562164959</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.984148667354583</v>
+        <v>3.005030395998295</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.223552325943428</v>
+        <v>-4.084996061025966</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.166882249211469</v>
+        <v>1.222304755178454</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4113057751436414</v>
+        <v>0.4461086562164959</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.103443068988772</v>
+        <v>3.124324797632485</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.237419087277346</v>
+        <v>-4.098862822359884</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.162168873664035</v>
+        <v>1.21759137963102</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3734478584098184</v>
+        <v>0.4082507394826729</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.081561647934612</v>
+        <v>3.102443376578325</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.192614915737416</v>
+        <v>-4.054058650819954</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.186099072676933</v>
+        <v>1.241521578643918</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3734478584098184</v>
+        <v>0.4082507394826729</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.087570178331538</v>
+        <v>3.108451906975251</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.224643559255988</v>
+        <v>-3.906315680584952</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.071237836546704</v>
+        <v>1.198568988015118</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4045857911514822</v>
+        <v>0.5760580967175561</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.004203159253736</v>
+        <v>3.107086542593381</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.308464780530686</v>
+        <v>-3.99013690185965</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.040502969568306</v>
+        <v>1.16783412103672</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4045857911514822</v>
+        <v>0.5760580967175561</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.006996780785217</v>
+        <v>3.109880164124862</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.302312074477902</v>
+        <v>-3.983984195806865</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.043626400381078</v>
+        <v>1.170957551849492</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4107384972042665</v>
+        <v>0.5822108027703404</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.011350752808546</v>
+        <v>3.11423413614819</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.319121372628404</v>
+        <v>-4.000793493957367</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.035983157860987</v>
+        <v>1.163314309329402</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3939291990537648</v>
+        <v>0.5654015046198388</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.000345650658355</v>
+        <v>3.103229033998</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.256823373852281</v>
+        <v>-3.938495495181245</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.127237911168257</v>
+        <v>1.254569062636672</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4392234633282069</v>
+        <v>0.6106957688942809</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.093857763019841</v>
+        <v>3.196741146359486</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.055033176187123</v>
+        <v>-3.736705297516087</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.010245991948447</v>
+        <v>1.137577143416862</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6372416554973612</v>
+        <v>0.8087139610634353</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.014960680035461</v>
+        <v>3.117844063375105</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.105919888873318</v>
+        <v>-3.787592010202282</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.060181539196145</v>
+        <v>1.187512690664559</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5863549428111667</v>
+        <v>0.7578272483772408</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.054718884745919</v>
+        <v>3.157602268085564</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.019309146223511</v>
+        <v>-3.700981267552475</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.109453572372111</v>
+        <v>1.236784723840526</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.664980674016325</v>
+        <v>0.8364529795823991</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.116522059585058</v>
+        <v>3.219405442924702</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.079518444228796</v>
+        <v>-3.761190565557759</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.083905833994669</v>
+        <v>1.211236985463084</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6047713760110405</v>
+        <v>0.7762436815771145</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.078932461606559</v>
+        <v>3.181815844946204</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.003096397796869</v>
+        <v>-3.684768519125833</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.112966270607368</v>
+        <v>1.240297422075783</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6047713760110405</v>
+        <v>0.7762436815771145</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.077424079646488</v>
+        <v>3.180307462986132</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.958723266158301</v>
+        <v>-3.640395387487264</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.130578390698232</v>
+        <v>1.257909542166647</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6491445076496091</v>
+        <v>0.8206168132156831</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.103910826065065</v>
+        <v>3.206794209404709</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.981203617017186</v>
+        <v>-3.662875738346149</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.115980044493268</v>
+        <v>1.243311195961683</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6491445076496091</v>
+        <v>0.8206168132156831</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.098304620203656</v>
+        <v>3.2011880035433</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.93354788645613</v>
+        <v>-3.615220007785093</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.141424093745495</v>
+        <v>1.26875524521391</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6968002382106647</v>
+        <v>0.8682725437767388</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.133279815568093</v>
+        <v>3.236163198907738</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.833029727957375</v>
+        <v>-3.514701849286338</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.186523730519722</v>
+        <v>1.313854881988137</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7973183967094193</v>
+        <v>0.9687907022754934</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.198483084042071</v>
+        <v>3.301366467381715</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.817124398525022</v>
+        <v>-3.498796519853986</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.179640534768535</v>
+        <v>1.30697168623695</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7182057360001803</v>
+        <v>0.8896780415662544</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.1377701600924</v>
+        <v>3.240653543432044</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.772285996916624</v>
+        <v>-3.453958118245588</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.201673598022523</v>
+        <v>1.329004749490938</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7227491689450498</v>
+        <v>0.8942214745111239</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.14459392246995</v>
+        <v>3.247477305809594</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.791784453158633</v>
+        <v>-3.473456574487596</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.198035155156798</v>
+        <v>1.325366306625213</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6746645276651455</v>
+        <v>0.8461368332312196</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.119904077333086</v>
+        <v>3.22278746067273</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.747581616072732</v>
+        <v>-3.429253737401695</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.221595892518995</v>
+        <v>1.34892704398741</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.718867364751046</v>
+        <v>0.89033967031712</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.152305382112463</v>
+        <v>3.255188765452107</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.755141281909779</v>
+        <v>-3.436813403238742</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.216982026653424</v>
+        <v>1.344313178121839</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7736707687608653</v>
+        <v>0.9451430743269393</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.183597424987602</v>
+        <v>3.286480808327247</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.596849864370507</v>
+        <v>-3.27852198569947</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.331546358852172</v>
+        <v>1.458877510320587</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7736707687608653</v>
+        <v>0.9451430743269393</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.234845190170642</v>
+        <v>3.337728573510286</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.389207860736031</v>
+        <v>-3.070879982064994</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.413043864900216</v>
+        <v>1.540375016368631</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9813127723953414</v>
+        <v>1.152785077961415</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.357871096945581</v>
+        <v>3.460754480285225</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.338175768013503</v>
+        <v>-3.019847889342466</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.428404930227497</v>
+        <v>1.555736081695912</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.032344865117869</v>
+        <v>1.203817170683943</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.383438580817367</v>
+        <v>3.486321964157012</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.272951586886297</v>
+        <v>-2.95462370821526</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.471682006771085</v>
+        <v>1.5990131582395</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.097569046245075</v>
+        <v>1.269041351811149</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.439760493586396</v>
+        <v>3.54264387692604</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.235524566815163</v>
+        <v>-2.917196688144126</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.482613787098818</v>
+        <v>1.609944938567233</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.102820584274257</v>
+        <v>1.274292889840331</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.438872388703185</v>
+        <v>3.541755772042829</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.255636222849871</v>
+        <v>-2.937308344178835</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.475825917016175</v>
+        <v>1.60315706848459</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.113847929271676</v>
+        <v>1.28532023483775</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.446745588032877</v>
+        <v>3.549628971372521</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.201891408422667</v>
+        <v>-2.88356352975163</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.657881613808268</v>
+        <v>1.785212765276683</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.123911238712138</v>
+        <v>1.295383544278212</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.613341344718365</v>
+        <v>3.716224728058009</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.127109147397654</v>
+        <v>-2.808781268726617</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.80790742743609</v>
+        <v>1.935238578904505</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.198693499737151</v>
+        <v>1.370165805303225</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.77832361055119</v>
+        <v>3.881206993890834</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.101025063133846</v>
+        <v>-2.782697184462809</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.810049037155472</v>
+        <v>1.937380188623887</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.198693499737151</v>
+        <v>1.370165805303225</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.770031586565049</v>
+        <v>3.872914969904693</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.013147150024726</v>
+        <v>-2.694819271353689</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.8433933979829</v>
+        <v>1.970724549451315</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.314619142160502</v>
+        <v>1.486091447726576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.837780167602839</v>
+        <v>3.940663550942483</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.004254688631442</v>
+        <v>-2.685926809960405</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.864504788267005</v>
+        <v>1.99183593973542</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.314619142160502</v>
+        <v>1.486091447726576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.85533457332963</v>
+        <v>3.958217956669275</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.17273080560132</v>
+        <v>-2.854402926930283</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.788969388883638</v>
+        <v>1.916300540352053</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.286671306443921</v>
+        <v>1.458143612009995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.830420919304266</v>
+        <v>3.933304302643911</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.72647461297188</v>
+        <v>-2.408146734300843</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.948741563123276</v>
+        <v>2.076072714591691</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.191952636774289</v>
+        <v>1.363424942340362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.754859414690348</v>
+        <v>3.857742798029992</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.703753509288727</v>
+        <v>-2.385425630617691</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.948494027093441</v>
+        <v>2.075825178561856</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.191952636774289</v>
+        <v>1.363424942340362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.745523437187253</v>
+        <v>3.848406820526897</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.83295532258277</v>
+        <v>-2.514627443911733</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.055719427626993</v>
+        <v>2.183050579095408</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.062750823480246</v>
+        <v>1.23422312904632</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.826908475061996</v>
+        <v>3.929791858401641</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.987736329361026</v>
+        <v>-2.669408450689989</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.030884847409338</v>
+        <v>2.158215998877752</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.02938314942577</v>
+        <v>1.200855454991844</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.843965693122957</v>
+        <v>3.946849076462602</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.980681639145852</v>
+        <v>-2.662353760474815</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.030382079484952</v>
+        <v>2.157713230953367</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.036437839640944</v>
+        <v>1.207910145207018</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.844873863241607</v>
+        <v>3.947757246581251</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.953730414819364</v>
+        <v>-2.635402536148327</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.051168722860289</v>
+        <v>2.178499874328704</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.051318185668663</v>
+        <v>1.222790491234737</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.86380822450298</v>
+        <v>3.966691607842624</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.08968342287568</v>
+        <v>-2.771355544204643</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.180890651782722</v>
+        <v>2.308221803251137</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.051318185668663</v>
+        <v>1.222790491234737</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.04791135664794</v>
+        <v>4.150794739987584</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.112091540680552</v>
+        <v>-2.793763662009515</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.164044099563767</v>
+        <v>2.291375251032181</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.051318185668663</v>
+        <v>1.222790491234737</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.040028051550933</v>
+        <v>4.142911434890577</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.140315776258153</v>
+        <v>-2.821987897587116</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.154808404882364</v>
+        <v>2.282139556350779</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.069294938119972</v>
+        <v>1.240767243686046</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.052868102571355</v>
+        <v>4.155751485911</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.149756702146683</v>
+        <v>-2.831428823475646</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.207285752248799</v>
+        <v>2.334616903717214</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.191722055663363</v>
+        <v>1.363194361229437</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.182578090819237</v>
+        <v>4.285461474158882</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.202030309482324</v>
+        <v>-2.883702430811287</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.189267403859843</v>
+        <v>2.316598555328258</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.139448448327722</v>
+        <v>1.310920753893796</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.154105020963153</v>
+        <v>4.256988404302797</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.27836028708323</v>
+        <v>-2.960032408412193</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.156847225713256</v>
+        <v>2.284178377181671</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.139448448327722</v>
+        <v>1.310920753893796</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.152216833856929</v>
+        <v>4.255100217196572</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.480614007407583</v>
+        <v>-3.162286128736546</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.070765967186377</v>
+        <v>2.198097118654792</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9371947280033683</v>
+        <v>1.108667033569442</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.025684831265179</v>
+        <v>4.128568214604823</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.642182432934838</v>
+        <v>-3.323854554263801</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.004572607185627</v>
+        <v>2.131903758654042</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.810411804205489</v>
+        <v>0.9818841097715628</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.948049087196603</v>
+        <v>4.050932470536248</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.774483725032391</v>
+        <v>-3.456155846361355</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.964725497212525</v>
+        <v>2.09205664868094</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.810411804205489</v>
+        <v>0.9818841097715628</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.961122494062522</v>
+        <v>4.064005877402167</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.960352035871622</v>
+        <v>-3.642024157200585</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.882383369659772</v>
+        <v>2.009714521128187</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6518462108855413</v>
+        <v>0.8233185164516151</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.857988334853494</v>
+        <v>3.960871718193138</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.988252822981095</v>
+        <v>-3.669924944310058</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.869747095942985</v>
+        <v>1.9970782474114</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6172492867426065</v>
+        <v>0.7887215923086803</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.835754221494735</v>
+        <v>3.938637604834379</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.110778925683988</v>
+        <v>-3.792451047012952</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.817501098839027</v>
+        <v>1.944832250307441</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4947231840397126</v>
+        <v>0.6661954896057865</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.759003003850197</v>
+        <v>3.861886387189841</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.341293421869577</v>
+        <v>-4.02296554319854</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.792001259955295</v>
+        <v>1.91933241142371</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2642086878541239</v>
+        <v>0.4356809934201977</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.687400265729348</v>
+        <v>3.790283649068992</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.598014239864401</v>
+        <v>-4.279686361193363</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.829624651759212</v>
+        <v>1.956955803227627</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.155794113710309</v>
+        <v>0.3272664192763829</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.762663240244906</v>
+        <v>3.86554662358455</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.752000657640542</v>
+        <v>-4.433672778969504</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.837010353794396</v>
+        <v>1.964341505262811</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.155794113710309</v>
+        <v>0.3272664192763829</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.831643509390545</v>
+        <v>3.934526892730189</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.701478753812876</v>
+        <v>-4.383150875141838</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.843270317445583</v>
+        <v>1.970601468913998</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.155794113710309</v>
+        <v>0.3272664192763829</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.817694711510666</v>
+        <v>3.920578094850311</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.87997522816077</v>
+        <v>-4.635626029149562</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.783742216761839</v>
+        <v>1.881481896366322</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.155794113710309</v>
+        <v>0.3272664192763829</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.82956520056608</v>
+        <v>3.932448583905725</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.172870984640182</v>
+        <v>-4.928521785628974</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.667794448689018</v>
+        <v>1.765534128293501</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.155794113710309</v>
+        <v>0.3272664192763829</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.830775735085024</v>
+        <v>3.933659118424668</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.330415056369624</v>
+        <v>-5.086065857358416</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.608898562224563</v>
+        <v>1.706638241829046</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08889230857003455</v>
+        <v>0.2603646141361084</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.794756394228181</v>
+        <v>3.897639777567825</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.608379451952898</v>
+        <v>-5.364030252941689</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.492790656727443</v>
+        <v>1.590530336331926</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.0007274257154497032</v>
+        <v>0.1707448798506241</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.73606240639308</v>
+        <v>3.838945789732724</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.725347144591789</v>
+        <v>-5.48099794558058</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.608207636370931</v>
+        <v>1.705947315975414</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.0007274257154497032</v>
+        <v>0.1707448798506241</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.898266463092124</v>
+        <v>4.001149846431768</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.810065086812742</v>
+        <v>-5.565715887801534</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.569167097446364</v>
+        <v>1.666906777050847</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.08584345464349608</v>
+        <v>0.08562885092257777</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.84204348369911</v>
+        <v>3.944926867038754</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.891999905081625</v>
+        <v>-5.647650706070417</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.546622587707301</v>
+        <v>1.644362267311784</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.09577820023057626</v>
+        <v>0.07569410533549759</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.846312053915353</v>
+        <v>3.949195437254997</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.993976027330032</v>
+        <v>-5.749626828318824</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.514757777263841</v>
+        <v>1.612497456868324</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1977543224789838</v>
+        <v>-0.02628201691290999</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.794052019022211</v>
+        <v>3.896935402361855</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.883969743852811</v>
+        <v>-5.639620544841603</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.550913177898905</v>
+        <v>1.648652857503388</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1745497505617086</v>
+        <v>-0.003077444995634782</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.800127649416751</v>
+        <v>3.903011032756396</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.740910168111885</v>
+        <v>-5.496560969100678</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.61238701891725</v>
+        <v>1.710126698521732</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1665363239717293</v>
+        <v>0.004935981594344496</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.809185716092713</v>
+        <v>3.912069099432357</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.439463442640047</v>
+        <v>-5.19511424362884</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.740226591988521</v>
+        <v>1.837966271593003</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1349104015001079</v>
+        <v>0.3063827070661818</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.997314634258352</v>
+        <v>4.100198017597996</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.464053686875231</v>
+        <v>-5.219704487864024</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.731361672047158</v>
+        <v>1.82910135165164</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1349104015001079</v>
+        <v>0.3063827070661818</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.998285812011062</v>
+        <v>4.101169195350707</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.413015310868711</v>
+        <v>-5.168666111857504</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.752619926829521</v>
+        <v>1.850359606434004</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1349104015001079</v>
+        <v>0.3063827070661818</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.999128716390818</v>
+        <v>4.102012099730461</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.37187601600208</v>
+        <v>-5.127526816990873</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.788113743650319</v>
+        <v>1.885853423254801</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1760496963667387</v>
+        <v>0.3475220019328126</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.042850392184941</v>
+        <v>4.145733775524586</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.261269875922478</v>
+        <v>-5.016920676911271</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.648540195806094</v>
+        <v>1.746279875410577</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2866558364463407</v>
+        <v>0.4581281420124146</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.925398072356638</v>
+        <v>4.028281455696281</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.391850610453321</v>
+        <v>-5.147501411442113</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.599809946067721</v>
+        <v>1.697549625672203</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1560751019154982</v>
+        <v>0.3275474074815721</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.850551675712095</v>
+        <v>3.953435059051739</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.227354276262359</v>
+        <v>-4.983005077251152</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.650035298820188</v>
+        <v>1.747774978424671</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1560751019154982</v>
+        <v>0.3275474074815721</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.834978494788178</v>
+        <v>3.937861878127822</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.254724208946791</v>
+        <v>-5.010375009935584</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.638275036182845</v>
+        <v>1.736014715787328</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1560751019154982</v>
+        <v>0.3275474074815721</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.834166205224608</v>
+        <v>3.937049588564252</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.26510940383668</v>
+        <v>-5.020760204825473</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.643989737351961</v>
+        <v>1.741729416956444</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1456899070256089</v>
+        <v>0.3171622125916828</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.837803867415746</v>
+        <v>3.94068725075539</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.283697562558905</v>
+        <v>-5.039348363547698</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.707391479639496</v>
+        <v>1.80513115924398</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1271017483033836</v>
+        <v>0.2985740538694574</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.897487977958837</v>
+        <v>4.00037136129848</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.283996109254941</v>
+        <v>-5.039646910243734</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.704141071779381</v>
+        <v>1.801880751383864</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1271017483033836</v>
+        <v>0.2985740538694574</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.894356988777135</v>
+        <v>3.997240372116779</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.183172975564514</v>
+        <v>-4.938823776553306</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.749001220194943</v>
+        <v>1.846740899799426</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1395659637877374</v>
+        <v>0.3110382693538112</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.906366413007138</v>
+        <v>4.009249796346783</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.992391614812107</v>
+        <v>-4.748042415800899</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.825443017974449</v>
+        <v>1.923182697578932</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3303473245401448</v>
+        <v>0.5018196301062186</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.020964482937126</v>
+        <v>4.123847866276771</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.973874760770286</v>
+        <v>-4.729525561759079</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.812686605328774</v>
+        <v>1.910426284933257</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.343277453965353</v>
+        <v>0.5147497595314268</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.008559406329848</v>
+        <v>4.111442789669492</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.948681576268968</v>
+        <v>-4.704332377257761</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.857730815741359</v>
+        <v>1.955470495345843</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3684706384666713</v>
+        <v>0.5399429440327451</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.058642253642697</v>
+        <v>4.161525636982342</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.936627449356005</v>
+        <v>-4.692278250344798</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.856239034407982</v>
+        <v>1.953978714012465</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3805247653796341</v>
+        <v>0.5519970709457079</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.059561297691912</v>
+        <v>4.162444681031557</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.943250696046364</v>
+        <v>-4.698901497035156</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.855470365915975</v>
+        <v>1.953210045520458</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.3739015186892758</v>
+        <v>0.5453738242553496</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.057467979861833</v>
+        <v>4.160351363201478</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.840370106517771</v>
+        <v>-4.596020907506563</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.909473627605295</v>
+        <v>2.007213307209778</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4767821082178687</v>
+        <v>0.6482544137839426</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.132047359456871</v>
+        <v>4.234930742796516</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.863812145697858</v>
+        <v>-4.61946294668665</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.920299482106854</v>
+        <v>2.018039161711337</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4767821082178687</v>
+        <v>0.6482544137839426</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.152250029630466</v>
+        <v>4.25513341297011</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.881884653989469</v>
+        <v>-4.637535454978262</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.91307047879021</v>
+        <v>2.010810158394692</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4767821082178687</v>
+        <v>0.6482544137839426</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.152250029630466</v>
+        <v>4.25513341297011</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.113058447866101</v>
+        <v>-4.868709248854894</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.780852874833023</v>
+        <v>1.878592554437506</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4767821082178687</v>
+        <v>0.6482544137839426</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.112501943223933</v>
+        <v>4.215385326563577</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.081772427325646</v>
+        <v>-4.837423228314439</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.800389902046145</v>
+        <v>1.898129581650628</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5080681287583241</v>
+        <v>0.6795404343243979</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.138296174545146</v>
+        <v>4.24117955788479</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.928747035212361</v>
+        <v>-4.684397836201154</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.960771058464363</v>
+        <v>2.058510738068846</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.6610935208716082</v>
+        <v>0.8325658264376821</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.32928240938602</v>
+        <v>4.432165792725664</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.957054349085632</v>
+        <v>-4.712705150074425</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.136914357823348</v>
+        <v>2.234654037427831</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.6610935208716082</v>
+        <v>0.8325658264376821</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.516748634294313</v>
+        <v>4.619632017633957</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.123647574199154</v>
+        <v>-4.879298375187947</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.039680019132021</v>
+        <v>2.137419698736504</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.4945002957580857</v>
+        <v>0.6659726013241596</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.386195650580282</v>
+        <v>4.489079033919926</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.950583194816854</v>
+        <v>-4.706233995805647</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.112582173546659</v>
+        <v>2.210321853151141</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.4945002957580857</v>
+        <v>0.6659726013241596</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.389872053242</v>
+        <v>4.492755436581644</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.441649689663235</v>
+        <v>3.773277399690336</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.922772990377027</v>
+        <v>4.124485843052149</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.950583194816854</v>
+        <v>-4.706233995805647</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.112582173546659</v>
+        <v>2.210321853151141</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.4945002957580857</v>
+        <v>0.6659726013241596</v>
       </c>
       <c r="G2055" t="n">
-        <v>3.915836787363395</v>
+        <v>4.117549640038517</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.8%</t>
+          <t>96.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-583.6%</t>
+          <t>-599.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.3%</t>
+          <t>430.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-632.2%</t>
+          <t>-655.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-233.9%</t>
+          <t>-240.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-165.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-225.5%</t>
+          <t>-235.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.3%</t>
+          <t>-390.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-170.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-135.7%</t>
+          <t>-141.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
     </row>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.986026926768527</v>
+        <v>-4.122144662255674</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.529304339009626</v>
+        <v>1.474857244814767</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.02157549763324162</v>
+        <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.111126235450839</v>
+        <v>3.091707624465316</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.220720920901079</v>
+        <v>-4.381278462700433</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.423711516358696</v>
+        <v>1.359488499638954</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.01523923040398645</v>
+        <v>-0.1164396263032174</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.103212770790483</v>
+        <v>3.042492533250944</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.556383568131531</v>
+        <v>-4.716941109930885</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.28802704912248</v>
+        <v>1.223804032402738</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.08317021589289125</v>
+        <v>-0.1843706117921222</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.061034771153105</v>
+        <v>3.000314533613567</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.632827898334403</v>
+        <v>-4.793385440133757</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.263936877275573</v>
+        <v>1.199713860555831</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.002724706799229371</v>
+        <v>-0.1039251026984603</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.115789636843544</v>
+        <v>3.055069399304005</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.99795528097315</v>
+        <v>-5.158512822772503</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.117140439225905</v>
+        <v>1.052917422506164</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.2990354910982419</v>
+        <v>-0.4002358869974728</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.937257681269968</v>
+        <v>2.876537443730429</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.406544058153829</v>
+        <v>-5.567101599953181</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9524664723683931</v>
+        <v>0.8882434556486518</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.7076242682789203</v>
+        <v>-0.8088246641781512</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.69086595897632</v>
+        <v>2.630145721436781</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.520304470176693</v>
+        <v>-5.680862011976046</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9021477400307076</v>
+        <v>0.8379247233109663</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.7076242682789203</v>
+        <v>-0.8088246641781512</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.68605139144778</v>
+        <v>2.625331153908242</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.936696344463691</v>
+        <v>-6.097253886263044</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.7335850409247859</v>
+        <v>0.6693620242050446</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.7076242682789203</v>
+        <v>-0.8088246641781512</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.684045442056658</v>
+        <v>2.623325204517119</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.297869974280679</v>
+        <v>-6.458427516080032</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5993742796666699</v>
+        <v>0.5351512629469286</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.7076242682789203</v>
+        <v>-0.8088246641781512</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.694304132725337</v>
+        <v>2.633583895185798</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.641128493923698</v>
+        <v>-6.80168603572305</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4581704369551574</v>
+        <v>0.3939474202354165</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.7076242682789203</v>
+        <v>-0.8088246641781512</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.690403697871032</v>
+        <v>2.629683460331493</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.689331311166042</v>
+        <v>-6.849888852965394</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.437294230113221</v>
+        <v>0.3730712133934797</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.7076242682789203</v>
+        <v>-0.8088246641781512</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.688808617926033</v>
+        <v>2.628088380386494</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.985992652976239</v>
+        <v>-7.146550194775592</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3224086693183499</v>
+        <v>0.258185652598609</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7763674040127989</v>
+        <v>-0.8775677999120298</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.651341712414914</v>
+        <v>2.590621474875375</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.172712361285542</v>
+        <v>-7.333269903084894</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.243694481460226</v>
+        <v>0.1794714647404847</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7763674040127989</v>
+        <v>-0.8775677999120298</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.647315407880511</v>
+        <v>2.586595170340972</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.555713750028173</v>
+        <v>-7.716271291827526</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09039182464158912</v>
+        <v>0.02616880792184828</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7763674040127989</v>
+        <v>-0.8775677999120298</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.647213306558927</v>
+        <v>2.586493069019388</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.560200195229561</v>
+        <v>-7.720757737028914</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09116876253246398</v>
+        <v>0.02694574581272269</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7808538492141877</v>
+        <v>-0.8820542451134186</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.647092955409524</v>
+        <v>2.586372717869985</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.919730517733563</v>
+        <v>-8.080288059532917</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04729306317108639</v>
+        <v>-0.1115160798908281</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7808538492141877</v>
+        <v>-0.8820542451134186</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.652443258707574</v>
+        <v>2.591723021168035</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.970079581187785</v>
+        <v>-8.130637122987139</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.0595166685955979</v>
+        <v>-0.1237396853153392</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8312029126684097</v>
+        <v>-0.9324033085676406</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.630149840592218</v>
+        <v>2.569429603052679</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.067698858609182</v>
+        <v>-8.228256400408535</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.09552262894238783</v>
+        <v>-0.1597456456621287</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9288221900898064</v>
+        <v>-1.030022585989037</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.574620024761149</v>
+        <v>2.51389978722161</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.121770358117541</v>
+        <v>-8.282327899916893</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1142576724241589</v>
+        <v>-0.1784806891439001</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9828936895981658</v>
+        <v>-1.084094085497397</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.545070681377705</v>
+        <v>2.484350443838167</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.326028533447404</v>
+        <v>-8.486586075246757</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1904477454374622</v>
+        <v>-0.2546707621572031</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.110532634212155</v>
+        <v>-1.211733030111386</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.474000511727954</v>
+        <v>2.413280274188416</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.359681371955878</v>
+        <v>-8.520238913755231</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1994263263564156</v>
+        <v>-0.2636493430761564</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.210946002129192</v>
+        <v>-1.312146398028423</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.418235045462168</v>
+        <v>2.357514807922629</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.286211540288429</v>
+        <v>-8.446769082087782</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1546666921960149</v>
+        <v>-0.2188897089157558</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.137476170461743</v>
+        <v>-1.238676566360974</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.477688645956059</v>
+        <v>2.41696840841652</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.461335957674972</v>
+        <v>-8.621893499474325</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2101612384031153</v>
+        <v>-0.2743842551228566</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.312600587848287</v>
+        <v>-1.413800983747518</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.387169216271649</v>
+        <v>2.326448978732111</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.695788051689462</v>
+        <v>-8.856345593488815</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3111612409105073</v>
+        <v>-0.3753842576302482</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.312600587848287</v>
+        <v>-1.413800983747518</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.379950051370053</v>
+        <v>2.319229813830514</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.800162782715908</v>
+        <v>-8.960720324515261</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3595833240950621</v>
+        <v>-0.423806340814803</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.416975318874733</v>
+        <v>-1.518175714773964</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.310653021980209</v>
+        <v>2.249932784440671</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.962676248414493</v>
+        <v>-9.123233790213845</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4234729205359393</v>
+        <v>-0.4876959372556806</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.51460874929342</v>
+        <v>-1.615809145192651</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.253188753567553</v>
+        <v>2.192468516028015</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.088713041782782</v>
+        <v>-9.249270583582135</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4711939092541404</v>
+        <v>-0.5354169259738817</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.489357126483677</v>
+        <v>-1.590557522382908</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.271033455882514</v>
+        <v>2.210313218342975</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.031641269886851</v>
+        <v>-9.192198811686204</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4443748648093671</v>
+        <v>-0.5085978815291083</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.489357126483677</v>
+        <v>-1.590557522382908</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.275023791568914</v>
+        <v>2.214303554029376</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.173313111610971</v>
+        <v>-9.333870653410324</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5025188283977569</v>
+        <v>-0.5667418451174981</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.489357126483677</v>
+        <v>-1.590557522382908</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.273548564670173</v>
+        <v>2.212828327130634</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.123722267186137</v>
+        <v>-9.28427980898549</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.467629080462951</v>
+        <v>-0.5318520971826923</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.439766282058843</v>
+        <v>-1.540966677958075</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.318356481489945</v>
+        <v>2.257636243950407</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.974803932714281</v>
+        <v>-9.135361474513633</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4211128803208912</v>
+        <v>-0.4853358970406325</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.40851669132367</v>
+        <v>-1.509717087222902</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.324055102284366</v>
+        <v>2.263334864744828</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.748958779994869</v>
+        <v>-8.909516321794221</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3211957461969179</v>
+        <v>-0.3854187629166592</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.366590015736507</v>
+        <v>-1.467790411635738</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.358790180672873</v>
+        <v>2.298069943133334</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.624380123657277</v>
+        <v>-8.78493766545663</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2702251391058224</v>
+        <v>-0.3344481558255636</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.366590015736507</v>
+        <v>-1.467790411635738</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.359929325228932</v>
+        <v>2.299209087689393</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.677275411701563</v>
+        <v>-8.837832953500916</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2887494801614294</v>
+        <v>-0.3529724968811703</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.361634669648061</v>
+        <v>-1.462835065547292</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.365536307044107</v>
+        <v>2.304816069504569</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.605142236413682</v>
+        <v>-8.765699778213035</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2541625058076402</v>
+        <v>-0.3183855225273815</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.361634669648061</v>
+        <v>-1.462835065547292</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.371270011282744</v>
+        <v>2.310549773743205</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.543103925459326</v>
+        <v>-8.694333385603388</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2390844438197628</v>
+        <v>-0.2995762278773877</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.299596358693703</v>
+        <v>-1.391468672937644</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.398755735461493</v>
+        <v>2.343632346915129</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.449644891474101</v>
+        <v>-8.600874351618163</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2115843115385805</v>
+        <v>-0.2720760955962054</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.299596358693703</v>
+        <v>-1.391468672937644</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.388872254148585</v>
+        <v>2.333748865602221</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.438991709920669</v>
+        <v>-8.590221170064732</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.209157599416582</v>
+        <v>-0.2696493834742069</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.299596358693703</v>
+        <v>-1.391468672937644</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.387037693649212</v>
+        <v>2.331914305102847</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.341084671244179</v>
+        <v>-8.492314131388241</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1702950989194463</v>
+        <v>-0.2307868829770712</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.231610608833147</v>
+        <v>-1.323482923077087</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.427528828592085</v>
+        <v>2.37240544004572</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.317131130268221</v>
+        <v>-8.468360590412283</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1600451763835697</v>
+        <v>-0.2205369604411946</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.207657067857189</v>
+        <v>-1.29952938210113</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.442569459323153</v>
+        <v>2.387446070776789</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.053071191945424</v>
+        <v>-8.204300652089486</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.06768151721620308</v>
+        <v>-0.128173301273828</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.943597129534393</v>
+        <v>-1.035469443778334</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.587745106155078</v>
+        <v>2.532621717608714</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.345991568440586</v>
+        <v>-7.497221028584648</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2123632985254313</v>
+        <v>0.1518715144678064</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.943597129534393</v>
+        <v>-1.035469443778334</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.584958072494778</v>
+        <v>2.529834683948413</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.305807270074395</v>
+        <v>-7.457036730218458</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2287806417597489</v>
+        <v>0.168288857702124</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9034128311682023</v>
+        <v>-0.9952851454121429</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.609412275402334</v>
+        <v>2.554288886855969</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.142407399135033</v>
+        <v>-7.293636859279095</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2935074113562508</v>
+        <v>0.2330156272986259</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7400129602288398</v>
+        <v>-0.8318852744727804</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.706819019186708</v>
+        <v>2.651695630640344</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.908926176905434</v>
+        <v>-7.060155637049497</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3948243290859428</v>
+        <v>0.3343325450283179</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5065317379992412</v>
+        <v>-0.5984040522431818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.854832181362319</v>
+        <v>2.799708792815955</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.759259785897919</v>
+        <v>-6.910489246041982</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4517986751759895</v>
+        <v>0.3913068911183646</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4136282467567053</v>
+        <v>-0.5055005610006459</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.907682065794882</v>
+        <v>2.852558677248517</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.626984312267033</v>
+        <v>-6.778213772411095</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.500076351375371</v>
+        <v>0.4395845673177461</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.2813527731258186</v>
+        <v>-0.3732250873697592</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.982414836720441</v>
+        <v>2.927291448174076</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.471245979707291</v>
+        <v>-6.622475439851353</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5651867450869048</v>
+        <v>0.5046949610292799</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1256144405660771</v>
+        <v>-0.2174867548100177</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.078672896943922</v>
+        <v>3.023549508397558</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.386281312977971</v>
+        <v>-6.537510773122033</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6120789530022912</v>
+        <v>0.5515871689446663</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.0406497738367575</v>
+        <v>-0.1325220880806981</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.142558038205173</v>
+        <v>3.087434649658809</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.491871302751075</v>
+        <v>-6.643100762895138</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.441867027493831</v>
+        <v>0.3813752434362061</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1462397636098619</v>
+        <v>-0.2381120778538025</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.951228114742092</v>
+        <v>2.896104726195727</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.423636718125648</v>
+        <v>-6.57486617826971</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5177052032210883</v>
+        <v>0.4572134191634634</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1278244407373259</v>
+        <v>-0.2196967549812665</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.0108216503427</v>
+        <v>2.955698261796335</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.275696676718049</v>
+        <v>-6.426926136862111</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4570022970959604</v>
+        <v>0.3965105130383355</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1075035248287683</v>
+        <v>-0.1993758390727089</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.903135277199667</v>
+        <v>2.848011888653302</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.22272715446406</v>
+        <v>-6.373956614608122</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4694761197440775</v>
+        <v>0.4089843356864526</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.05453400257477942</v>
+        <v>-0.14640631681872</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.926203004298582</v>
+        <v>2.871079615752217</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.056938958503769</v>
+        <v>-6.208168418647832</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.528830786033101</v>
+        <v>0.4683390019754761</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.05453400257477942</v>
+        <v>-0.14640631681872</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.919242392203488</v>
+        <v>2.864119003657124</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.023575752025001</v>
+        <v>-6.174805212169063</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5566384230057513</v>
+        <v>0.4961466389481264</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.05453400257477942</v>
+        <v>-0.14640631681872</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.933704746584632</v>
+        <v>2.878581358038267</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.915316614902479</v>
+        <v>-6.066546075046541</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.594474198313955</v>
+        <v>0.5339824142563301</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.05453400257477942</v>
+        <v>-0.14640631681872</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.928236867043827</v>
+        <v>2.873113478497462</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.792025480085348</v>
+        <v>-5.94325494022941</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6412887462513845</v>
+        <v>0.5807969621937596</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.06875713224235108</v>
+        <v>-0.02311518200158952</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.999709641944682</v>
+        <v>2.944586253398318</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.739328612954057</v>
+        <v>-5.890558073098119</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6700684713412262</v>
+        <v>0.6095766872836013</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1214539993736423</v>
+        <v>0.02958168512970166</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.039028740460782</v>
+        <v>2.983905351914417</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.495563170970613</v>
+        <v>-5.646792631114675</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7633553564816546</v>
+        <v>0.7028635724240297</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1214539993736423</v>
+        <v>0.02958168512970166</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.034809448807832</v>
+        <v>2.979686060261468</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.40578749859414</v>
+        <v>-5.557016958738203</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8013899393522594</v>
+        <v>0.7408981552946345</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1830534442879523</v>
+        <v>0.09118113004401168</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.073893429676434</v>
+        <v>3.01877004113007</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.155937104645066</v>
+        <v>-5.307166564789128</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8940721719155915</v>
+        <v>0.8335803878579666</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1830534442879523</v>
+        <v>0.09118113004401168</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.066635504660137</v>
+        <v>3.011512116113772</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.980045012177634</v>
+        <v>-5.131274472321696</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.968028132423213</v>
+        <v>0.9075363483655878</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1830534442879523</v>
+        <v>0.09118113004401168</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.070234628180785</v>
+        <v>3.015111239634421</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.80859854915517</v>
+        <v>-4.959828009299232</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.049934223686752</v>
+        <v>0.989442439629127</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3544999073104154</v>
+        <v>0.2626275930664748</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.186430012048817</v>
+        <v>3.131306623502452</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.728576262046049</v>
+        <v>-4.879805722190111</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.080963616146697</v>
+        <v>1.020471832089072</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4345221944195364</v>
+        <v>0.3426498801755958</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.233463861930586</v>
+        <v>3.178340473384222</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.664940519812115</v>
+        <v>-4.816169979956177</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.111112714094588</v>
+        <v>1.050620930036964</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.498157936653471</v>
+        <v>0.4062856224095303</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.276340108325265</v>
+        <v>3.2212167197789</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.553513760486195</v>
+        <v>-4.704743220630257</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.136877676608752</v>
+        <v>1.076385892551127</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.498157936653471</v>
+        <v>0.4062856224095303</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.25753436710906</v>
+        <v>3.202410978562696</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.564016383551484</v>
+        <v>-4.715245843695546</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.134419704007514</v>
+        <v>1.073927919949889</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4876553135881821</v>
+        <v>0.3957829993442414</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.252975869894764</v>
+        <v>3.1978524813484</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.491773815380289</v>
+        <v>-4.643003275524351</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.167246045110812</v>
+        <v>1.106754261053187</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4876553135881821</v>
+        <v>0.3957829993442414</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.256905183729584</v>
+        <v>3.20178179518322</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.474060128502424</v>
+        <v>-4.625289588646486</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.175010103779298</v>
+        <v>1.114518319721673</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.490836642485099</v>
+        <v>0.3989643282411582</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.259492564985075</v>
+        <v>3.20436917643871</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.365255243022697</v>
+        <v>-4.516484703166759</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.215530129191182</v>
+        <v>1.155038345133558</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.490836642485099</v>
+        <v>0.3989643282411582</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.256490636205068</v>
+        <v>3.201367247658704</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.145234444985686</v>
+        <v>-4.296463905129748</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.305117485416601</v>
+        <v>1.244625701358976</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6320564875530792</v>
+        <v>0.5401841733091385</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.34280158025647</v>
+        <v>3.287678191710106</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.012366755922408</v>
+        <v>-4.163596216066471</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.374158743843735</v>
+        <v>1.31366695978611</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6320564875530792</v>
+        <v>0.5401841733091385</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.358695763058293</v>
+        <v>3.303572374511929</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.89219367255791</v>
+        <v>-4.043423132701972</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.423373821629836</v>
+        <v>1.362882037572211</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7522295709175781</v>
+        <v>0.6603572566736374</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.431945457517295</v>
+        <v>3.37682206897093</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.756940311227932</v>
+        <v>-3.908169771371995</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.487563268723267</v>
+        <v>1.427071484665642</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8874829322475553</v>
+        <v>0.7956106180036145</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.523185576876721</v>
+        <v>3.468062188330356</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.816815138585625</v>
+        <v>-3.968044598729687</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.449650829181616</v>
+        <v>1.389159045123991</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8276081048898631</v>
+        <v>0.7357357906459224</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.473298171863531</v>
+        <v>3.418174783317167</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.696994907674787</v>
+        <v>-3.84822436781885</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.512868090780159</v>
+        <v>1.452376306722535</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8276081048898631</v>
+        <v>0.7357357906459224</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.48858734109774</v>
+        <v>3.433463952551376</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.699464614136593</v>
+        <v>-3.850694074280656</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.419524407517879</v>
+        <v>1.359032623460254</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8251383984280569</v>
+        <v>0.7332660841841163</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.394749716543098</v>
+        <v>3.339626327996733</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.767834800460603</v>
+        <v>-3.919064260604666</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.311438194473576</v>
+        <v>1.250946410415951</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8344140974642719</v>
+        <v>0.7425417832203313</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.319576997450128</v>
+        <v>3.264453608903764</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.78162285330765</v>
+        <v>-3.932852313451712</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.296359681966649</v>
+        <v>1.235867897909024</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8344140974642719</v>
+        <v>0.7425417832203313</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.310013706082019</v>
+        <v>3.254890317535655</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>2.804664929620302</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.837142929200239</v>
+        <v>-3.903844996783841</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.411182488301815</v>
+        <v>1.242770506593018</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8344140974642719</v>
+        <v>0.7425417832203313</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.447044542774222</v>
+        <v>3.250189999552501</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>2.80923216161209</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.66166866940777</v>
+        <v>-3.728370736991372</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.485939424210591</v>
+        <v>1.317527442501794</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8344140974642719</v>
+        <v>0.7425417832203313</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.451611774766009</v>
+        <v>3.254757231544289</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>2.784974190373297</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.772604922049019</v>
+        <v>-3.83930698963262</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.417306951915299</v>
+        <v>1.248894970206501</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8344140974642719</v>
+        <v>0.7425417832203313</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.427353803527216</v>
+        <v>3.230499260305496</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>2.713512503774747</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.738941376576737</v>
+        <v>-3.805643444160339</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.359310683505661</v>
+        <v>1.190898701796864</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8680776429365538</v>
+        <v>0.7762053286926132</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.376090244212036</v>
+        <v>3.179235700990314</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>2.723684890206879</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.679088757373014</v>
+        <v>-3.745790824956615</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.393424117619283</v>
+        <v>1.225012135910486</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8680776429365538</v>
+        <v>0.7762053286926132</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.386262630644168</v>
+        <v>3.189408087422447</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>2.718631160780739</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.592845294346636</v>
+        <v>-3.659547361930238</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.422867773403694</v>
+        <v>1.254455791694897</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8680776429365538</v>
+        <v>0.7762053286926132</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.381208901218028</v>
+        <v>3.184354357996307</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>2.710406936225265</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.638152113745616</v>
+        <v>-3.704854181329218</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.396520821088628</v>
+        <v>1.228108839379831</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.827267479927323</v>
+        <v>0.7353951656833824</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.348498578857015</v>
+        <v>3.151644035635294</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>2.710958809258366</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.667185218447918</v>
+        <v>-3.733887286031519</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.385459452240808</v>
+        <v>1.217047470532011</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.827267479927323</v>
+        <v>0.7353951656833824</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.349050451890117</v>
+        <v>3.152195908668396</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>2.640231501149732</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.574374736997059</v>
+        <v>-3.64107680458066</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.351856336712518</v>
+        <v>1.183444355003721</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9200779613781823</v>
+        <v>0.8282056471342417</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.334009432651998</v>
+        <v>3.137154889430277</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>2.642104977074333</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.618764206326486</v>
+        <v>-3.685466273910087</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.335974024905348</v>
+        <v>1.167562043196551</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8756884920487547</v>
+        <v>0.7838161778048141</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.309249226978943</v>
+        <v>3.112394683757222</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>2.637180685586056</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.735305811431829</v>
+        <v>-3.80200787901543</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.284433091374933</v>
+        <v>1.116021109666136</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7591468869434119</v>
+        <v>0.6672745726994713</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.23439997242746</v>
+        <v>3.037545429205739</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>2.642671981416723</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.775229906014401</v>
+        <v>-3.841931973598002</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.273954749372572</v>
+        <v>1.105542767663775</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7591468869434119</v>
+        <v>0.6672745726994713</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.239891268258127</v>
+        <v>3.043036725036406</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>2.654169183185262</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.803010303915754</v>
+        <v>-3.869712371499355</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.27433979198057</v>
+        <v>1.105927810271773</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7313664890420588</v>
+        <v>0.6394941747981182</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.234720231285854</v>
+        <v>3.037865688064133</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>2.492524903185915</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.921390976645892</v>
+        <v>-3.988093044229494</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.065343242889168</v>
+        <v>0.8969312611803706</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6641486368910826</v>
+        <v>0.572276322647142</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.032745239995922</v>
+        <v>2.835890696774201</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>2.612674563905121</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.030005055089223</v>
+        <v>-4.096707122672825</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.142047272231041</v>
+        <v>0.9736352905222436</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6641486368910826</v>
+        <v>0.572276322647142</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.152894900715127</v>
+        <v>2.956040357493406</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>2.627187590007444</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.99459601684108</v>
+        <v>-4.061298084424682</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.170723913632621</v>
+        <v>1.002311931923824</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6641486368910826</v>
+        <v>0.572276322647142</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.16740792681745</v>
+        <v>2.970553383595729</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>2.624607031349813</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.956212354282929</v>
+        <v>-4.056540871635747</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.18349681999825</v>
+        <v>1.001634258381767</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7025322994492338</v>
+        <v>0.5770335354360773</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.18785756569471</v>
+        <v>2.970827152611459</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>2.621336060195115</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.779096024247763</v>
+        <v>-3.879424541600581</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.251072380857619</v>
+        <v>1.069209819241135</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7025322994492338</v>
+        <v>0.5770335354360773</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.184586594540012</v>
+        <v>2.967556181456762</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>2.622019451957028</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.824188269081309</v>
+        <v>-3.924516786434126</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.233718874686113</v>
+        <v>1.05185631306963</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.640636256279844</v>
+        <v>0.5151374922666875</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.148132360400291</v>
+        <v>2.931101947317041</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>2.615806427263442</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.644812847842541</v>
+        <v>-3.745141365195359</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.299256018488035</v>
+        <v>1.117393456871552</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7974130144505627</v>
+        <v>0.6719142504374062</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.235985390609136</v>
+        <v>3.018954977525886</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>2.596613882595032</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.689827061363147</v>
+        <v>-3.790155578715965</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.262057788411382</v>
+        <v>1.080195226794899</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7670641191359581</v>
+        <v>0.6415653551228016</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.198583508751963</v>
+        <v>2.981553095668713</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>2.602305444933978</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.956831571635583</v>
+        <v>-4.0571600889884</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.160947546641354</v>
+        <v>0.9790849850248706</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5727010810930095</v>
+        <v>0.447202317079853</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.08765724826514</v>
+        <v>2.87062683518189</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>2.601509366830479</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.058029353072755</v>
+        <v>-4.158357870425573</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.119672355962986</v>
+        <v>0.9378097943465029</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5042922675476904</v>
+        <v>0.3787935035345338</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.04581588203445</v>
+        <v>2.8287854689512</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>2.599109328384796</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.051518386458443</v>
+        <v>-4.15184690381126</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.119876704163028</v>
+        <v>0.9380141425465447</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5042922675476904</v>
+        <v>0.3787935035345338</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.043415843588767</v>
+        <v>2.826385430505517</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>2.595634047593041</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.032480258751145</v>
+        <v>-4.132808776103963</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.124016674454192</v>
+        <v>0.9421541128377084</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4461086562164959</v>
+        <v>0.3206098922033392</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.005030395998295</v>
+        <v>2.787999982915045</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.856659603902588</v>
+        <v>2.714928449227231</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.084996061025966</v>
+        <v>-4.185324578378784</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.222304755178454</v>
+        <v>1.040442193561971</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4461086562164959</v>
+        <v>0.3206098922033392</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.124324797632485</v>
+        <v>2.907294384549235</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.857492932888721</v>
+        <v>2.715761778213365</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.098862822359884</v>
+        <v>-4.199191339712701</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.21759137963102</v>
+        <v>1.035728818014537</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4082507394826729</v>
+        <v>0.2827519754695163</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.102443376578325</v>
+        <v>2.885412963495075</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.863501463285647</v>
+        <v>2.721770308610291</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.054058650819954</v>
+        <v>-4.154387168172772</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.241521578643918</v>
+        <v>1.059659017027435</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4082507394826729</v>
+        <v>0.2827519754695163</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.108451906975251</v>
+        <v>2.891421493892001</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.761451684562847</v>
+        <v>2.61972052988749</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.906315680584952</v>
+        <v>-4.006644197937769</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.198568988015118</v>
+        <v>1.016706426398635</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5760580967175561</v>
+        <v>0.4505593327043995</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.107086542593381</v>
+        <v>2.89005612951013</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>2.622514151418971</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.99013690185965</v>
+        <v>-4.090465419212467</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.16783412103672</v>
+        <v>0.9859715594202372</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5760580967175561</v>
+        <v>0.4505593327043995</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.109880164124862</v>
+        <v>2.892849751041611</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.62317649981063</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.983984195806865</v>
+        <v>-4.084312713159683</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.170957551849492</v>
+        <v>0.9890949902330093</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5822108027703404</v>
+        <v>0.4567120387571837</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.11423413614819</v>
+        <v>2.89720372306494</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.62225697655074</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.000793493957367</v>
+        <v>-4.101122011310185</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.163314309329402</v>
+        <v>0.9814517477129188</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5654015046198388</v>
+        <v>0.4399027406066821</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.103229033998</v>
+        <v>2.88619862091475</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.688592530347561</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.938495495181245</v>
+        <v>-4.038824012534063</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.254569062636672</v>
+        <v>1.072706501020189</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6106957688942809</v>
+        <v>0.4851970048811242</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.196741146359486</v>
+        <v>2.979710733276236</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.490884532061688</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.736705297516087</v>
+        <v>-3.837033814868905</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.137577143416862</v>
+        <v>0.9557145818003787</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8087139610634353</v>
+        <v>0.6832151970502786</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.117844063375105</v>
+        <v>2.900813650291855</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.561174764383863</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.787592010202282</v>
+        <v>-3.887920527555099</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.187512690664559</v>
+        <v>1.005650129048076</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7578272483772408</v>
+        <v>0.632328484364084</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.157602268085564</v>
+        <v>2.940571855002314</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.575802500499907</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.700981267552475</v>
+        <v>-3.801309784905292</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.236784723840526</v>
+        <v>1.054922162224043</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8364529795823991</v>
+        <v>0.7109542155692422</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.219405442924702</v>
+        <v>3.002375029841452</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.574338481324578</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.761190565557759</v>
+        <v>-3.861519082910577</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.211236985463084</v>
+        <v>1.0293744238466</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7762436815771145</v>
+        <v>0.6507449175639577</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.181815844946204</v>
+        <v>2.964785431862953</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.572830099364507</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.684768519125833</v>
+        <v>-3.78509703647865</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.240297422075783</v>
+        <v>1.0584348604593</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7762436815771145</v>
+        <v>0.6507449175639577</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.180307462986132</v>
+        <v>2.963277049902882</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.572692966799943</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.640395387487264</v>
+        <v>-3.740723904840081</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.257909542166647</v>
+        <v>1.076046980550164</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8206168132156831</v>
+        <v>0.6951180492025263</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.206794209404709</v>
+        <v>2.989763796321459</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.567086760938534</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.662875738346149</v>
+        <v>-3.763204255698966</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.243311195961683</v>
+        <v>1.0614486343452</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8206168132156831</v>
+        <v>0.6951180492025263</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.2011880035433</v>
+        <v>2.98415759046005</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.573468517966338</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.615220007785093</v>
+        <v>-3.71554852513791</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.26875524521391</v>
+        <v>1.086892683597427</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8682725437767388</v>
+        <v>0.7427737797635819</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.236163198907738</v>
+        <v>3.019132785824488</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.578360891341063</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.514701849286338</v>
+        <v>-3.615030366639155</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.313854881988137</v>
+        <v>1.131992320371654</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9687907022754934</v>
+        <v>0.8432919382623365</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.301366467381715</v>
+        <v>3.084336054298465</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.565115563816935</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.498796519853986</v>
+        <v>-3.599125037206803</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.30697168623695</v>
+        <v>1.125109124620467</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8896780415662544</v>
+        <v>0.7641792775530976</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.240653543432044</v>
+        <v>3.023623130348794</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.569213266427564</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.453958118245588</v>
+        <v>-3.554286635598405</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.329004749490938</v>
+        <v>1.147142187874455</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8942214745111239</v>
+        <v>0.768722710497967</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.247477305809594</v>
+        <v>3.030446892726344</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.573374206058642</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.473456574487596</v>
+        <v>-3.573785091840413</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.325366306625213</v>
+        <v>1.14350374500873</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8461368332312196</v>
+        <v>0.7206380692180627</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.22278746067273</v>
+        <v>3.00575704758948</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.579253808586479</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.429253737401695</v>
+        <v>-3.529582254754513</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.34892704398741</v>
+        <v>1.167064482370927</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.89033967031712</v>
+        <v>0.7648409063039632</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.255188765452107</v>
+        <v>3.038158352368857</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.577663809055727</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.436813403238742</v>
+        <v>-3.53714192059156</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.344313178121839</v>
+        <v>1.162450616505356</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9451430743269393</v>
+        <v>0.8196443103137825</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.286480808327247</v>
+        <v>3.069450395243996</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.628911574238766</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.27852198569947</v>
+        <v>-3.378850503052287</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.458877510320587</v>
+        <v>1.277014948704104</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9451430743269393</v>
+        <v>0.8196443103137825</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.337728573510286</v>
+        <v>3.120698160427036</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.627352278833019</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.070879982064994</v>
+        <v>-3.171208499417811</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.540375016368631</v>
+        <v>1.358512454752148</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.152785077961415</v>
+        <v>1.027286313948259</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.460754480285225</v>
+        <v>3.243724067201975</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.622300507071289</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.019847889342466</v>
+        <v>-3.120176406695283</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.555736081695912</v>
+        <v>1.373873520079429</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.203817170683943</v>
+        <v>1.078318406670787</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.486321964157012</v>
+        <v>3.269291551073762</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.639487911163994</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.95462370821526</v>
+        <v>-3.054952225568077</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.5990131582395</v>
+        <v>1.417150596623016</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.269041351811149</v>
+        <v>1.143542587797992</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.54264387692604</v>
+        <v>3.32561346384279</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.635448883463275</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.917196688144126</v>
+        <v>-3.017525205496943</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.609944938567233</v>
+        <v>1.42808237695075</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.274292889840331</v>
+        <v>1.148794125827174</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.541755772042829</v>
+        <v>3.324725358959579</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.636705675794515</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.937308344178835</v>
+        <v>-3.037636861531652</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.60315706848459</v>
+        <v>1.421294506868107</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.28532023483775</v>
+        <v>1.159821470824593</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.549628971372521</v>
+        <v>3.332598558289271</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.797263446815726</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.88356352975163</v>
+        <v>-2.983892047104447</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.785212765276683</v>
+        <v>1.6033502036602</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.295383544278212</v>
+        <v>1.169884780265055</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.716224728058009</v>
+        <v>3.499194314974759</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>2.917376356033543</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.808781268726617</v>
+        <v>-2.909109786079434</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.935238578904505</v>
+        <v>1.753376017288022</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.370165805303225</v>
+        <v>1.244667041290068</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.881206993890834</v>
+        <v>3.664176580807584</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>2.909084332047402</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.782697184462809</v>
+        <v>-2.883025701815626</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.937380188623887</v>
+        <v>1.755517627007404</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.370165805303225</v>
+        <v>1.244667041290068</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.872914969904693</v>
+        <v>3.655884556821443</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>2.907277527631182</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.694819271353689</v>
+        <v>-2.795147788706506</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.970724549451315</v>
+        <v>1.788861987834832</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.486091447726576</v>
+        <v>1.360592683713419</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.940663550942483</v>
+        <v>3.723633137859233</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>2.924831933357973</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.685926809960405</v>
+        <v>-2.786255327313222</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.99183593973542</v>
+        <v>1.809973378118937</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.486091447726576</v>
+        <v>1.360592683713419</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.958217956669275</v>
+        <v>3.741187543586025</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>2.916686980762557</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.854402926930283</v>
+        <v>-2.9547314442831</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.916300540352053</v>
+        <v>1.734437978735569</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.458143612009995</v>
+        <v>1.332644847996838</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.933304302643911</v>
+        <v>3.71627388956066</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.897956677950419</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.408146734300843</v>
+        <v>-2.50847525165366</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.076072714591691</v>
+        <v>1.894210152975207</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.363424942340362</v>
+        <v>1.237926178327206</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.857742798029992</v>
+        <v>3.640712384946742</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.888620700447323</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.385425630617691</v>
+        <v>-2.485754147970508</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.075825178561856</v>
+        <v>1.893962616945373</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.363424942340362</v>
+        <v>1.237926178327206</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.848406820526897</v>
+        <v>3.631376407443647</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.047526826298492</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.514627443911733</v>
+        <v>-2.61495596126455</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.183050579095408</v>
+        <v>2.001188017478925</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.23422312904632</v>
+        <v>1.108724365033164</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.929791858401641</v>
+        <v>3.712761445318391</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.084604648792139</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.669408450689989</v>
+        <v>-2.769736968042806</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.158215998877752</v>
+        <v>1.976353437261269</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.200855454991844</v>
+        <v>1.075356690978687</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.946849076462602</v>
+        <v>3.729818663379351</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.081280004781684</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.662353760474815</v>
+        <v>-2.762682277827632</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.157713230953367</v>
+        <v>1.975850669336884</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.207910145207018</v>
+        <v>1.082411381193861</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.947757246581251</v>
+        <v>3.730726833498001</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.091286158426426</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.635402536148327</v>
+        <v>-2.735731053501144</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.178499874328704</v>
+        <v>1.99663731271222</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.222790491234737</v>
+        <v>1.09729172722158</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.966691607842624</v>
+        <v>3.749661194759374</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.275389290571385</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.771355544204643</v>
+        <v>-2.871684061557461</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.308221803251137</v>
+        <v>2.126359241634654</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.222790491234737</v>
+        <v>1.09729172722158</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.150794739987584</v>
+        <v>3.933764326904334</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.267505985474378</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.793763662009515</v>
+        <v>-2.894092179362333</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.291375251032181</v>
+        <v>2.109512689415698</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.222790491234737</v>
+        <v>1.09729172722158</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.142911434890577</v>
+        <v>3.925881021807327</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.269559985024016</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.821987897587116</v>
+        <v>-2.922316414939933</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.282139556350779</v>
+        <v>2.100276994734295</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.240767243686046</v>
+        <v>1.115268479672889</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.155751485911</v>
+        <v>3.938721072827749</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.325813702745863</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.831428823475646</v>
+        <v>-2.931757340828463</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.334616903717214</v>
+        <v>2.152754342100731</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.363194361229437</v>
+        <v>1.23769559721628</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.285461474158882</v>
+        <v>4.068431061075631</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.328704797291164</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.883702430811287</v>
+        <v>-2.984030948164104</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.316598555328258</v>
+        <v>2.134735993711775</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.310920753893796</v>
+        <v>1.185421989880639</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.256988404302797</v>
+        <v>4.039957991219548</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.326816610184939</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.960032408412193</v>
+        <v>-3.06036092576501</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.284178377181671</v>
+        <v>2.102315815565188</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.310920753893796</v>
+        <v>1.185421989880639</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.255100217196572</v>
+        <v>4.038069804113323</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.321636839787801</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.162286128736546</v>
+        <v>-3.262614646089363</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.198097118654792</v>
+        <v>2.016234557038309</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.108667033569442</v>
+        <v>0.9831682695562856</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.128568214604823</v>
+        <v>3.911537801521573</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.320070849997954</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.323854554263801</v>
+        <v>-3.424183071616619</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.131903758654042</v>
+        <v>1.950041197037559</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9818841097715628</v>
+        <v>0.8563853457584062</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.050932470536248</v>
+        <v>3.833902057452998</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.333144256863872</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.456155846361355</v>
+        <v>-3.556484363714172</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.09205664868094</v>
+        <v>1.910194087064456</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9818841097715628</v>
+        <v>0.8563853457584062</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.064005877402167</v>
+        <v>3.846975464318916</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.325149453646812</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.642024157200585</v>
+        <v>-3.742352674553402</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.009714521128187</v>
+        <v>1.827851959511704</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8233185164516151</v>
+        <v>0.6978197524384585</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.960871718193138</v>
+        <v>3.743841305109888</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.323673494773814</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.669924944310058</v>
+        <v>-3.770253461662875</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.9970782474114</v>
+        <v>1.815215685794917</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7887215923086803</v>
+        <v>0.6632228282955237</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.938637604834379</v>
+        <v>3.721607191751129</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.320437938751013</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.792451047012952</v>
+        <v>-3.892779564365769</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.944832250307441</v>
+        <v>1.762969688690958</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6661954896057865</v>
+        <v>0.5406967255926298</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.861886387189841</v>
+        <v>3.644855974106591</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.387143898341517</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.02296554319854</v>
+        <v>-4.123294060551357</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.91933241142371</v>
+        <v>1.737469849807227</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4356809934201977</v>
+        <v>0.3101822294070411</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.790283649068992</v>
+        <v>3.573253235985742</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.527455617343364</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.279686361193363</v>
+        <v>-4.380014878546181</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.956955803227627</v>
+        <v>1.775093241611144</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3272664192763829</v>
+        <v>0.2017676552632263</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.86554662358455</v>
+        <v>3.6485162105013</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.596435886489004</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.433672778969504</v>
+        <v>-4.534001296322321</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.964341505262811</v>
+        <v>1.782478943646328</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3272664192763829</v>
+        <v>0.2017676552632263</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.934526892730189</v>
+        <v>3.71749647964694</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.582487088609124</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.383150875141838</v>
+        <v>-4.483479392494655</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.970601468913998</v>
+        <v>1.788738907297515</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3272664192763829</v>
+        <v>0.2017676552632263</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.920578094850311</v>
+        <v>3.703547681767061</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.594357577664538</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.635626029149562</v>
+        <v>-4.73595454650238</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.881481896366322</v>
+        <v>1.699619334749839</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3272664192763829</v>
+        <v>0.2017676552632263</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.932448583905725</v>
+        <v>3.715418170822474</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.595568112183482</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.928521785628974</v>
+        <v>-5.028850302981792</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.765534128293501</v>
+        <v>1.583671566677018</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3272664192763829</v>
+        <v>0.2017676552632263</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.933659118424668</v>
+        <v>3.716628705341418</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.599689854410804</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.086065857358416</v>
+        <v>-5.186394374711234</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.706638241829046</v>
+        <v>1.524775680212563</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2603646141361084</v>
+        <v>0.1348658501229518</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897639777567825</v>
+        <v>3.680609364484575</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.594767707146993</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.364030252941689</v>
+        <v>-5.464358770294507</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.590530336331926</v>
+        <v>1.408667774715443</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1707448798506241</v>
+        <v>0.04524611583746752</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.838945789732724</v>
+        <v>3.621915376649474</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.756971763846037</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.48099794558058</v>
+        <v>-5.581326462933398</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.705947315975414</v>
+        <v>1.524084754358931</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1707448798506241</v>
+        <v>0.04524611583746752</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.001149846431768</v>
+        <v>3.784119433348518</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.751818401809851</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.565715887801534</v>
+        <v>-5.666044405154351</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.666906777050847</v>
+        <v>1.485044215434363</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08562885092257777</v>
+        <v>-0.03986991309057886</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.944926867038754</v>
+        <v>3.727896453955504</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.762047819378342</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.647650706070417</v>
+        <v>-5.747979223423235</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.644362267311784</v>
+        <v>1.462499705695302</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07569410533549759</v>
+        <v>-0.04980465867765904</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.949195437254997</v>
+        <v>3.732165024171747</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.770973457834245</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.749626828318824</v>
+        <v>-5.849955345671642</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.612497456868324</v>
+        <v>1.430634895251841</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.02628201691290999</v>
+        <v>-0.1517807809260666</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.896935402361855</v>
+        <v>3.679904989278605</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.76312634507842</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.639620544841603</v>
+        <v>-5.73994906219442</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.648652857503388</v>
+        <v>1.466790295886905</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.003077444995634782</v>
+        <v>-0.1285762090087914</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.903011032756396</v>
+        <v>3.685980619673145</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.767376355800395</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.496560969100678</v>
+        <v>-5.596889486453495</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.710126698521732</v>
+        <v>1.528264136905249</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.004935981594344496</v>
+        <v>-0.1205627824188121</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.912069099432357</v>
+        <v>3.695038686349108</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.774637238682931</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.19511424362884</v>
+        <v>-5.295442760981658</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.837966271593003</v>
+        <v>1.65610370997652</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3063827070661818</v>
+        <v>0.1808839430530251</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.100198017597996</v>
+        <v>3.883167604514746</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.775608416435641</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.219704487864024</v>
+        <v>-5.320033005216842</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.82910135165164</v>
+        <v>1.647238790035157</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3063827070661818</v>
+        <v>0.1808839430530251</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.101169195350707</v>
+        <v>3.884138782267457</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.776451320815397</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.168666111857504</v>
+        <v>-5.268994629210321</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.850359606434004</v>
+        <v>1.668497044817521</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3063827070661818</v>
+        <v>0.1808839430530251</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.102012099730461</v>
+        <v>3.884981686647212</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.795489419689542</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.127526816990873</v>
+        <v>-5.22785533434369</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.885853423254801</v>
+        <v>1.703990861638319</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3475220019328126</v>
+        <v>0.2220232379196559</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.145733775524586</v>
+        <v>3.928703362441336</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.611673415813477</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.016920676911271</v>
+        <v>-5.117249194264089</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.746279875410577</v>
+        <v>1.564417313794094</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4581281420124146</v>
+        <v>0.332629377999258</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.028281455696281</v>
+        <v>3.811251042613032</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.615175459887441</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.147501411442113</v>
+        <v>-5.247829928794931</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.697549625672203</v>
+        <v>1.515687064055721</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3275474074815721</v>
+        <v>0.2020486434684154</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.953435059051739</v>
+        <v>3.736404645968491</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.599602278963523</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.983005077251152</v>
+        <v>-5.083333594603969</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.747774978424671</v>
+        <v>1.565912416808188</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3275474074815721</v>
+        <v>0.2020486434684154</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.937861878127822</v>
+        <v>3.720831465044573</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.598789989399953</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.010375009935584</v>
+        <v>-5.110703527288401</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.736014715787328</v>
+        <v>1.554152154170845</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3275474074815721</v>
+        <v>0.2020486434684154</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.937049588564252</v>
+        <v>3.720019175481003</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.608658768525026</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.020760204825473</v>
+        <v>-5.121088722178291</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.741729416956444</v>
+        <v>1.559866855339962</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3171622125916828</v>
+        <v>0.1916634485785261</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.94068725075539</v>
+        <v>3.723656837672142</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.679495774301451</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.039348363547698</v>
+        <v>-5.139676880900516</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.80513115924398</v>
+        <v>1.623268597627497</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2985740538694574</v>
+        <v>0.1730752898563008</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.00037136129848</v>
+        <v>3.783340948215232</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.676364785119749</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.039646910243734</v>
+        <v>-5.139975427596552</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.801880751383864</v>
+        <v>1.620018189767381</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2985740538694574</v>
+        <v>0.1730752898563008</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.997240372116779</v>
+        <v>3.78020995903353</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.680895680059141</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.938823776553306</v>
+        <v>-5.039152293906124</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.846740899799426</v>
+        <v>1.664878338182944</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3110382693538112</v>
+        <v>0.1855395053406546</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.009249796346783</v>
+        <v>3.792219383263534</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.681024933537684</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.748042415800899</v>
+        <v>-4.848370933153717</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.923182697578932</v>
+        <v>1.74132013596245</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5018196301062186</v>
+        <v>0.376320866093062</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.123847866276771</v>
+        <v>3.906817453193521</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.66086177927528</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.729525561759079</v>
+        <v>-4.829854079111897</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.910426284933257</v>
+        <v>1.728563723316775</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5147497595314268</v>
+        <v>0.3892509955182702</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.111442789669492</v>
+        <v>3.894412376586243</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.695828715887339</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.704332377257761</v>
+        <v>-4.804660894610579</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.955470495345843</v>
+        <v>1.77360793372936</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5399429440327451</v>
+        <v>0.4144441800195885</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.161525636982342</v>
+        <v>3.944495223899092</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.689515283788777</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.692278250344798</v>
+        <v>-4.792606767697616</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.953978714012465</v>
+        <v>1.772116152395983</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5519970709457079</v>
+        <v>0.4264983069325514</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.162444681031557</v>
+        <v>3.945414267948308</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.691395913972912</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.698901497035156</v>
+        <v>-4.799230014387974</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.953210045520458</v>
+        <v>1.771347483903976</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5453738242553496</v>
+        <v>0.419875060242193</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.160351363201478</v>
+        <v>3.943320950118228</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.704246939850795</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.596020907506563</v>
+        <v>-4.696349424859381</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.007213307209778</v>
+        <v>1.825350745593295</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6482544137839426</v>
+        <v>0.5227556497707859</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.234930742796516</v>
+        <v>4.017900329713266</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.724449610024389</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.61946294668665</v>
+        <v>-4.719791464039468</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.018039161711337</v>
+        <v>1.836176600094855</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6482544137839426</v>
+        <v>0.5227556497707859</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.25513341297011</v>
+        <v>4.038102999886861</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.724449610024389</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.637535454978262</v>
+        <v>-4.73786397233108</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.010810158394692</v>
+        <v>1.82894759677821</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6482544137839426</v>
+        <v>0.5227556497707859</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.25513341297011</v>
+        <v>4.038102999886861</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.684701523617856</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.868709248854894</v>
+        <v>-4.969037766207712</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.878592554437506</v>
+        <v>1.696729992821024</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6482544137839426</v>
+        <v>0.5227556497707859</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.215385326563577</v>
+        <v>3.998354913480328</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.691724142614796</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.837423228314439</v>
+        <v>-4.937751745667256</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.898129581650628</v>
+        <v>1.716267020034146</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6795404343243979</v>
+        <v>0.5540416703112413</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.24117955788479</v>
+        <v>4.024149144801541</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.7908951421877</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.684397836201154</v>
+        <v>-4.784726353553972</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.058510738068846</v>
+        <v>1.876648176452364</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8325658264376821</v>
+        <v>0.7070670624245254</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.432165792725664</v>
+        <v>4.215135379642415</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>3.978361367095992</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.712705150074425</v>
+        <v>-4.813033667427242</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.234654037427831</v>
+        <v>2.052791475811348</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8325658264376821</v>
+        <v>0.7070670624245254</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.619632017633957</v>
+        <v>4.402601604550708</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>3.947764318450075</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.879298375187947</v>
+        <v>-4.979626892540765</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.137419698736504</v>
+        <v>1.955557137120022</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6659726013241596</v>
+        <v>0.540473837311003</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.489079033919926</v>
+        <v>4.272048620836677</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.093171875787148</v>
+        <v>3.951440721111792</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.706233995805647</v>
+        <v>-4.876620771807296</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.210321853151141</v>
+        <v>2.000435988075127</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6659726013241596</v>
+        <v>0.540473837311003</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.492755436581644</v>
+        <v>4.275725023498395</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.773277399690336</v>
+        <v>3.842518422725566</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.124485843052149</v>
+        <v>4.080135432225489</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.706233995805647</v>
+        <v>-4.936253652735314</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.210321853151141</v>
+        <v>2.105277546817616</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6659726013241596</v>
+        <v>0.5335510266498745</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.117549640038517</v>
+        <v>4.400266048215413</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240813.xlsx
+++ b/tame_output/ON/bt/strategyON_20240813.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-599.7%</t>
+          <t>-597.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.2%</t>
+          <t>430.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-655.2%</t>
+          <t>-643.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-240.3%</t>
+          <t>-239.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.7%</t>
+          <t>-159.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-235.6%</t>
+          <t>-228.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-390.7%</t>
+          <t>-296.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-170.6%</t>
+          <t>-154.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-141.8%</t>
+          <t>-137.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.381278462700433</v>
+        <v>-4.356838656388226</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.359488499638954</v>
+        <v>1.369264422163837</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.1164396263032174</v>
+        <v>-0.04760358204652515</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.042492533250944</v>
+        <v>3.08379415980496</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.716941109930885</v>
+        <v>-4.692501303618679</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.223804032402738</v>
+        <v>1.233579954927621</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.1843706117921222</v>
+        <v>-0.11553456753543</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.000314533613567</v>
+        <v>3.041616160167582</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.793385440133757</v>
+        <v>-4.76894563382155</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.199713860555831</v>
+        <v>1.209489783080714</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.1039251026984603</v>
+        <v>-0.03508905844176807</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.055069399304005</v>
+        <v>3.096371025858021</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.158512822772503</v>
+        <v>-5.134073016460297</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.052917422506164</v>
+        <v>1.062693345031047</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4002358869974728</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.876537443730429</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.567101599953181</v>
+        <v>-5.542661793640976</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8882434556486518</v>
+        <v>0.8980193781735339</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8088246641781512</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.630145721436781</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.680862011976046</v>
+        <v>-5.656422205663841</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8379247233109663</v>
+        <v>0.8477006458358489</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8088246641781512</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.625331153908242</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.097253886263044</v>
+        <v>-6.072814079950838</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6693620242050446</v>
+        <v>0.6791379467299272</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8088246641781512</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.623325204517119</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.458427516080032</v>
+        <v>-6.433987709767826</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5351512629469286</v>
+        <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8088246641781512</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.633583895185798</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.80168603572305</v>
+        <v>-6.777246229410845</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3939474202354165</v>
+        <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8088246641781512</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.629683460331493</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.849888852965394</v>
+        <v>-6.825449046653189</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3730712133934797</v>
+        <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8088246641781512</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.628088380386494</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.146550194775592</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.258185652598609</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8775677999120298</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.590621474875375</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.333269903084894</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1794714647404847</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8775677999120298</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.586595170340972</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.716271291827526</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.02616880792184828</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8775677999120298</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.586493069019388</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.720757737028914</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.02694574581272269</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8820542451134186</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.586372717869985</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.080288059532917</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1115160798908281</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8820542451134186</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.591723021168035</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.130637122987139</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1237396853153392</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9324033085676406</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.569429603052679</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.228256400408535</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1597456456621287</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.030022585989037</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.51389978722161</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.282327899916893</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1784806891439001</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.084094085497397</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.484350443838167</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.486586075246757</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2546707621572031</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.211733030111386</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.413280274188416</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.520238913755231</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2636493430761564</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.312146398028423</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.357514807922629</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.446769082087782</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2188897089157558</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.238676566360974</v>
+        <v>-1.169840522104282</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.41696840841652</v>
+        <v>2.458270034970535</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.621893499474325</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2743842551228566</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.413800983747518</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.326448978732111</v>
+        <v>2.367750605286126</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.856345593488815</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3753842576302482</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.413800983747518</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.319229813830514</v>
+        <v>2.36053144038453</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.960720324515261</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.423806340814803</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.518175714773964</v>
+        <v>-1.449339670517272</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.249932784440671</v>
+        <v>2.291234410994686</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.123233790213845</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4876959372556806</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.615809145192651</v>
+        <v>-1.546973100935959</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.192468516028015</v>
+        <v>2.23377014258203</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.249270583582135</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5354169259738817</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.590557522382908</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.210313218342975</v>
+        <v>2.25161484489699</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.192198811686204</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5085978815291083</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.590557522382908</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.214303554029376</v>
+        <v>2.255605180583391</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.333870653410324</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5667418451174981</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.590557522382908</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.212828327130634</v>
+        <v>2.254129953684649</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.28427980898549</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5318520971826923</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.540966677958075</v>
+        <v>-1.472130633701382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.257636243950407</v>
+        <v>2.298937870504422</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.135361474513633</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4853358970406325</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.509717087222902</v>
+        <v>-1.440881042966209</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.263334864744828</v>
+        <v>2.304636491298843</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.909516321794221</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3854187629166592</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.467790411635738</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.298069943133334</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.78493766545663</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3344481558255636</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.467790411635738</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.299209087689393</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.837832953500916</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3529724968811703</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.462835065547292</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.304816069504569</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.765699778213035</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3183855225273815</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.462835065547292</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.310549773743205</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.694333385603388</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2995762278773877</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.391468672937644</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.343632346915129</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.600874351618163</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2720760955962054</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.391468672937644</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.333748865602221</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.590221170064732</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2696493834742069</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.391468672937644</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.331914305102847</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.492314131388241</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2307868829770712</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.323482923077087</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37240544004572</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.468360590412283</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2205369604411946</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.29952938210113</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.387446070776789</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.204300652089486</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.128173301273828</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.035469443778334</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.532621717608714</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.497221028584648</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1518715144678064</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.035469443778334</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.529834683948413</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.457036730218458</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.168288857702124</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9952851454121429</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.554288886855969</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.293636859279095</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2330156272986259</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8318852744727804</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.651695630640344</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.060155637049497</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3343325450283179</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5984040522431818</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.799708792815955</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.910489246041982</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3913068911183646</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5055005610006459</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.852558677248517</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.778213772411095</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4395845673177461</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3732250873697592</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.927291448174076</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.622475439851353</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5046949610292799</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2174867548100177</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.023549508397558</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.537510773122033</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5515871689446663</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1325220880806981</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.087434649658809</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.643100762895138</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3813752434362061</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2381120778538025</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.896104726195727</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.57486617826971</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4572134191634634</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2196967549812665</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.955698261796335</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.426926136862111</v>
+        <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3965105130383355</v>
+        <v>0.4062864355632176</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1993758390727089</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.848011888653302</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.373956614608122</v>
+        <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4089843356864526</v>
+        <v>0.4187602582113348</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.14640631681872</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.871079615752217</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.208168418647832</v>
+        <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4683390019754761</v>
+        <v>0.4781149245003582</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.14640631681872</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.864119003657124</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.174805212169063</v>
+        <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4961466389481264</v>
+        <v>0.5059225614730085</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.14640631681872</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.878581358038267</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.066546075046541</v>
+        <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5339824142563301</v>
+        <v>0.5437583367812122</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.14640631681872</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.873113478497462</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.94325494022941</v>
+        <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5807969621937596</v>
+        <v>0.5905728847186418</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.02311518200158952</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.944586253398318</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.890558073098119</v>
+        <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6095766872836013</v>
+        <v>0.6193526098084834</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.02958168512970166</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.983905351914417</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.646792631114675</v>
+        <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7028635724240297</v>
+        <v>0.7126394949489119</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.02958168512970166</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.979686060261468</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.557016958738203</v>
+        <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7408981552946345</v>
+        <v>0.7506740778195167</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.09118113004401168</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.01877004113007</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.307166564789128</v>
+        <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8335803878579666</v>
+        <v>0.8433563103828488</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.09118113004401168</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.011512116113772</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.131274472321696</v>
+        <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9075363483655878</v>
+        <v>0.9173122708904704</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.09118113004401168</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.015111239634421</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.959828009299232</v>
+        <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.989442439629127</v>
+        <v>0.9992183621540094</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2626275930664748</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.131306623502452</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.879805722190111</v>
+        <v>-4.855365915877906</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.020471832089072</v>
+        <v>1.030247754613955</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3426498801755958</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.178340473384222</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.816169979956177</v>
+        <v>-4.791730173643971</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.050620930036964</v>
+        <v>1.060396852561846</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4062856224095303</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.2212167197789</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.704743220630257</v>
+        <v>-4.680303414318051</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.076385892551127</v>
+        <v>1.08616181507601</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4062856224095303</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.202410978562696</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.715245843695546</v>
+        <v>-4.69080603738334</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.073927919949889</v>
+        <v>1.083703842474771</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3957829993442414</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.1978524813484</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.643003275524351</v>
+        <v>-4.618563469212146</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.106754261053187</v>
+        <v>1.116530183578069</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3957829993442414</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.20178179518322</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.625289588646486</v>
+        <v>-4.60084978233428</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.114518319721673</v>
+        <v>1.124294242246555</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3989643282411582</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.20436917643871</v>
+        <v>3.245670802992725</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.516484703166759</v>
+        <v>-4.492044896854553</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.155038345133558</v>
+        <v>1.16481426765844</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3989643282411582</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.201367247658704</v>
+        <v>3.242668874212719</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.296463905129748</v>
+        <v>-4.272024098817543</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.244625701358976</v>
+        <v>1.254401623883858</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5401841733091385</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.287678191710106</v>
+        <v>3.328979818264121</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.163596216066471</v>
+        <v>-4.139156409754265</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.31366695978611</v>
+        <v>1.323442882310992</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5401841733091385</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.303572374511929</v>
+        <v>3.344874001065945</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.043423132701972</v>
+        <v>-4.018983326389766</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.362882037572211</v>
+        <v>1.372657960097094</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6603572566736374</v>
+        <v>0.7291933009303296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.37682206897093</v>
+        <v>3.418123695524946</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.908169771371995</v>
+        <v>-3.883729965059789</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.427071484665642</v>
+        <v>1.436847407190525</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7956106180036145</v>
+        <v>0.8644466622603068</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.468062188330356</v>
+        <v>3.509363814884372</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.968044598729687</v>
+        <v>-3.943604792417482</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.389159045123991</v>
+        <v>1.398934967648873</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7357357906459224</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.418174783317167</v>
+        <v>3.459476409871182</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.84822436781885</v>
+        <v>-3.823784561506644</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.452376306722535</v>
+        <v>1.462152229247417</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7357357906459224</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.433463952551376</v>
+        <v>3.474765579105391</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.850694074280656</v>
+        <v>-3.82625426796845</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.359032623460254</v>
+        <v>1.368808545985136</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7332660841841163</v>
+        <v>0.8021021284408085</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.339626327996733</v>
+        <v>3.380927954550749</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.919064260604666</v>
+        <v>-3.89462445429246</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.250946410415951</v>
+        <v>1.260722332940833</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7425417832203313</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.264453608903764</v>
+        <v>3.305755235457779</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.932852313451712</v>
+        <v>-3.908412507139507</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.235867897909024</v>
+        <v>1.245643820433906</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7425417832203313</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.254890317535655</v>
+        <v>3.29619194408967</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.804664929620302</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.903844996783841</v>
+        <v>-3.963932583032096</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.242770506593018</v>
+        <v>1.360466626769073</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7425417832203313</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.250189999552501</v>
+        <v>3.433222780781873</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.80923216161209</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.728370736991372</v>
+        <v>-3.788458323239627</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.317527442501794</v>
+        <v>1.435223562677848</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7425417832203313</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.254757231544289</v>
+        <v>3.43779001277366</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.784974190373297</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.83930698963262</v>
+        <v>-3.899394575880875</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.248894970206501</v>
+        <v>1.366591090382556</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7425417832203313</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.230499260305496</v>
+        <v>3.413532041534868</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.713512503774747</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.805643444160339</v>
+        <v>-3.865731030408594</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.190898701796864</v>
+        <v>1.308594821972918</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7762053286926132</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.179235700990314</v>
+        <v>3.362268482219687</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.723684890206879</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.745790824956615</v>
+        <v>-3.80587841120487</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.225012135910486</v>
+        <v>1.34270825608654</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7762053286926132</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.189408087422447</v>
+        <v>3.372440868651819</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.718631160780739</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.659547361930238</v>
+        <v>-3.719634948178493</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.254455791694897</v>
+        <v>1.372151911870951</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7762053286926132</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.184354357996307</v>
+        <v>3.367387139225679</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.710406936225265</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.704854181329218</v>
+        <v>-3.764941767577473</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.228108839379831</v>
+        <v>1.345804959555885</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7353951656833824</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.151644035635294</v>
+        <v>3.334676816864667</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.710958809258366</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.733887286031519</v>
+        <v>-3.793974872279775</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.217047470532011</v>
+        <v>1.334743590708066</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7353951656833824</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.152195908668396</v>
+        <v>3.335228689897768</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.640231501149732</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.64107680458066</v>
+        <v>-3.701164390828915</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.183444355003721</v>
+        <v>1.301140475179775</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8282056471342417</v>
+        <v>0.8970416913909339</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.137154889430277</v>
+        <v>3.320187670659649</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.642104977074333</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.685466273910087</v>
+        <v>-3.745553860158343</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.167562043196551</v>
+        <v>1.285258163372605</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7838161778048141</v>
+        <v>0.8526522220615063</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.112394683757222</v>
+        <v>3.295427464986593</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.637180685586056</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.80200787901543</v>
+        <v>-3.862095465263686</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.116021109666136</v>
+        <v>1.233717229842191</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6672745726994713</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.037545429205739</v>
+        <v>3.220578210435111</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.642671981416723</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.841931973598002</v>
+        <v>-3.902019559846257</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.105542767663775</v>
+        <v>1.223238887839829</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6672745726994713</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.043036725036406</v>
+        <v>3.226069506265778</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.654169183185262</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.869712371499355</v>
+        <v>-3.929799957747611</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.105927810271773</v>
+        <v>1.223623930447827</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6394941747981182</v>
+        <v>0.7083302190548104</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.037865688064133</v>
+        <v>3.220898469293505</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.492524903185915</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.988093044229494</v>
+        <v>-4.048180630477749</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8969312611803706</v>
+        <v>1.014627381356425</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.572276322647142</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.835890696774201</v>
+        <v>3.018923478003573</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.612674563905121</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.096707122672825</v>
+        <v>-4.15679470892108</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9736352905222436</v>
+        <v>1.091331410698298</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.572276322647142</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.956040357493406</v>
+        <v>3.139073138722778</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.627187590007444</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.061298084424682</v>
+        <v>-4.121385670672937</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.002311931923824</v>
+        <v>1.120008052099879</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.572276322647142</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.970553383595729</v>
+        <v>3.153586164825101</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.624607031349813</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.056540871635747</v>
+        <v>-4.083002008114786</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.001634258381767</v>
+        <v>1.132780958465508</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5770335354360773</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.970827152611459</v>
+        <v>3.174035803702361</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.621336060195115</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.879424541600581</v>
+        <v>-3.90588567807962</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.069209819241135</v>
+        <v>1.200356519324876</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5770335354360773</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.967556181456762</v>
+        <v>3.170764832547663</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.622019451957028</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.924516786434126</v>
+        <v>-3.950977922913165</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.05185631306963</v>
+        <v>1.183003013153371</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5151374922666875</v>
+        <v>0.6175999862925956</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.931101947317041</v>
+        <v>3.134310598407942</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.615806427263442</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.745141365195359</v>
+        <v>-3.771602501674398</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.117393456871552</v>
+        <v>1.248540156955292</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6719142504374062</v>
+        <v>0.7743767444633143</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.018954977525886</v>
+        <v>3.222163628616787</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.596613882595032</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.790155578715965</v>
+        <v>-3.816616715195004</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.080195226794899</v>
+        <v>1.21134192687864</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6415653551228016</v>
+        <v>0.7440278491487097</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.981553095668713</v>
+        <v>3.184761746759615</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.602305444933978</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.0571600889884</v>
+        <v>-4.083621225467439</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9790849850248706</v>
+        <v>1.110231685108611</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.447202317079853</v>
+        <v>0.5496648111057612</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.87062683518189</v>
+        <v>3.073835486272791</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.601509366830479</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.158357870425573</v>
+        <v>-4.184819006904612</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9378097943465029</v>
+        <v>1.068956494430243</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3787935035345338</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.8287854689512</v>
+        <v>3.031994120042101</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.599109328384796</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.15184690381126</v>
+        <v>-4.178308040290299</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9380141425465447</v>
+        <v>1.069160842630285</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3787935035345338</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.826385430505517</v>
+        <v>3.029594081596418</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.595634047593041</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.132808776103963</v>
+        <v>-4.159269912583002</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9421541128377084</v>
+        <v>1.073300812921449</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3206098922033392</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.787999982915045</v>
+        <v>2.991208634005946</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.714928449227231</v>
+        <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.185324578378784</v>
+        <v>-4.211785714857823</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.040442193561971</v>
+        <v>1.171588893645711</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3206098922033392</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.907294384549235</v>
+        <v>3.110503035640136</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.715761778213365</v>
+        <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.199191339712701</v>
+        <v>-4.22565247619174</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.035728818014537</v>
+        <v>1.166875518098278</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2827519754695163</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.885412963495075</v>
+        <v>3.088621614585976</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.721770308610291</v>
+        <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.154387168172772</v>
+        <v>-4.180848304651811</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.059659017027435</v>
+        <v>1.190805717111175</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2827519754695163</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.891421493892001</v>
+        <v>3.094630144982902</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.61972052988749</v>
+        <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.006644197937769</v>
+        <v>-4.033105334416808</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.016706426398635</v>
+        <v>1.147853126482376</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4505593327043995</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.89005612951013</v>
+        <v>3.093264780601031</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.622514151418971</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.090465419212467</v>
+        <v>-4.116926555691506</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9859715594202372</v>
+        <v>1.117118259503978</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4505593327043995</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.892849751041611</v>
+        <v>3.096058402132512</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.62317649981063</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.084312713159683</v>
+        <v>-4.110773849638722</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9890949902330093</v>
+        <v>1.12024169031675</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4567120387571837</v>
+        <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.89720372306494</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.62225697655074</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.101122011310185</v>
+        <v>-4.127583147789224</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9814517477129188</v>
+        <v>1.112598447796659</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4399027406066821</v>
+        <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.88619862091475</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.688592530347561</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.038824012534063</v>
+        <v>-4.065285149013102</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.072706501020189</v>
+        <v>1.203853201103929</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4851970048811242</v>
+        <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.979710733276236</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.490884532061688</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.837033814868905</v>
+        <v>-3.863494951347944</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9557145818003787</v>
+        <v>1.086861281884119</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6832151970502786</v>
+        <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.900813650291855</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.561174764383863</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.887920527555099</v>
+        <v>-3.914381664034138</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.005650129048076</v>
+        <v>1.136796829131817</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.632328484364084</v>
+        <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.940571855002314</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.575802500499907</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.801309784905292</v>
+        <v>-3.827770921384331</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.054922162224043</v>
+        <v>1.186068862307783</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7109542155692422</v>
+        <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.002375029841452</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.574338481324578</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.861519082910577</v>
+        <v>-3.887980219389616</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.0293744238466</v>
+        <v>1.160521123930341</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6507449175639577</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.964785431862953</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.572830099364507</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.78509703647865</v>
+        <v>-3.811558172957689</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.0584348604593</v>
+        <v>1.18958156054304</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6507449175639577</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.963277049902882</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.572692966799943</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.740723904840081</v>
+        <v>-3.76718504131912</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.076046980550164</v>
+        <v>1.207193680633904</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6951180492025263</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.989763796321459</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.567086760938534</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.763204255698966</v>
+        <v>-3.789665392178005</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.0614486343452</v>
+        <v>1.192595334428941</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6951180492025263</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.98415759046005</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.573468517966338</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.71554852513791</v>
+        <v>-3.742009661616949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.086892683597427</v>
+        <v>1.218039383681168</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7427737797635819</v>
+        <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.019132785824488</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.578360891341063</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.615030366639155</v>
+        <v>-3.641491503118194</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.131992320371654</v>
+        <v>1.263139020455394</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8432919382623365</v>
+        <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.084336054298465</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.565115563816935</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.599125037206803</v>
+        <v>-3.625586173685842</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.125109124620467</v>
+        <v>1.256255824704207</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7641792775530976</v>
+        <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.023623130348794</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.569213266427564</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.554286635598405</v>
+        <v>-3.580747772077444</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.147142187874455</v>
+        <v>1.278288887958195</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.768722710497967</v>
+        <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.030446892726344</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.573374206058642</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.573785091840413</v>
+        <v>-3.600246228319452</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.14350374500873</v>
+        <v>1.27465044509247</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7206380692180627</v>
+        <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.00575704758948</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.579253808586479</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.529582254754513</v>
+        <v>-3.556043391233552</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.167064482370927</v>
+        <v>1.298211182454667</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7648409063039632</v>
+        <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.038158352368857</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.577663809055727</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.53714192059156</v>
+        <v>-3.563603057070599</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.162450616505356</v>
+        <v>1.293597316589096</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8196443103137825</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.069450395243996</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.628911574238766</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.378850503052287</v>
+        <v>-3.405311639531326</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.277014948704104</v>
+        <v>1.408161648787845</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8196443103137825</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.120698160427036</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.627352278833019</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.171208499417811</v>
+        <v>-3.19766963589685</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.358512454752148</v>
+        <v>1.489659154835888</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.027286313948259</v>
+        <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.243724067201975</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.622300507071289</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.120176406695283</v>
+        <v>-3.146637543174322</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.373873520079429</v>
+        <v>1.505020220163169</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.078318406670787</v>
+        <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.269291551073762</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.639487911163994</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.054952225568077</v>
+        <v>-3.081413362047116</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.417150596623016</v>
+        <v>1.548297296706757</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.143542587797992</v>
+        <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.32561346384279</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.635448883463275</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.017525205496943</v>
+        <v>-3.043986341975983</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.42808237695075</v>
+        <v>1.559229077034491</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.148794125827174</v>
+        <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.324725358959579</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.636705675794515</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.037636861531652</v>
+        <v>-3.064097998010691</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.421294506868107</v>
+        <v>1.552441206951848</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.159821470824593</v>
+        <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.332598558289271</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.797263446815726</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.983892047104447</v>
+        <v>-3.010353183583486</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.6033502036602</v>
+        <v>1.73449690374394</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.169884780265055</v>
+        <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.499194314974759</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.917376356033543</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.909109786079434</v>
+        <v>-2.935570922558473</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.753376017288022</v>
+        <v>1.884522717371763</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.244667041290068</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.664176580807584</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.909084332047402</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.883025701815626</v>
+        <v>-2.909486838294665</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.755517627007404</v>
+        <v>1.886664327091145</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.244667041290068</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.655884556821443</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.907277527631182</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.795147788706506</v>
+        <v>-2.821608925185545</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.788861987834832</v>
+        <v>1.920008687918572</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360592683713419</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.723633137859233</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.924831933357973</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.786255327313222</v>
+        <v>-2.812716463792261</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.809973378118937</v>
+        <v>1.941120078202677</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360592683713419</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.741187543586025</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.916686980762557</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.9547314442831</v>
+        <v>-2.981192580762139</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.734437978735569</v>
+        <v>1.86558467881931</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332644847996838</v>
+        <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.71627388956066</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.897956677950419</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.50847525165366</v>
+        <v>-2.534936388132699</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.894210152975207</v>
+        <v>2.025356853058948</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.237926178327206</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.640712384946742</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.888620700447323</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.485754147970508</v>
+        <v>-2.512215284449547</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.893962616945373</v>
+        <v>2.025109317029114</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.237926178327206</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.631376407443647</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.047526826298492</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.61495596126455</v>
+        <v>-2.641417097743589</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.001188017478925</v>
+        <v>2.132334717562665</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.108724365033164</v>
+        <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.712761445318391</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.084604648792139</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.769736968042806</v>
+        <v>-2.796198104521845</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.976353437261269</v>
+        <v>2.10750013734501</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.075356690978687</v>
+        <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.729818663379351</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.081280004781684</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.762682277827632</v>
+        <v>-2.789143414306671</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.975850669336884</v>
+        <v>2.106997369420625</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.082411381193861</v>
+        <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.730726833498001</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.091286158426426</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.735731053501144</v>
+        <v>-2.762192189980183</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.99663731271222</v>
+        <v>2.127784012795961</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.09729172722158</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.749661194759374</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.275389290571385</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.871684061557461</v>
+        <v>-2.8981451980365</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.126359241634654</v>
+        <v>2.257505941718394</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.09729172722158</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.933764326904334</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.267505985474378</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.894092179362333</v>
+        <v>-2.920553315841372</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.109512689415698</v>
+        <v>2.240659389499439</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.09729172722158</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.925881021807327</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.269559985024016</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.922316414939933</v>
+        <v>-2.948777551418972</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.100276994734295</v>
+        <v>2.231423694818036</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.115268479672889</v>
+        <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.938721072827749</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.325813702745863</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.931757340828463</v>
+        <v>-2.958218477307502</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.152754342100731</v>
+        <v>2.283901042184471</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.23769559721628</v>
+        <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.068431061075631</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.328704797291164</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.984030948164104</v>
+        <v>-3.010492084643143</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.134735993711775</v>
+        <v>2.265882693795516</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.185421989880639</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.039957991219548</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.326816610184939</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.06036092576501</v>
+        <v>-3.086822062244049</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.102315815565188</v>
+        <v>2.233462515648928</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.185421989880639</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.038069804113323</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.321636839787801</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.262614646089363</v>
+        <v>-3.289075782568402</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.016234557038309</v>
+        <v>2.147381257122049</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9831682695562856</v>
+        <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.911537801521573</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.320070849997954</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.424183071616619</v>
+        <v>-3.450644208095658</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.950041197037559</v>
+        <v>2.081187897121299</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8563853457584062</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.833902057452998</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.333144256863872</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.556484363714172</v>
+        <v>-3.582945500193211</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.910194087064456</v>
+        <v>2.041340787148197</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8563853457584062</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.846975464318916</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.325149453646812</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.742352674553402</v>
+        <v>-3.768813811032441</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.827851959511704</v>
+        <v>1.958998659595445</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6978197524384585</v>
+        <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.743841305109888</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.323673494773814</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.770253461662875</v>
+        <v>-3.796714598141914</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.815215685794917</v>
+        <v>1.946362385878658</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6632228282955237</v>
+        <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.721607191751129</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.320437938751013</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.892779564365769</v>
+        <v>-3.919240700844808</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.762969688690958</v>
+        <v>1.894116388774699</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5406967255926298</v>
+        <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.644855974106591</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.387143898341517</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.123294060551357</v>
+        <v>-4.149755197030396</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.737469849807227</v>
+        <v>1.868616549890967</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3101822294070411</v>
+        <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.573253235985742</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.527455617343364</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.380014878546181</v>
+        <v>-4.40647601502522</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.775093241611144</v>
+        <v>1.906239941694885</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2017676552632263</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.6485162105013</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.596435886489004</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.534001296322321</v>
+        <v>-4.56046243280136</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.782478943646328</v>
+        <v>1.913625643730068</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2017676552632263</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.71749647964694</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.582487088609124</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.483479392494655</v>
+        <v>-4.509940528973694</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.788738907297515</v>
+        <v>1.919885607381255</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2017676552632263</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.703547681767061</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.594357577664538</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.73595454650238</v>
+        <v>-4.762415682981419</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.699619334749839</v>
+        <v>1.83076603483358</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2017676552632263</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.715418170822474</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.595568112183482</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.028850302981792</v>
+        <v>-5.055311439460831</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.583671566677018</v>
+        <v>1.714818266760759</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2017676552632263</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.716628705341418</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.599689854410804</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.186394374711234</v>
+        <v>-5.212855511190273</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.524775680212563</v>
+        <v>1.655922380296303</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1348658501229518</v>
+        <v>0.23732834414886</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.680609364484575</v>
+        <v>3.883818015575476</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.594767707146993</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.464358770294507</v>
+        <v>-5.490819906773546</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.408667774715443</v>
+        <v>1.539814474799183</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.04524611583746752</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.621915376649474</v>
+        <v>3.825124027740375</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.756971763846037</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.581326462933398</v>
+        <v>-5.607787599412437</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.524084754358931</v>
+        <v>1.655231454442671</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.04524611583746752</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.784119433348518</v>
+        <v>3.987328084439419</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.751818401809851</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.666044405154351</v>
+        <v>-5.69250554163339</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.485044215434363</v>
+        <v>1.616190915518104</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.03986991309057886</v>
+        <v>0.06259258093532938</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.727896453955504</v>
+        <v>3.931105105046405</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.762047819378342</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.747979223423235</v>
+        <v>-5.774440359902274</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.462499705695302</v>
+        <v>1.593646405779042</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.04980465867765904</v>
+        <v>0.05265783534824919</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.732165024171747</v>
+        <v>3.935373675262649</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.770973457834245</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.849955345671642</v>
+        <v>-5.876416482150681</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.430634895251841</v>
+        <v>1.561781595335581</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1517807809260666</v>
+        <v>-0.04931828690015838</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.679904989278605</v>
+        <v>3.883113640369506</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.76312634507842</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.73994906219442</v>
+        <v>-5.766410198673459</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.466790295886905</v>
+        <v>1.597936995970645</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1285762090087914</v>
+        <v>-0.02611371498288317</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.685980619673145</v>
+        <v>3.889189270764047</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.767376355800395</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.596889486453495</v>
+        <v>-5.623350622932534</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.528264136905249</v>
+        <v>1.65941083698899</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1205627824188121</v>
+        <v>-0.0181002883929039</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.695038686349108</v>
+        <v>3.898247337440008</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.774637238682931</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.295442760981658</v>
+        <v>-5.321903897460697</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.65610370997652</v>
+        <v>1.787250410060261</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1808839430530251</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.883167604514746</v>
+        <v>4.086376255605647</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.775608416435641</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.320033005216842</v>
+        <v>-5.346494141695881</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.647238790035157</v>
+        <v>1.778385490118898</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1808839430530251</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.884138782267457</v>
+        <v>4.087347433358357</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.776451320815397</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.268994629210321</v>
+        <v>-5.29545576568936</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.668497044817521</v>
+        <v>1.799643744901261</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1808839430530251</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.884981686647212</v>
+        <v>4.088190337738113</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.795489419689542</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.22785533434369</v>
+        <v>-5.202626284116455</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.703990861638319</v>
+        <v>1.855813636404569</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2220232379196559</v>
+        <v>0.3761759186518381</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.928703362441336</v>
+        <v>4.162926125556001</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.611673415813477</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.117249194264089</v>
+        <v>-5.092020144036853</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.564417313794094</v>
+        <v>1.716240088560344</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.332629377999258</v>
+        <v>0.4867820587314401</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.811251042613032</v>
+        <v>4.045473805727696</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.615175459887441</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.247829928794931</v>
+        <v>-5.222600878567696</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.515687064055721</v>
+        <v>1.66750983882197</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2020486434684154</v>
+        <v>0.3562013242005976</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.736404645968491</v>
+        <v>3.970627409083155</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.599602278963523</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.083333594603969</v>
+        <v>-5.058104544376734</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.565912416808188</v>
+        <v>1.717735191574438</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2020486434684154</v>
+        <v>0.3562013242005976</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.720831465044573</v>
+        <v>3.955054228159238</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.598789989399953</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.110703527288401</v>
+        <v>-5.085474477061166</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.554152154170845</v>
+        <v>1.705974928937095</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2020486434684154</v>
+        <v>0.3562013242005976</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.720019175481003</v>
+        <v>3.954241938595668</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.608658768525026</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.121088722178291</v>
+        <v>-5.095859671951056</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.559866855339962</v>
+        <v>1.711689630106211</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1916634485785261</v>
+        <v>0.3458161293107083</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.723656837672142</v>
+        <v>3.957879600786806</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.679495774301451</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.139676880900516</v>
+        <v>-5.114447830673281</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.623268597627497</v>
+        <v>1.775091372393746</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1730752898563008</v>
+        <v>0.3272279705884829</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.783340948215232</v>
+        <v>4.017563711329896</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.676364785119749</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.139975427596552</v>
+        <v>-5.114746377369316</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.620018189767381</v>
+        <v>1.77184096453363</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1730752898563008</v>
+        <v>0.3272279705884829</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.78020995903353</v>
+        <v>4.014432722148195</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.680895680059141</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.039152293906124</v>
+        <v>-5.013923243678889</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.664878338182944</v>
+        <v>1.816701112949193</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1855395053406546</v>
+        <v>0.3396921860728367</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.792219383263534</v>
+        <v>4.026442146378198</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.681024933537684</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.848370933153717</v>
+        <v>-4.823141882926482</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.74132013596245</v>
+        <v>1.893142910728699</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.376320866093062</v>
+        <v>0.5304735468252442</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.906817453193521</v>
+        <v>4.141040216308186</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.66086177927528</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.829854079111897</v>
+        <v>-4.804625028884661</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.728563723316775</v>
+        <v>1.880386498083024</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3892509955182702</v>
+        <v>0.5434036762504524</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.894412376586243</v>
+        <v>4.128635139700908</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.695828715887339</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.804660894610579</v>
+        <v>-4.779431844383343</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.77360793372936</v>
+        <v>1.925430708495609</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4144441800195885</v>
+        <v>0.5685968607517707</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.944495223899092</v>
+        <v>4.178717987013757</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.689515283788777</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.792606767697616</v>
+        <v>-4.767377717470381</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.772116152395983</v>
+        <v>1.923938927162232</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4264983069325514</v>
+        <v>0.5806509876647336</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.945414267948308</v>
+        <v>4.179637031062972</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.691395913972912</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.799230014387974</v>
+        <v>-4.774000964160739</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.771347483903976</v>
+        <v>1.923170258670225</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.419875060242193</v>
+        <v>0.5740277409743753</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.943320950118228</v>
+        <v>4.177543713232893</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.704246939850795</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.696349424859381</v>
+        <v>-4.671120374632146</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.825350745593295</v>
+        <v>1.977173520359544</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5227556497707859</v>
+        <v>0.6769083305029682</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.017900329713266</v>
+        <v>4.252123092827931</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.724449610024389</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.719791464039468</v>
+        <v>-4.694562413812233</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.836176600094855</v>
+        <v>1.987999374861104</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5227556497707859</v>
+        <v>0.6769083305029682</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.038102999886861</v>
+        <v>4.272325763001525</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.724449610024389</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.73786397233108</v>
+        <v>-4.712634922103844</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.82894759677821</v>
+        <v>1.980770371544459</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5227556497707859</v>
+        <v>0.6769083305029682</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.038102999886861</v>
+        <v>4.272325763001525</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.684701523617856</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.969037766207712</v>
+        <v>-4.943808715980476</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.696729992821024</v>
+        <v>1.848552767587273</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5227556497707859</v>
+        <v>0.6769083305029682</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.998354913480328</v>
+        <v>4.232577676594993</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.691724142614796</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.937751745667256</v>
+        <v>-4.912522695440021</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.716267020034146</v>
+        <v>1.868089794800395</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5540416703112413</v>
+        <v>0.7081943510434235</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.024149144801541</v>
+        <v>4.258371907916206</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.7908951421877</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.784726353553972</v>
+        <v>-4.759497303326737</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.876648176452364</v>
+        <v>2.028470951218613</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7070670624245254</v>
+        <v>0.8612197431567077</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.215135379642415</v>
+        <v>4.44935814275708</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.978361367095992</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.813033667427242</v>
+        <v>-4.787804617200007</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.052791475811348</v>
+        <v>2.204614250577597</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7070670624245254</v>
+        <v>0.8612197431567077</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.402601604550708</v>
+        <v>4.636824367665373</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.947764318450075</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.979626892540765</v>
+        <v>-4.954397842313529</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.955557137120022</v>
+        <v>2.107379911886271</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.540473837311003</v>
+        <v>0.6946265180431852</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.272048620836677</v>
+        <v>4.506271383951341</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.951440721111792</v>
+        <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.876620771807296</v>
+        <v>-4.781333462931229</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.000435988075127</v>
+        <v>2.180282066300909</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.540473837311003</v>
+        <v>0.6946265180431852</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.275725023498395</v>
+        <v>4.509947786613059</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.842518422725566</v>
+        <v>3.787538917305512</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.080135432225489</v>
+        <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.936253652735314</v>
+        <v>-4.819124510064246</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.105277546817616</v>
+        <v>2.162783702571197</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.5335510266498745</v>
+        <v>0.6946265180431852</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.400266048215413</v>
+        <v>4.507565841736554</v>
       </c>
     </row>
   </sheetData>
